--- a/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>BWTL</t>
   </si>
@@ -656,403 +656,416 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E8" s="3">
         <v>11200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>10500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>10400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>14000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9600</v>
-      </c>
-      <c r="N8" s="3">
-        <v>7600</v>
       </c>
       <c r="O8" s="3">
         <v>7600</v>
       </c>
       <c r="P8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Q8" s="3">
         <v>8900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>7100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>9300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>22900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>8300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6300</v>
-      </c>
-      <c r="AD8" s="3">
-        <v>5900</v>
       </c>
       <c r="AE8" s="3">
         <v>5900</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E9" s="3">
         <v>6000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>7300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5200</v>
-      </c>
-      <c r="N9" s="3">
-        <v>3800</v>
       </c>
       <c r="O9" s="3">
         <v>3800</v>
       </c>
       <c r="P9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Q9" s="3">
         <v>4100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>13200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>9300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4000</v>
-      </c>
-      <c r="Z9" s="3">
-        <v>3600</v>
       </c>
       <c r="AA9" s="3">
         <v>3600</v>
       </c>
       <c r="AB9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AC9" s="3">
         <v>4500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E10" s="3">
         <v>5200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4100</v>
-      </c>
-      <c r="F10" s="3">
-        <v>4000</v>
       </c>
       <c r="G10" s="3">
         <v>4000</v>
       </c>
       <c r="H10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="I10" s="3">
         <v>5600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>4700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>4300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>6800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4400</v>
-      </c>
-      <c r="N10" s="3">
-        <v>3800</v>
       </c>
       <c r="O10" s="3">
         <v>3800</v>
       </c>
       <c r="P10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Q10" s="3">
         <v>4800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>2500</v>
-      </c>
-      <c r="R10" s="3">
-        <v>3100</v>
       </c>
       <c r="S10" s="3">
         <v>3100</v>
       </c>
       <c r="T10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="U10" s="3">
         <v>4200</v>
-      </c>
-      <c r="U10" s="3">
-        <v>3100</v>
       </c>
       <c r="V10" s="3">
         <v>3100</v>
       </c>
       <c r="W10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="X10" s="3">
         <v>9700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>6700</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>2900</v>
       </c>
       <c r="Z10" s="3">
         <v>2900</v>
       </c>
       <c r="AA10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AB10" s="3">
         <v>2800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>2600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1084,8 +1097,9 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1173,8 +1187,11 @@
       <c r="AE12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1262,8 +1279,11 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1285,11 +1305,11 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1297,11 +1317,11 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>100</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1318,8 +1338,8 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1327,17 +1347,17 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1345,14 +1365,17 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>100</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1414,14 +1437,14 @@
         <v>300</v>
       </c>
       <c r="W15" s="3">
+        <v>300</v>
+      </c>
+      <c r="X15" s="3">
         <v>800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>500</v>
       </c>
-      <c r="Y15" s="3">
-        <v>300</v>
-      </c>
       <c r="Z15" s="3">
         <v>300</v>
       </c>
@@ -1429,19 +1452,22 @@
         <v>300</v>
       </c>
       <c r="AB15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC15" s="3">
         <v>200</v>
       </c>
-      <c r="AC15" s="3">
-        <v>300</v>
-      </c>
       <c r="AD15" s="3">
         <v>300</v>
       </c>
       <c r="AE15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF15" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1470,186 +1496,193 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E17" s="3">
         <v>10400</v>
-      </c>
-      <c r="E17" s="3">
-        <v>9300</v>
       </c>
       <c r="F17" s="3">
         <v>9300</v>
       </c>
       <c r="G17" s="3">
+        <v>9300</v>
+      </c>
+      <c r="H17" s="3">
         <v>9000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>12600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>8700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>6800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>22500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>15500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>7700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
         <v>800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>500</v>
       </c>
-      <c r="J18" s="3">
-        <v>300</v>
-      </c>
       <c r="K18" s="3">
+        <v>300</v>
+      </c>
+      <c r="L18" s="3">
         <v>500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>600</v>
-      </c>
-      <c r="U18" s="3">
-        <v>100</v>
       </c>
       <c r="V18" s="3">
         <v>100</v>
       </c>
       <c r="W18" s="3">
+        <v>100</v>
+      </c>
+      <c r="X18" s="3">
         <v>400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>100</v>
       </c>
-      <c r="Z18" s="3">
-        <v>0</v>
-      </c>
       <c r="AA18" s="3">
         <v>0</v>
       </c>
       <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-100</v>
       </c>
-      <c r="AE18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1681,13 +1714,14 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1699,11 +1733,11 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1711,17 +1745,17 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1729,11 +1763,11 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
         <v>0</v>
       </c>
@@ -1741,126 +1775,132 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
         <v>100</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
       </c>
       <c r="Z20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB20" s="3">
         <v>100</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>200</v>
+      </c>
+      <c r="E21" s="3">
         <v>1100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>500</v>
       </c>
-      <c r="F21" s="3">
-        <v>300</v>
-      </c>
       <c r="G21" s="3">
+        <v>300</v>
+      </c>
+      <c r="H21" s="3">
         <v>400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>100</v>
       </c>
-      <c r="R21" s="3">
-        <v>300</v>
-      </c>
       <c r="S21" s="3">
+        <v>300</v>
+      </c>
+      <c r="T21" s="3">
         <v>400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1100</v>
       </c>
-      <c r="Y21" s="3">
-        <v>300</v>
-      </c>
       <c r="Z21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA21" s="3">
         <v>500</v>
       </c>
-      <c r="AA21" s="3">
-        <v>300</v>
-      </c>
       <c r="AB21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC21" s="3">
         <v>800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>100</v>
       </c>
-      <c r="AE21" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1922,10 +1962,10 @@
         <v>100</v>
       </c>
       <c r="W22" s="3">
+        <v>100</v>
+      </c>
+      <c r="X22" s="3">
         <v>200</v>
-      </c>
-      <c r="X22" s="3">
-        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
@@ -1937,7 +1977,7 @@
         <v>100</v>
       </c>
       <c r="AB22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -1948,106 +1988,112 @@
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E23" s="3">
         <v>800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-100</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
         <v>1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
       <c r="T23" s="3">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3">
         <v>500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="X23" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y23" s="3">
         <v>500</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
       <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>200</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
       <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
         <v>500</v>
       </c>
-      <c r="AC23" s="3">
-        <v>300</v>
-      </c>
       <c r="AD23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE23" s="3">
         <v>-200</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
@@ -2055,79 +2101,82 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>300</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X24" s="3">
         <v>100</v>
       </c>
       <c r="Y24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>100</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-100</v>
       </c>
-      <c r="AE24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2215,186 +2264,195 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E26" s="3">
         <v>600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
-        <v>300</v>
-      </c>
       <c r="J26" s="3">
+        <v>300</v>
+      </c>
+      <c r="K26" s="3">
         <v>100</v>
       </c>
-      <c r="K26" s="3">
-        <v>300</v>
-      </c>
       <c r="L26" s="3">
+        <v>300</v>
+      </c>
+      <c r="M26" s="3">
         <v>1000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>100</v>
       </c>
-      <c r="O26" s="3">
-        <v>300</v>
-      </c>
       <c r="P26" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q26" s="3">
         <v>700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
       <c r="T26" s="3">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>200</v>
       </c>
-      <c r="X26" s="3">
-        <v>300</v>
-      </c>
       <c r="Y26" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>100</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
       <c r="AB26" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD26" s="3">
         <v>200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-100</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E27" s="3">
         <v>600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>800</v>
       </c>
-      <c r="I27" s="3">
-        <v>300</v>
-      </c>
       <c r="J27" s="3">
+        <v>300</v>
+      </c>
+      <c r="K27" s="3">
         <v>100</v>
       </c>
-      <c r="K27" s="3">
-        <v>300</v>
-      </c>
       <c r="L27" s="3">
+        <v>300</v>
+      </c>
+      <c r="M27" s="3">
         <v>1000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>100</v>
       </c>
-      <c r="O27" s="3">
-        <v>300</v>
-      </c>
       <c r="P27" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q27" s="3">
         <v>700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
       <c r="T27" s="3">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3">
         <v>400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>200</v>
       </c>
-      <c r="X27" s="3">
-        <v>300</v>
-      </c>
       <c r="Y27" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>100</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
       <c r="AB27" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AC27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD27" s="3">
         <v>200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-100</v>
       </c>
-      <c r="AE27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,8 +2540,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2523,8 +2584,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
@@ -2541,38 +2602,41 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>-200</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="3">
         <v>200</v>
       </c>
       <c r="Z29" s="3">
+        <v>200</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-200</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>200</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2660,8 +2724,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2749,13 +2816,16 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -2767,11 +2837,11 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -2779,17 +2849,17 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -2797,11 +2867,11 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -2809,126 +2879,132 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W32" s="3">
         <v>-100</v>
       </c>
       <c r="X32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
       <c r="Z32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3">
         <v>-300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-100</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
-        <v>0</v>
-      </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E33" s="3">
         <v>600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
-        <v>300</v>
-      </c>
       <c r="J33" s="3">
+        <v>300</v>
+      </c>
+      <c r="K33" s="3">
         <v>100</v>
       </c>
-      <c r="K33" s="3">
-        <v>300</v>
-      </c>
       <c r="L33" s="3">
+        <v>300</v>
+      </c>
+      <c r="M33" s="3">
         <v>1000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>100</v>
       </c>
-      <c r="O33" s="3">
-        <v>300</v>
-      </c>
       <c r="P33" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q33" s="3">
         <v>700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
       <c r="T33" s="3">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3">
         <v>400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
       <c r="AB33" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AC33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD33" s="3">
         <v>400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-100</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3016,191 +3092,200 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E35" s="3">
         <v>600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
-        <v>300</v>
-      </c>
       <c r="J35" s="3">
+        <v>300</v>
+      </c>
+      <c r="K35" s="3">
         <v>100</v>
       </c>
-      <c r="K35" s="3">
-        <v>300</v>
-      </c>
       <c r="L35" s="3">
+        <v>300</v>
+      </c>
+      <c r="M35" s="3">
         <v>1000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>100</v>
       </c>
-      <c r="O35" s="3">
-        <v>300</v>
-      </c>
       <c r="P35" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q35" s="3">
         <v>700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
       <c r="T35" s="3">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3">
         <v>400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
       <c r="AB35" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AC35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD35" s="3">
         <v>400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-100</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3232,8 +3317,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3265,102 +3351,106 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2800</v>
+      </c>
+      <c r="E41" s="3">
         <v>7200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6300</v>
-      </c>
-      <c r="F41" s="3">
-        <v>7300</v>
       </c>
       <c r="G41" s="3">
         <v>7300</v>
       </c>
       <c r="H41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="I41" s="3">
         <v>7800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>9100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>5200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3600</v>
-      </c>
-      <c r="Z41" s="3">
-        <v>4000</v>
       </c>
       <c r="AA41" s="3">
         <v>4000</v>
       </c>
       <c r="AB41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AC41" s="3">
         <v>4300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1200</v>
+        <v>5200</v>
       </c>
       <c r="E42" s="3">
         <v>1200</v>
@@ -3411,13 +3501,13 @@
         <v>1200</v>
       </c>
       <c r="U42" s="3">
+        <v>1200</v>
+      </c>
+      <c r="V42" s="3">
         <v>1000</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>900</v>
-      </c>
-      <c r="W42" s="3">
-        <v>1000</v>
       </c>
       <c r="X42" s="3">
         <v>1000</v>
@@ -3443,8 +3533,11 @@
       <c r="AE42" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3494,11 +3587,11 @@
         <v>0</v>
       </c>
       <c r="S43" s="3">
+        <v>0</v>
+      </c>
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
@@ -3532,97 +3625,103 @@
       <c r="AE43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E44" s="3">
         <v>5900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6500</v>
-      </c>
-      <c r="F44" s="3">
-        <v>5700</v>
       </c>
       <c r="G44" s="3">
         <v>5700</v>
       </c>
       <c r="H44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="I44" s="3">
         <v>5800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>5300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>4200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4000</v>
-      </c>
-      <c r="S44" s="3">
-        <v>4200</v>
       </c>
       <c r="T44" s="3">
         <v>4200</v>
       </c>
       <c r="U44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V44" s="3">
         <v>4400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3630,43 +3729,43 @@
         <v>400</v>
       </c>
       <c r="E45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F45" s="3">
+        <v>300</v>
+      </c>
+      <c r="G45" s="3">
         <v>400</v>
       </c>
-      <c r="G45" s="3">
-        <v>300</v>
-      </c>
       <c r="H45" s="3">
+        <v>300</v>
+      </c>
+      <c r="I45" s="3">
         <v>200</v>
       </c>
-      <c r="I45" s="3">
-        <v>300</v>
-      </c>
       <c r="J45" s="3">
         <v>300</v>
       </c>
       <c r="K45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="L45" s="3">
         <v>200</v>
       </c>
       <c r="M45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N45" s="3">
         <v>300</v>
       </c>
       <c r="O45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P45" s="3">
         <v>200</v>
       </c>
       <c r="Q45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R45" s="3">
         <v>300</v>
@@ -3687,7 +3786,7 @@
         <v>300</v>
       </c>
       <c r="X45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Y45" s="3">
         <v>400</v>
@@ -3696,7 +3795,7 @@
         <v>400</v>
       </c>
       <c r="AA45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AB45" s="3">
         <v>300</v>
@@ -3705,102 +3804,108 @@
         <v>300</v>
       </c>
       <c r="AD45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE45" s="3">
         <v>400</v>
       </c>
-      <c r="AE45" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E46" s="3">
         <v>14700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>15100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>15000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>12700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>12000</v>
-      </c>
-      <c r="Q46" s="3">
-        <v>10300</v>
       </c>
       <c r="R46" s="3">
         <v>10300</v>
       </c>
       <c r="S46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="T46" s="3">
         <v>10500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>10900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>9600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>9400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>9700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>8900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>8500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3808,29 +3913,29 @@
         <v>300</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F47" s="3">
         <v>0</v>
       </c>
       <c r="G47" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="H47" s="3">
         <v>300</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J47" s="3">
         <v>0</v>
       </c>
       <c r="K47" s="3">
+        <v>0</v>
+      </c>
+      <c r="L47" s="3">
         <v>700</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -3847,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="R47" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="S47" s="3">
         <v>800</v>
@@ -3862,7 +3967,7 @@
         <v>800</v>
       </c>
       <c r="W47" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="X47" s="3">
         <v>300</v>
@@ -3886,99 +3991,105 @@
         <v>300</v>
       </c>
       <c r="AE47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E48" s="3">
         <v>13000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>13200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>12900</v>
       </c>
       <c r="H48" s="3">
         <v>12900</v>
       </c>
       <c r="I48" s="3">
+        <v>12900</v>
+      </c>
+      <c r="J48" s="3">
         <v>13800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14500</v>
-      </c>
-      <c r="O48" s="3">
-        <v>14600</v>
       </c>
       <c r="P48" s="3">
         <v>14600</v>
       </c>
       <c r="Q48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="R48" s="3">
         <v>14900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>13700</v>
-      </c>
-      <c r="T48" s="3">
-        <v>14000</v>
       </c>
       <c r="U48" s="3">
         <v>14000</v>
       </c>
       <c r="V48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="W48" s="3">
         <v>13000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>12100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>10500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>9800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>9600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>9500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4033,14 +4144,14 @@
       <c r="T49" s="3">
         <v>0</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>8</v>
+      <c r="U49" s="3">
+        <v>0</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
@@ -4052,11 +4163,11 @@
         <v>0</v>
       </c>
       <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="3">
         <v>100</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
-      </c>
       <c r="AC49" s="3">
         <v>0</v>
       </c>
@@ -4066,8 +4177,11 @@
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4155,8 +4269,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4244,8 +4361,11 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4297,17 +4417,17 @@
       <c r="S52" s="3">
         <v>0</v>
       </c>
-      <c r="T52" s="3" t="s">
+      <c r="T52" s="3">
+        <v>0</v>
+      </c>
+      <c r="U52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U52" s="3">
-        <v>0</v>
-      </c>
       <c r="V52" s="3">
         <v>0</v>
       </c>
       <c r="W52" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="X52" s="3">
         <v>500</v>
@@ -4333,8 +4453,11 @@
       <c r="AE52" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4422,97 +4545,103 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>27200</v>
+      </c>
+      <c r="E54" s="3">
         <v>28100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>28000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>29400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26700</v>
-      </c>
-      <c r="Q54" s="3">
-        <v>25200</v>
       </c>
       <c r="R54" s="3">
         <v>25200</v>
       </c>
       <c r="S54" s="3">
+        <v>25200</v>
+      </c>
+      <c r="T54" s="3">
         <v>25100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>25700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>24400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>23300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>23600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>23700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>22100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>20300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>19700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>20000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>19300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>18900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4544,8 +4673,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4577,102 +4707,106 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1100</v>
-      </c>
-      <c r="P57" s="3">
-        <v>1000</v>
       </c>
       <c r="Q57" s="3">
         <v>1000</v>
       </c>
       <c r="R57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1000</v>
-      </c>
-      <c r="T57" s="3">
-        <v>1400</v>
       </c>
       <c r="U57" s="3">
         <v>1400</v>
       </c>
       <c r="V57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W57" s="3">
         <v>600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>800</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>1200</v>
       </c>
       <c r="AC57" s="3">
         <v>1200</v>
       </c>
       <c r="AD57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AE57" s="3">
         <v>600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E58" s="3">
         <v>500</v>
@@ -4702,10 +4836,10 @@
         <v>500</v>
       </c>
       <c r="N58" s="3">
+        <v>500</v>
+      </c>
+      <c r="O58" s="3">
         <v>600</v>
-      </c>
-      <c r="O58" s="3">
-        <v>500</v>
       </c>
       <c r="P58" s="3">
         <v>500</v>
@@ -4723,7 +4857,7 @@
         <v>500</v>
       </c>
       <c r="U58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="V58" s="3">
         <v>400</v>
@@ -4732,357 +4866,369 @@
         <v>400</v>
       </c>
       <c r="X58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Y58" s="3">
         <v>300</v>
       </c>
       <c r="Z58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AA58" s="3">
         <v>200</v>
       </c>
       <c r="AB58" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AC58" s="3">
         <v>400</v>
       </c>
       <c r="AD58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AE58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1200</v>
-      </c>
-      <c r="W59" s="3">
-        <v>1000</v>
       </c>
       <c r="X59" s="3">
         <v>1000</v>
       </c>
       <c r="Y59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z59" s="3">
         <v>700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E60" s="3">
         <v>3200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E61" s="3">
         <v>5700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>8200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>8300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E62" s="3">
         <v>2000</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1900</v>
       </c>
       <c r="F62" s="3">
         <v>1900</v>
       </c>
       <c r="G62" s="3">
-        <v>1800</v>
+        <v>1900</v>
       </c>
       <c r="H62" s="3">
         <v>1800</v>
       </c>
       <c r="I62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J62" s="3">
         <v>1700</v>
-      </c>
-      <c r="J62" s="3">
-        <v>2100</v>
       </c>
       <c r="K62" s="3">
         <v>2100</v>
       </c>
       <c r="L62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="M62" s="3">
         <v>2200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2100</v>
-      </c>
-      <c r="O62" s="3">
-        <v>2000</v>
       </c>
       <c r="P62" s="3">
         <v>2000</v>
       </c>
       <c r="Q62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="R62" s="3">
         <v>1700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1900</v>
-      </c>
-      <c r="S62" s="3">
-        <v>1700</v>
       </c>
       <c r="T62" s="3">
         <v>1700</v>
       </c>
       <c r="U62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="V62" s="3">
         <v>1500</v>
-      </c>
-      <c r="V62" s="3">
-        <v>600</v>
       </c>
       <c r="W62" s="3">
         <v>600</v>
@@ -5091,10 +5237,10 @@
         <v>600</v>
       </c>
       <c r="Y62" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z62" s="3">
         <v>500</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>800</v>
       </c>
       <c r="AA62" s="3">
         <v>800</v>
@@ -5103,16 +5249,19 @@
         <v>800</v>
       </c>
       <c r="AC62" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AD62" s="3">
         <v>700</v>
       </c>
       <c r="AE62" s="3">
+        <v>700</v>
+      </c>
+      <c r="AF62" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5200,8 +5349,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5289,8 +5441,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5378,97 +5533,103 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E66" s="3">
         <v>11000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>13900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>12400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>12100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>10800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>9600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5500,8 +5661,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5589,8 +5751,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5678,8 +5843,11 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5767,8 +5935,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5856,97 +6027,103 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E72" s="3">
         <v>8400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>4800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4100</v>
-      </c>
-      <c r="S72" s="3">
-        <v>4200</v>
       </c>
       <c r="T72" s="3">
         <v>4200</v>
       </c>
       <c r="U72" s="3">
+        <v>4200</v>
+      </c>
+      <c r="V72" s="3">
         <v>3800</v>
-      </c>
-      <c r="V72" s="3">
-        <v>3700</v>
       </c>
       <c r="W72" s="3">
         <v>3700</v>
       </c>
       <c r="X72" s="3">
+        <v>3700</v>
+      </c>
+      <c r="Y72" s="3">
         <v>3800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>3500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>3200</v>
-      </c>
-      <c r="AA72" s="3">
-        <v>3300</v>
       </c>
       <c r="AB72" s="3">
         <v>3300</v>
       </c>
       <c r="AC72" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AD72" s="3">
         <v>3000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>2800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6034,8 +6211,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6123,8 +6303,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6212,64 +6395,67 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17000</v>
+      </c>
+      <c r="E76" s="3">
         <v>17200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16500</v>
-      </c>
-      <c r="G76" s="3">
-        <v>16700</v>
       </c>
       <c r="H76" s="3">
         <v>16700</v>
       </c>
       <c r="I76" s="3">
+        <v>16700</v>
+      </c>
+      <c r="J76" s="3">
         <v>15900</v>
-      </c>
-      <c r="J76" s="3">
-        <v>15500</v>
       </c>
       <c r="K76" s="3">
         <v>15500</v>
       </c>
       <c r="L76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="M76" s="3">
         <v>15200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>12800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13000</v>
-      </c>
-      <c r="S76" s="3">
-        <v>13200</v>
       </c>
       <c r="T76" s="3">
         <v>13200</v>
       </c>
       <c r="U76" s="3">
-        <v>12800</v>
+        <v>13200</v>
       </c>
       <c r="V76" s="3">
         <v>12800</v>
@@ -6278,31 +6464,34 @@
         <v>12800</v>
       </c>
       <c r="X76" s="3">
+        <v>12800</v>
+      </c>
+      <c r="Y76" s="3">
         <v>12900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12300</v>
-      </c>
-      <c r="AA76" s="3">
-        <v>12400</v>
       </c>
       <c r="AB76" s="3">
         <v>12400</v>
       </c>
       <c r="AC76" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AD76" s="3">
         <v>12100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>11900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6390,191 +6579,200 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E81" s="3">
         <v>600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
-        <v>300</v>
-      </c>
       <c r="J81" s="3">
+        <v>300</v>
+      </c>
+      <c r="K81" s="3">
         <v>100</v>
       </c>
-      <c r="K81" s="3">
-        <v>300</v>
-      </c>
       <c r="L81" s="3">
+        <v>300</v>
+      </c>
+      <c r="M81" s="3">
         <v>1000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>100</v>
       </c>
-      <c r="O81" s="3">
-        <v>300</v>
-      </c>
       <c r="P81" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q81" s="3">
         <v>700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
       <c r="T81" s="3">
+        <v>0</v>
+      </c>
+      <c r="U81" s="3">
         <v>400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
       <c r="AB81" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AC81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD81" s="3">
         <v>400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-100</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6606,8 +6804,9 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6669,14 +6868,14 @@
         <v>300</v>
       </c>
       <c r="W83" s="3">
+        <v>300</v>
+      </c>
+      <c r="X83" s="3">
         <v>800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>500</v>
       </c>
-      <c r="Y83" s="3">
-        <v>300</v>
-      </c>
       <c r="Z83" s="3">
         <v>300</v>
       </c>
@@ -6684,19 +6883,22 @@
         <v>300</v>
       </c>
       <c r="AB83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC83" s="3">
         <v>200</v>
       </c>
-      <c r="AC83" s="3">
-        <v>300</v>
-      </c>
       <c r="AD83" s="3">
         <v>300</v>
       </c>
       <c r="AE83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6784,8 +6986,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6873,8 +7078,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6962,8 +7170,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7051,8 +7262,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7140,97 +7354,103 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E89" s="3">
         <v>1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-500</v>
       </c>
-      <c r="F89" s="3">
-        <v>300</v>
-      </c>
       <c r="G89" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H89" s="3">
+        <v>0</v>
+      </c>
+      <c r="I89" s="3">
         <v>1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-1900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>3100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>400</v>
-      </c>
-      <c r="W89" s="3">
-        <v>800</v>
       </c>
       <c r="X89" s="3">
         <v>800</v>
       </c>
       <c r="Y89" s="3">
+        <v>800</v>
+      </c>
+      <c r="Z89" s="3">
         <v>-100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>1100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7262,8 +7482,9 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7271,88 +7492,91 @@
         <v>-200</v>
       </c>
       <c r="E91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-200</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-300</v>
       </c>
       <c r="H91" s="3">
         <v>-300</v>
       </c>
       <c r="I91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J91" s="3">
         <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="M91" s="3">
         <v>-200</v>
       </c>
       <c r="N91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O91" s="3">
         <v>-300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-200</v>
       </c>
-      <c r="P91" s="3">
-        <v>0</v>
-      </c>
       <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
         <v>-400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-200</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
-      </c>
       <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7440,8 +7664,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7529,97 +7756,103 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
-      </c>
-      <c r="J94" s="3">
-        <v>-300</v>
       </c>
       <c r="K94" s="3">
         <v>-300</v>
       </c>
       <c r="L94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="M94" s="3">
         <v>-200</v>
       </c>
       <c r="N94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
       <c r="Q94" s="3">
+        <v>0</v>
+      </c>
+      <c r="R94" s="3">
         <v>-400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-700</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-400</v>
       </c>
       <c r="AB94" s="3">
         <v>-400</v>
       </c>
       <c r="AC94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="AD94" s="3">
         <v>100</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
-      </c>
       <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7651,8 +7884,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7740,8 +7974,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7829,8 +8066,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7918,8 +8158,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8007,8 +8250,11 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8022,25 +8268,25 @@
         <v>-100</v>
       </c>
       <c r="G100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H100" s="3">
         <v>-200</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
       </c>
       <c r="I100" s="3">
         <v>-100</v>
       </c>
       <c r="J100" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="K100" s="3">
         <v>-200</v>
       </c>
       <c r="L100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M100" s="3">
         <v>-1300</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-100</v>
       </c>
       <c r="N100" s="3">
         <v>-100</v>
@@ -8052,37 +8298,37 @@
         <v>-100</v>
       </c>
       <c r="Q100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R100" s="3">
         <v>1000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-100</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>2800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>700</v>
-      </c>
-      <c r="AA100" s="3">
-        <v>-100</v>
       </c>
       <c r="AB100" s="3">
         <v>-100</v>
@@ -8096,8 +8342,11 @@
       <c r="AE100" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8185,93 +8434,99 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3">
-        <v>300</v>
-      </c>
       <c r="O102" s="3">
+        <v>300</v>
+      </c>
+      <c r="P102" s="3">
         <v>700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-500</v>
       </c>
-      <c r="V102" s="3">
-        <v>300</v>
-      </c>
       <c r="W102" s="3">
+        <v>300</v>
+      </c>
+      <c r="X102" s="3">
         <v>100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>BWTL</t>
   </si>
@@ -656,232 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42766</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E8" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F8" s="3">
         <v>8200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>11200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>9500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>9200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>9100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>12900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>10500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>10400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>9700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>14000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>9600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>7600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>7600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>8900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>5300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>7000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>7100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>9300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>7200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>6900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>22900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>16000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>6900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>6500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>6400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>8300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>6300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>5900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -889,183 +902,195 @@
         <v>4700</v>
       </c>
       <c r="E9" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F9" s="3">
+        <v>4700</v>
+      </c>
+      <c r="G9" s="3">
         <v>6000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>5400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>5200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>5100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>7300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>6200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>5700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>5400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>7200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>5200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>4100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>3900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>4000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>5100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>4100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>3800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>13200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>9300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>4000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>3600</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>3600</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>4500</v>
       </c>
       <c r="AD9" s="3">
         <v>3600</v>
       </c>
       <c r="AE9" s="3">
+        <v>4500</v>
+      </c>
+      <c r="AF9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AG9" s="3">
         <v>3300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>3600</v>
+      </c>
+      <c r="F10" s="3">
         <v>3500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>5200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>4100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>4000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>4000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>5600</v>
-      </c>
-      <c r="J10" s="3">
-        <v>4300</v>
-      </c>
-      <c r="K10" s="3">
-        <v>4700</v>
       </c>
       <c r="L10" s="3">
         <v>4300</v>
       </c>
       <c r="M10" s="3">
+        <v>4700</v>
+      </c>
+      <c r="N10" s="3">
+        <v>4300</v>
+      </c>
+      <c r="O10" s="3">
         <v>6800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>4400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>3800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>3800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>4800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>2500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>3100</v>
-      </c>
-      <c r="T10" s="3">
-        <v>3100</v>
-      </c>
-      <c r="U10" s="3">
-        <v>4200</v>
       </c>
       <c r="V10" s="3">
         <v>3100</v>
       </c>
       <c r="W10" s="3">
+        <v>4200</v>
+      </c>
+      <c r="X10" s="3">
         <v>3100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Z10" s="3">
         <v>9700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>6700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>2900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>2900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>2800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>3800</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>2700</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>2600</v>
       </c>
       <c r="AF10" s="3">
         <v>2700</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3">
+        <v>2600</v>
+      </c>
+      <c r="AH10" s="3">
+        <v>2700</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1123,10 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1217,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,52 +1315,58 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>100</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>100</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1341,41 +1380,47 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>100</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1440,34 +1485,40 @@
         <v>300</v>
       </c>
       <c r="X15" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z15" s="3">
         <v>800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="AA15" s="3">
         <v>500</v>
       </c>
-      <c r="Z15" s="3">
-        <v>300</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>300</v>
-      </c>
       <c r="AB15" s="3">
         <v>300</v>
       </c>
       <c r="AC15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE15" s="3">
         <v>200</v>
       </c>
-      <c r="AD15" s="3">
-        <v>300</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>300</v>
-      </c>
       <c r="AF15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH15" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1548,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F17" s="3">
         <v>8400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>10400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>9300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>9000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>11800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>10000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>10100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>9200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>12600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>9000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>7400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>7200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>7800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>7100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>7000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>8700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>7100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>6800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>22500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>15500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>6800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>6500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>6400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>7700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>6200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>6000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>1100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>300</v>
       </c>
       <c r="L18" s="3">
         <v>500</v>
       </c>
       <c r="M18" s="3">
+        <v>300</v>
+      </c>
+      <c r="N18" s="3">
+        <v>500</v>
+      </c>
+      <c r="O18" s="3">
         <v>1400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>-100</v>
-      </c>
-      <c r="T18" s="3">
-        <v>100</v>
-      </c>
-      <c r="U18" s="3">
-        <v>600</v>
       </c>
       <c r="V18" s="3">
         <v>100</v>
       </c>
       <c r="W18" s="3">
+        <v>600</v>
+      </c>
+      <c r="X18" s="3">
         <v>100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z18" s="3">
         <v>400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>100</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>0</v>
-      </c>
       <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3">
         <v>600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>-100</v>
       </c>
-      <c r="AF18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,20 +1780,22 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3">
+        <v>100</v>
+      </c>
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
       <c r="G20" s="3">
         <v>0</v>
       </c>
@@ -1736,19 +1803,19 @@
         <v>0</v>
       </c>
       <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>100</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1760,147 +1827,159 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Y20" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>0</v>
-      </c>
       <c r="AA20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD20" s="3">
         <v>100</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>300</v>
-      </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
       <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+        <v>300</v>
+      </c>
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3">
+        <v>100</v>
+      </c>
+      <c r="F21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>500</v>
       </c>
-      <c r="G21" s="3">
-        <v>300</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>300</v>
+      </c>
+      <c r="J21" s="3">
         <v>400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>1500</v>
-      </c>
-      <c r="J21" s="3">
-        <v>800</v>
-      </c>
-      <c r="K21" s="3">
-        <v>500</v>
       </c>
       <c r="L21" s="3">
         <v>800</v>
       </c>
       <c r="M21" s="3">
+        <v>500</v>
+      </c>
+      <c r="N21" s="3">
+        <v>800</v>
+      </c>
+      <c r="O21" s="3">
         <v>1700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>100</v>
       </c>
-      <c r="S21" s="3">
-        <v>300</v>
-      </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
+        <v>300</v>
+      </c>
+      <c r="V21" s="3">
         <v>400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1100</v>
       </c>
-      <c r="Z21" s="3">
-        <v>300</v>
-      </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC21" s="3">
         <v>500</v>
       </c>
-      <c r="AB21" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE21" s="3">
         <v>800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>100</v>
       </c>
-      <c r="AF21" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH21" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1965,13 +2044,13 @@
         <v>100</v>
       </c>
       <c r="X22" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="Y22" s="3">
         <v>100</v>
       </c>
       <c r="Z22" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AA22" s="3">
         <v>100</v>
@@ -1980,10 +2059,10 @@
         <v>100</v>
       </c>
       <c r="AC22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
@@ -1991,100 +2070,112 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>-200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G23" s="3">
         <v>800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-100</v>
       </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
         <v>1100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
         <v>500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>100</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3">
-        <v>300</v>
-      </c>
       <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA23" s="3">
         <v>500</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
-      <c r="AB23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="3">
         <v>500</v>
       </c>
-      <c r="AD23" s="3">
-        <v>300</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG23" s="3">
         <v>-200</v>
       </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2092,70 +2183,70 @@
         <v>0</v>
       </c>
       <c r="E24" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
         <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
       <c r="M24" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
         <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="P24" s="3">
         <v>100</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
+        <v>100</v>
+      </c>
+      <c r="S24" s="3">
         <v>200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-100</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
-      </c>
-      <c r="T24" s="3">
-        <v>0</v>
-      </c>
       <c r="U24" s="3">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>100</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>0</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
@@ -2164,19 +2255,25 @@
         <v>0</v>
       </c>
       <c r="AC24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="3">
         <v>200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>-100</v>
       </c>
-      <c r="AF24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2364,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F26" s="3">
         <v>-100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
-        <v>300</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
+        <v>300</v>
+      </c>
+      <c r="M26" s="3">
         <v>100</v>
       </c>
-      <c r="L26" s="3">
-        <v>300</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
+        <v>300</v>
+      </c>
+      <c r="O26" s="3">
         <v>1000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>100</v>
       </c>
-      <c r="P26" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
+        <v>300</v>
+      </c>
+      <c r="S26" s="3">
         <v>700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>100</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>200</v>
       </c>
-      <c r="Y26" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
       <c r="AA26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
         <v>100</v>
       </c>
-      <c r="AB26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC26" s="3">
-        <v>300</v>
-      </c>
       <c r="AD26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF26" s="3">
         <v>200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>-100</v>
       </c>
-      <c r="AF26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F27" s="3">
         <v>-100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
         <v>800</v>
       </c>
-      <c r="J27" s="3">
-        <v>300</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
+        <v>300</v>
+      </c>
+      <c r="M27" s="3">
         <v>100</v>
       </c>
-      <c r="L27" s="3">
-        <v>300</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
+        <v>300</v>
+      </c>
+      <c r="O27" s="3">
         <v>1000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>100</v>
       </c>
-      <c r="P27" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
+        <v>300</v>
+      </c>
+      <c r="S27" s="3">
         <v>700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
         <v>400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>100</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>200</v>
       </c>
-      <c r="Y27" s="3">
-        <v>300</v>
-      </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
       <c r="AA27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3">
         <v>100</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="3">
-        <v>300</v>
-      </c>
       <c r="AD27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF27" s="3">
         <v>200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>-100</v>
       </c>
-      <c r="AF27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2658,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2587,11 +2708,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2605,38 +2726,44 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-200</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>200</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>-200</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>200</v>
       </c>
-      <c r="AE29" s="3" t="s">
+      <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2854,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,20 +2952,26 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
       <c r="G32" s="3">
         <v>0</v>
       </c>
@@ -2840,19 +2979,19 @@
         <v>0</v>
       </c>
       <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-100</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
@@ -2864,147 +3003,159 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>0</v>
-      </c>
       <c r="AA32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-100</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3">
         <v>800</v>
       </c>
-      <c r="J33" s="3">
-        <v>300</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
+        <v>300</v>
+      </c>
+      <c r="M33" s="3">
         <v>100</v>
       </c>
-      <c r="L33" s="3">
-        <v>300</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
+        <v>300</v>
+      </c>
+      <c r="O33" s="3">
         <v>1000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>100</v>
       </c>
-      <c r="P33" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
+        <v>300</v>
+      </c>
+      <c r="S33" s="3">
         <v>700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
         <v>400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>-200</v>
-      </c>
-      <c r="X33" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y33" s="3">
-        <v>600</v>
       </c>
       <c r="Z33" s="3">
         <v>200</v>
       </c>
       <c r="AA33" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-100</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC33" s="3">
-        <v>300</v>
-      </c>
       <c r="AD33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF33" s="3">
         <v>400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>-100</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3246,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
         <v>800</v>
       </c>
-      <c r="J35" s="3">
-        <v>300</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
+        <v>300</v>
+      </c>
+      <c r="M35" s="3">
         <v>100</v>
       </c>
-      <c r="L35" s="3">
-        <v>300</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
+        <v>300</v>
+      </c>
+      <c r="O35" s="3">
         <v>1000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>100</v>
       </c>
-      <c r="P35" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
+        <v>300</v>
+      </c>
+      <c r="S35" s="3">
         <v>700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3">
         <v>400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>-200</v>
-      </c>
-      <c r="X35" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y35" s="3">
-        <v>600</v>
       </c>
       <c r="Z35" s="3">
         <v>200</v>
       </c>
       <c r="AA35" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-100</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC35" s="3">
-        <v>300</v>
-      </c>
       <c r="AD35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF35" s="3">
         <v>400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>-100</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42766</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3487,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,111 +3523,119 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3500</v>
+      </c>
+      <c r="F41" s="3">
         <v>2800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>7200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>6300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>7300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>7300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>7800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>8100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>8400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>9100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>7400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>6600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>4400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>4700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>4800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>5200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>3900</v>
-      </c>
-      <c r="W41" s="3">
-        <v>4400</v>
-      </c>
-      <c r="X41" s="3">
-        <v>4100</v>
       </c>
       <c r="Y41" s="3">
         <v>4400</v>
       </c>
       <c r="Z41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AA41" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AB41" s="3">
         <v>3600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>4000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>4000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>4300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>3600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>3500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4800</v>
+      </c>
+      <c r="F42" s="3">
         <v>5200</v>
-      </c>
-      <c r="E42" s="3">
-        <v>1200</v>
-      </c>
-      <c r="F42" s="3">
-        <v>1200</v>
       </c>
       <c r="G42" s="3">
         <v>1200</v>
@@ -3504,16 +3683,16 @@
         <v>1200</v>
       </c>
       <c r="V42" s="3">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="W42" s="3">
-        <v>900</v>
+        <v>1200</v>
       </c>
       <c r="X42" s="3">
         <v>1000</v>
       </c>
       <c r="Y42" s="3">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="Z42" s="3">
         <v>1000</v>
@@ -3536,8 +3715,14 @@
       <c r="AF42" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3590,14 +3775,14 @@
         <v>0</v>
       </c>
       <c r="T43" s="3">
+        <v>0</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
@@ -3628,100 +3813,112 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F44" s="3">
         <v>5500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>5900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>6500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>5700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>5700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>5800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>5900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>5400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>5300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>4200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>4600</v>
-      </c>
-      <c r="O44" s="3">
-        <v>3900</v>
-      </c>
-      <c r="P44" s="3">
-        <v>4000</v>
       </c>
       <c r="Q44" s="3">
         <v>3900</v>
       </c>
       <c r="R44" s="3">
+        <v>4000</v>
+      </c>
+      <c r="S44" s="3">
+        <v>3900</v>
+      </c>
+      <c r="T44" s="3">
         <v>4400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>4000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>4200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>4200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>4400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>3800</v>
-      </c>
-      <c r="X44" s="3">
-        <v>4300</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>4100</v>
       </c>
       <c r="Z44" s="3">
         <v>4300</v>
       </c>
       <c r="AA44" s="3">
+        <v>4100</v>
+      </c>
+      <c r="AB44" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AC44" s="3">
         <v>3600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>3900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>4000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>4100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>3700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3729,10 +3926,10 @@
         <v>400</v>
       </c>
       <c r="E45" s="3">
+        <v>500</v>
+      </c>
+      <c r="F45" s="3">
         <v>400</v>
-      </c>
-      <c r="F45" s="3">
-        <v>300</v>
       </c>
       <c r="G45" s="3">
         <v>400</v>
@@ -3741,38 +3938,38 @@
         <v>300</v>
       </c>
       <c r="I45" s="3">
+        <v>400</v>
+      </c>
+      <c r="J45" s="3">
+        <v>300</v>
+      </c>
+      <c r="K45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
-        <v>300</v>
-      </c>
-      <c r="K45" s="3">
-        <v>300</v>
-      </c>
       <c r="L45" s="3">
+        <v>300</v>
+      </c>
+      <c r="M45" s="3">
+        <v>300</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
-        <v>300</v>
-      </c>
-      <c r="O45" s="3">
-        <v>300</v>
-      </c>
       <c r="P45" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>300</v>
+      </c>
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
-        <v>300</v>
-      </c>
-      <c r="S45" s="3">
-        <v>300</v>
-      </c>
       <c r="T45" s="3">
         <v>300</v>
       </c>
@@ -3789,159 +3986,171 @@
         <v>300</v>
       </c>
       <c r="Y45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Z45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AA45" s="3">
         <v>400</v>
       </c>
       <c r="AB45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AC45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AD45" s="3">
         <v>300</v>
       </c>
       <c r="AE45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG45" s="3">
         <v>400</v>
       </c>
-      <c r="AF45" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F46" s="3">
         <v>13900</v>
-      </c>
-      <c r="E46" s="3">
-        <v>14700</v>
-      </c>
-      <c r="F46" s="3">
-        <v>14400</v>
       </c>
       <c r="G46" s="3">
         <v>14700</v>
       </c>
       <c r="H46" s="3">
+        <v>14400</v>
+      </c>
+      <c r="I46" s="3">
+        <v>14700</v>
+      </c>
+      <c r="J46" s="3">
         <v>14600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>15100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>13400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>15000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>15100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>14600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>13500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>13000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>12700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>12000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>10300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>10300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>10500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>10900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>9600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>9400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>9700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>9900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>9300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>9000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>9100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>9500</v>
-      </c>
-      <c r="AD46" s="3">
-        <v>8900</v>
-      </c>
-      <c r="AE46" s="3">
-        <v>8500</v>
       </c>
       <c r="AF46" s="3">
         <v>8900</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>8500</v>
+      </c>
+      <c r="AH46" s="3">
+        <v>8900</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>300</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H47" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I47" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3">
         <v>700</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
@@ -3955,10 +4164,10 @@
         <v>0</v>
       </c>
       <c r="S47" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="T47" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="U47" s="3">
         <v>800</v>
@@ -3970,10 +4179,10 @@
         <v>800</v>
       </c>
       <c r="X47" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="Y47" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="Z47" s="3">
         <v>300</v>
@@ -3994,10 +4203,16 @@
         <v>300</v>
       </c>
       <c r="AF47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4005,82 +4220,82 @@
         <v>12900</v>
       </c>
       <c r="E48" s="3">
+        <v>13100</v>
+      </c>
+      <c r="F48" s="3">
+        <v>12900</v>
+      </c>
+      <c r="G48" s="3">
         <v>13000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>13400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>13200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>12900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>12900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>13800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>14300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>13700</v>
-      </c>
-      <c r="M48" s="3">
-        <v>14500</v>
-      </c>
-      <c r="N48" s="3">
-        <v>14300</v>
       </c>
       <c r="O48" s="3">
         <v>14500</v>
       </c>
       <c r="P48" s="3">
+        <v>14300</v>
+      </c>
+      <c r="Q48" s="3">
+        <v>14500</v>
+      </c>
+      <c r="R48" s="3">
         <v>14600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>14600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>14900</v>
-      </c>
-      <c r="S48" s="3">
-        <v>14000</v>
-      </c>
-      <c r="T48" s="3">
-        <v>13700</v>
       </c>
       <c r="U48" s="3">
         <v>14000</v>
       </c>
       <c r="V48" s="3">
+        <v>13700</v>
+      </c>
+      <c r="W48" s="3">
         <v>14000</v>
       </c>
-      <c r="W48" s="3">
-        <v>13000</v>
-      </c>
       <c r="X48" s="3">
-        <v>13100</v>
+        <v>14000</v>
       </c>
       <c r="Y48" s="3">
         <v>13000</v>
       </c>
       <c r="Z48" s="3">
+        <v>13100</v>
+      </c>
+      <c r="AA48" s="3">
+        <v>13000</v>
+      </c>
+      <c r="AB48" s="3">
         <v>12100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>10500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>9800</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>9600</v>
-      </c>
-      <c r="AD48" s="3">
-        <v>9500</v>
       </c>
       <c r="AE48" s="3">
         <v>9600</v>
@@ -4088,8 +4303,14 @@
       <c r="AF48" s="3">
         <v>9500</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>9600</v>
+      </c>
+      <c r="AH48" s="3">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4147,18 +4368,18 @@
       <c r="U49" s="3">
         <v>0</v>
       </c>
-      <c r="V49" s="3" t="s">
+      <c r="V49" s="3">
+        <v>0</v>
+      </c>
+      <c r="W49" s="3">
+        <v>0</v>
+      </c>
+      <c r="X49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W49" s="3" t="s">
+      <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>0</v>
-      </c>
       <c r="Z49" s="3">
         <v>0</v>
       </c>
@@ -4166,22 +4387,28 @@
         <v>0</v>
       </c>
       <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="3">
         <v>100</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="3">
-        <v>0</v>
-      </c>
       <c r="AE49" s="3">
         <v>0</v>
       </c>
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4499,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,8 +4597,14 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4420,20 +4659,20 @@
       <c r="T52" s="3">
         <v>0</v>
       </c>
-      <c r="U52" s="3" t="s">
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+      <c r="V52" s="3">
+        <v>0</v>
+      </c>
+      <c r="W52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
-      </c>
-      <c r="W52" s="3">
-        <v>0</v>
-      </c>
       <c r="X52" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Y52" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="3">
         <v>500</v>
@@ -4456,8 +4695,14 @@
       <c r="AF52" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3">
+        <v>500</v>
+      </c>
+      <c r="AH52" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4793,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E54" s="3">
+        <v>27100</v>
+      </c>
+      <c r="F54" s="3">
         <v>27200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>28100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>27800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>28000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>27900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>28400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>27200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>29400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>29600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>29200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>27900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>27600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>27400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>26700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>25200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>25200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>25100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>25700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>24400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>23300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>23600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>23700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>22100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>20300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>19700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>20000</v>
-      </c>
-      <c r="AD54" s="3">
-        <v>19300</v>
-      </c>
-      <c r="AE54" s="3">
-        <v>18900</v>
       </c>
       <c r="AF54" s="3">
         <v>19300</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3">
+        <v>18900</v>
+      </c>
+      <c r="AH54" s="3">
+        <v>19300</v>
+      </c>
+    </row>
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4931,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4967,108 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
+        <v>800</v>
+      </c>
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>2000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1100</v>
-      </c>
-      <c r="I57" s="3">
-        <v>1300</v>
-      </c>
-      <c r="J57" s="3">
-        <v>1600</v>
       </c>
       <c r="K57" s="3">
         <v>1300</v>
       </c>
       <c r="L57" s="3">
-        <v>1900</v>
+        <v>1600</v>
       </c>
       <c r="M57" s="3">
-        <v>1400</v>
+        <v>1300</v>
       </c>
       <c r="N57" s="3">
         <v>1900</v>
       </c>
       <c r="O57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="P57" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q57" s="3">
         <v>900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>1100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1000</v>
-      </c>
-      <c r="R57" s="3">
-        <v>1000</v>
-      </c>
-      <c r="S57" s="3">
-        <v>900</v>
       </c>
       <c r="T57" s="3">
         <v>1000</v>
       </c>
       <c r="U57" s="3">
+        <v>900</v>
+      </c>
+      <c r="V57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W57" s="3">
         <v>1400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>1300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>1200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>1200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4809,10 +5076,10 @@
         <v>400</v>
       </c>
       <c r="E58" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="F58" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="G58" s="3">
         <v>500</v>
@@ -4839,13 +5106,13 @@
         <v>500</v>
       </c>
       <c r="O58" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="P58" s="3">
         <v>500</v>
       </c>
       <c r="Q58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="R58" s="3">
         <v>500</v>
@@ -4860,280 +5127,298 @@
         <v>500</v>
       </c>
       <c r="V58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="W58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="X58" s="3">
         <v>400</v>
       </c>
       <c r="Y58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="Z58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AA58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC58" s="3">
         <v>200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>400</v>
       </c>
-      <c r="AE58" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF58" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1600</v>
+      </c>
+      <c r="F59" s="3">
         <v>1400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>2100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>1800</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="R59" s="3">
-        <v>600</v>
       </c>
       <c r="S59" s="3">
         <v>1400</v>
       </c>
       <c r="T59" s="3">
+        <v>600</v>
+      </c>
+      <c r="U59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="V59" s="3">
         <v>1100</v>
-      </c>
-      <c r="U59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="V59" s="3">
-        <v>600</v>
       </c>
       <c r="W59" s="3">
         <v>1200</v>
       </c>
       <c r="X59" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z59" s="3">
         <v>1000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>1000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>1200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>1000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>1100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>1000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F60" s="3">
         <v>2600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>3200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>3500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>3600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>3400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>3700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>3300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>5300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>5400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>5100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>3800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>3600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>3500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>3000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>2200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>2800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>2600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>3100</v>
-      </c>
-      <c r="V60" s="3">
-        <v>2500</v>
-      </c>
-      <c r="W60" s="3">
-        <v>2200</v>
       </c>
       <c r="X60" s="3">
         <v>2500</v>
       </c>
       <c r="Y60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="Z60" s="3">
+        <v>2500</v>
+      </c>
+      <c r="AA60" s="3">
         <v>2600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>2200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>2000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F61" s="3">
         <v>5600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>5900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>6000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>6200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>6300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>6400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>6600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>8300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>8500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>7500</v>
-      </c>
-      <c r="T61" s="3">
-        <v>7600</v>
-      </c>
-      <c r="U61" s="3">
-        <v>7700</v>
       </c>
       <c r="V61" s="3">
         <v>7600</v>
@@ -5142,126 +5427,138 @@
         <v>7700</v>
       </c>
       <c r="X61" s="3">
+        <v>7600</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>7700</v>
+      </c>
+      <c r="Z61" s="3">
         <v>7800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>7600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>6600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>5100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>4500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>4100</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>4200</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>4300</v>
       </c>
       <c r="AF61" s="3">
         <v>4200</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>4300</v>
+      </c>
+      <c r="AH61" s="3">
+        <v>4200</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E62" s="3">
         <v>1900</v>
-      </c>
-      <c r="E62" s="3">
-        <v>2000</v>
       </c>
       <c r="F62" s="3">
         <v>1900</v>
       </c>
       <c r="G62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="H62" s="3">
         <v>1900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="J62" s="3">
         <v>1800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>1800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>1700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>2100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2000</v>
-      </c>
-      <c r="R62" s="3">
-        <v>1700</v>
-      </c>
-      <c r="S62" s="3">
-        <v>1900</v>
       </c>
       <c r="T62" s="3">
         <v>1700</v>
       </c>
       <c r="U62" s="3">
+        <v>1900</v>
+      </c>
+      <c r="V62" s="3">
         <v>1700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="X62" s="3">
         <v>1500</v>
-      </c>
-      <c r="W62" s="3">
-        <v>600</v>
-      </c>
-      <c r="X62" s="3">
-        <v>600</v>
       </c>
       <c r="Y62" s="3">
         <v>600</v>
       </c>
       <c r="Z62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB62" s="3">
         <v>500</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>800</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>800</v>
       </c>
       <c r="AC62" s="3">
         <v>800</v>
       </c>
       <c r="AD62" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE62" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF62" s="3">
         <v>700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5649,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5747,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5845,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="F66" s="3">
         <v>10100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>11000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>11200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>11400</v>
-      </c>
-      <c r="H66" s="3">
-        <v>11300</v>
-      </c>
-      <c r="I66" s="3">
-        <v>11600</v>
       </c>
       <c r="J66" s="3">
         <v>11300</v>
       </c>
       <c r="K66" s="3">
+        <v>11600</v>
+      </c>
+      <c r="L66" s="3">
+        <v>11300</v>
+      </c>
+      <c r="M66" s="3">
         <v>13900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>14100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>14000</v>
-      </c>
-      <c r="N66" s="3">
-        <v>13700</v>
-      </c>
-      <c r="O66" s="3">
-        <v>13800</v>
       </c>
       <c r="P66" s="3">
         <v>13700</v>
       </c>
       <c r="Q66" s="3">
+        <v>13800</v>
+      </c>
+      <c r="R66" s="3">
+        <v>13700</v>
+      </c>
+      <c r="S66" s="3">
         <v>13200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>12400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>12100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>11900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>12500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>11600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>10500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>10900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>10800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>9600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>8000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>7300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>7600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>7200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>7000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5983,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6077,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6175,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6273,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6371,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>8100</v>
+      </c>
+      <c r="F72" s="3">
         <v>8200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>8400</v>
-      </c>
-      <c r="F72" s="3">
-        <v>7800</v>
-      </c>
-      <c r="G72" s="3">
-        <v>7700</v>
       </c>
       <c r="H72" s="3">
         <v>7800</v>
       </c>
       <c r="I72" s="3">
+        <v>7700</v>
+      </c>
+      <c r="J72" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K72" s="3">
         <v>7900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>6700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>6500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>6200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>5200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>4500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>3800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>4100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>4200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>4200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>3800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>3700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>3700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>3800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>3500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>3200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>3300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>3300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>3000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>2800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6567,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6665,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6763,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>16800</v>
+      </c>
+      <c r="F76" s="3">
         <v>17000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>17200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>16600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>16500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>16700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>15900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>15500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>15500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>15200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>14200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>13800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>13700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>13500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>12800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>13000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>13200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>13200</v>
-      </c>
-      <c r="V76" s="3">
-        <v>12800</v>
-      </c>
-      <c r="W76" s="3">
-        <v>12800</v>
       </c>
       <c r="X76" s="3">
         <v>12800</v>
       </c>
       <c r="Y76" s="3">
+        <v>12800</v>
+      </c>
+      <c r="Z76" s="3">
+        <v>12800</v>
+      </c>
+      <c r="AA76" s="3">
         <v>12900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>12500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>12300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>12400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>12400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>12100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>11900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6959,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42766</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
-        <v>0</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
+        <v>0</v>
+      </c>
+      <c r="K81" s="3">
         <v>800</v>
       </c>
-      <c r="J81" s="3">
-        <v>300</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
+        <v>300</v>
+      </c>
+      <c r="M81" s="3">
         <v>100</v>
       </c>
-      <c r="L81" s="3">
-        <v>300</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
+        <v>300</v>
+      </c>
+      <c r="O81" s="3">
         <v>1000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>100</v>
       </c>
-      <c r="P81" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
+        <v>300</v>
+      </c>
+      <c r="S81" s="3">
         <v>700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
+        <v>0</v>
+      </c>
+      <c r="W81" s="3">
         <v>400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>-200</v>
-      </c>
-      <c r="X81" s="3">
-        <v>200</v>
-      </c>
-      <c r="Y81" s="3">
-        <v>600</v>
       </c>
       <c r="Z81" s="3">
         <v>200</v>
       </c>
       <c r="AA81" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB81" s="3">
+        <v>200</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-100</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC81" s="3">
-        <v>300</v>
-      </c>
       <c r="AD81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF81" s="3">
         <v>400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>-100</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,8 +7200,10 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6871,34 +7268,40 @@
         <v>300</v>
       </c>
       <c r="X83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>500</v>
       </c>
-      <c r="Z83" s="3">
-        <v>300</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>300</v>
-      </c>
       <c r="AB83" s="3">
         <v>300</v>
       </c>
       <c r="AC83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE83" s="3">
         <v>200</v>
       </c>
-      <c r="AD83" s="3">
-        <v>300</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>300</v>
-      </c>
       <c r="AF83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7392,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7490,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7588,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7686,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7784,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>500</v>
+      </c>
+      <c r="F89" s="3">
         <v>-200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-500</v>
       </c>
-      <c r="G89" s="3">
-        <v>300</v>
-      </c>
-      <c r="H89" s="3">
-        <v>0</v>
-      </c>
       <c r="I89" s="3">
+        <v>300</v>
+      </c>
+      <c r="J89" s="3">
+        <v>0</v>
+      </c>
+      <c r="K89" s="3">
         <v>1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>3100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>2400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>1000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>800</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>100</v>
       </c>
       <c r="AB89" s="3">
         <v>-100</v>
       </c>
       <c r="AC89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AE89" s="3">
         <v>1100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AH89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7922,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="E91" s="3">
         <v>-200</v>
       </c>
       <c r="F91" s="3">
-        <v>-400</v>
+        <v>-200</v>
       </c>
       <c r="G91" s="3">
         <v>-200</v>
       </c>
       <c r="H91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-300</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-300</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-200</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="M91" s="3">
         <v>-300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-200</v>
       </c>
       <c r="Q91" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="R91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S91" s="3">
+        <v>0</v>
+      </c>
+      <c r="T91" s="3">
         <v>-400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-200</v>
       </c>
-      <c r="AE91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8114,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8212,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4200</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-400</v>
       </c>
       <c r="G94" s="3">
         <v>-200</v>
       </c>
       <c r="H94" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-200</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-300</v>
       </c>
       <c r="P94" s="3">
         <v>-200</v>
       </c>
       <c r="Q94" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="R94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S94" s="3">
+        <v>0</v>
+      </c>
+      <c r="T94" s="3">
         <v>-400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-1400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>100</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8350,10 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8444,14 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8542,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8640,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,13 +8738,19 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-100</v>
+        <v>-700</v>
       </c>
       <c r="E100" s="3">
         <v>-100</v>
@@ -8271,28 +8762,28 @@
         <v>-100</v>
       </c>
       <c r="H100" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="I100" s="3">
         <v>-100</v>
       </c>
       <c r="J100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1300</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-100</v>
       </c>
       <c r="P100" s="3">
         <v>-100</v>
@@ -8301,40 +8792,40 @@
         <v>-100</v>
       </c>
       <c r="R100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="T100" s="3">
         <v>1000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-200</v>
-      </c>
-      <c r="T100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="U100" s="3">
-        <v>200</v>
       </c>
       <c r="V100" s="3">
         <v>-100</v>
       </c>
       <c r="W100" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="X100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>2800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>2600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>1500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>700</v>
-      </c>
-      <c r="AB100" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AC100" s="3">
-        <v>-100</v>
       </c>
       <c r="AD100" s="3">
         <v>-100</v>
@@ -8345,8 +8836,14 @@
       <c r="AF100" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="AH100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8934,108 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-4500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-1000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>1900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-100</v>
       </c>
-      <c r="O102" s="3">
-        <v>300</v>
-      </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
+        <v>300</v>
+      </c>
+      <c r="R102" s="3">
         <v>700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>2300</v>
-      </c>
-      <c r="R102" s="3">
-        <v>-400</v>
-      </c>
-      <c r="S102" s="3">
-        <v>-100</v>
       </c>
       <c r="T102" s="3">
         <v>-400</v>
       </c>
       <c r="U102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V102" s="3">
+        <v>-400</v>
+      </c>
+      <c r="W102" s="3">
         <v>1300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-500</v>
       </c>
-      <c r="W102" s="3">
-        <v>300</v>
-      </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z102" s="3">
         <v>100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>BWTL</t>
   </si>
@@ -1555,8 +1555,8 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>8</v>
+      <c r="D17" s="3">
+        <v>8500</v>
       </c>
       <c r="E17" s="3">
         <v>8200</v>
@@ -1653,8 +1653,8 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>8</v>
+      <c r="D18" s="3">
+        <v>-100</v>
       </c>
       <c r="E18" s="3">
         <v>-300</v>
@@ -1787,8 +1787,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>8</v>
+      <c r="D20" s="3">
+        <v>100</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
@@ -1885,8 +1885,8 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>8</v>
+      <c r="D21" s="3">
+        <v>300</v>
       </c>
       <c r="E21" s="3">
         <v>100</v>
@@ -2375,8 +2375,8 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>8</v>
+      <c r="D26" s="3">
+        <v>0</v>
       </c>
       <c r="E26" s="3">
         <v>-200</v>
@@ -2473,8 +2473,8 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>8</v>
+      <c r="D27" s="3">
+        <v>0</v>
       </c>
       <c r="E27" s="3">
         <v>-200</v>
@@ -2963,8 +2963,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>8</v>
+      <c r="D32" s="3">
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
@@ -3061,8 +3061,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>8</v>
+      <c r="D33" s="3">
+        <v>0</v>
       </c>
       <c r="E33" s="3">
         <v>-200</v>
@@ -3257,8 +3257,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>8</v>
+      <c r="D35" s="3">
+        <v>0</v>
       </c>
       <c r="E35" s="3">
         <v>-200</v>
@@ -3923,7 +3923,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E45" s="3">
         <v>500</v>
@@ -7073,8 +7073,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>8</v>
+      <c r="D81" s="3">
+        <v>0</v>
       </c>
       <c r="E81" s="3">
         <v>-200</v>

--- a/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>BWTL</t>
   </si>
@@ -656,360 +656,370 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42766</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E8" s="3">
         <v>8400</v>
       </c>
-      <c r="E8" s="3">
-        <v>7900</v>
-      </c>
       <c r="F8" s="3">
+        <v>6400</v>
+      </c>
+      <c r="G8" s="3">
         <v>8200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>11200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9500</v>
       </c>
-      <c r="I8" s="3">
-        <v>9200</v>
-      </c>
       <c r="J8" s="3">
+        <v>7700</v>
+      </c>
+      <c r="K8" s="3">
         <v>9100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>10500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9600</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>7600</v>
       </c>
       <c r="R8" s="3">
         <v>7600</v>
       </c>
       <c r="S8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="T8" s="3">
         <v>8900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>7000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>9300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>22900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>16000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>8300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6300</v>
-      </c>
-      <c r="AG8" s="3">
-        <v>5900</v>
       </c>
       <c r="AH8" s="3">
         <v>5900</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E9" s="3">
         <v>4700</v>
       </c>
-      <c r="E9" s="3">
-        <v>4300</v>
-      </c>
       <c r="F9" s="3">
+        <v>2800</v>
+      </c>
+      <c r="G9" s="3">
         <v>4700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K9" s="3">
+        <v>5100</v>
+      </c>
+      <c r="L9" s="3">
+        <v>7300</v>
+      </c>
+      <c r="M9" s="3">
+        <v>6200</v>
+      </c>
+      <c r="N9" s="3">
+        <v>5700</v>
+      </c>
+      <c r="O9" s="3">
+        <v>5400</v>
+      </c>
+      <c r="P9" s="3">
+        <v>7200</v>
+      </c>
+      <c r="Q9" s="3">
         <v>5200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>5100</v>
-      </c>
-      <c r="K9" s="3">
-        <v>7300</v>
-      </c>
-      <c r="L9" s="3">
-        <v>6200</v>
-      </c>
-      <c r="M9" s="3">
-        <v>5700</v>
-      </c>
-      <c r="N9" s="3">
-        <v>5400</v>
-      </c>
-      <c r="O9" s="3">
-        <v>7200</v>
-      </c>
-      <c r="P9" s="3">
-        <v>5200</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>3800</v>
       </c>
       <c r="R9" s="3">
         <v>3800</v>
       </c>
       <c r="S9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="T9" s="3">
         <v>4100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>13200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>9300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4000</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>3600</v>
       </c>
       <c r="AD9" s="3">
         <v>3600</v>
       </c>
       <c r="AE9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AF9" s="3">
         <v>4500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E10" s="3">
         <v>3700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3600</v>
       </c>
-      <c r="F10" s="3">
-        <v>3500</v>
-      </c>
       <c r="G10" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H10" s="3">
         <v>5200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>4100</v>
       </c>
       <c r="I10" s="3">
         <v>4000</v>
@@ -1018,79 +1028,82 @@
         <v>4000</v>
       </c>
       <c r="K10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="L10" s="3">
         <v>5600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>4300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>6800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4400</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>3800</v>
       </c>
       <c r="R10" s="3">
         <v>3800</v>
       </c>
       <c r="S10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="T10" s="3">
         <v>4800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2500</v>
-      </c>
-      <c r="U10" s="3">
-        <v>3100</v>
       </c>
       <c r="V10" s="3">
         <v>3100</v>
       </c>
       <c r="W10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="X10" s="3">
         <v>4200</v>
-      </c>
-      <c r="X10" s="3">
-        <v>3100</v>
       </c>
       <c r="Y10" s="3">
         <v>3100</v>
       </c>
       <c r="Z10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AA10" s="3">
         <v>9700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>6700</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>2900</v>
       </c>
       <c r="AC10" s="3">
         <v>2900</v>
       </c>
       <c r="AD10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AE10" s="3">
         <v>2800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1345,19 +1365,19 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
+        <v>-100</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1365,11 +1385,11 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>100</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="R14" s="3">
+        <v>100</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1386,8 +1406,8 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1395,17 +1415,17 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1413,14 +1433,17 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,14 +1514,14 @@
         <v>300</v>
       </c>
       <c r="Z15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA15" s="3">
         <v>800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>500</v>
       </c>
-      <c r="AB15" s="3">
-        <v>300</v>
-      </c>
       <c r="AC15" s="3">
         <v>300</v>
       </c>
@@ -1506,19 +1529,22 @@
         <v>300</v>
       </c>
       <c r="AE15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF15" s="3">
         <v>200</v>
       </c>
-      <c r="AF15" s="3">
-        <v>300</v>
-      </c>
       <c r="AG15" s="3">
         <v>300</v>
       </c>
       <c r="AH15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI15" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>9700</v>
+      </c>
+      <c r="E17" s="3">
         <v>8500</v>
       </c>
-      <c r="E17" s="3">
-        <v>8200</v>
-      </c>
       <c r="F17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G17" s="3">
         <v>8400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10400</v>
-      </c>
-      <c r="H17" s="3">
-        <v>9300</v>
       </c>
       <c r="I17" s="3">
         <v>9300</v>
       </c>
       <c r="J17" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K17" s="3">
         <v>9000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>11800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>10000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>12600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>6800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>22500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>15500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>7700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
+        <v>100</v>
+      </c>
+      <c r="J18" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>100</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M18" s="3">
+        <v>500</v>
+      </c>
+      <c r="N18" s="3">
+        <v>300</v>
+      </c>
+      <c r="O18" s="3">
+        <v>500</v>
+      </c>
+      <c r="P18" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>600</v>
+      </c>
+      <c r="R18" s="3">
         <v>200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="S18" s="3">
+        <v>400</v>
+      </c>
+      <c r="T18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="U18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="V18" s="3">
         <v>-100</v>
       </c>
-      <c r="J18" s="3">
-        <v>100</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="W18" s="3">
+        <v>100</v>
+      </c>
+      <c r="X18" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>400</v>
+      </c>
+      <c r="AB18" s="3">
         <v>500</v>
       </c>
-      <c r="M18" s="3">
-        <v>300</v>
-      </c>
-      <c r="N18" s="3">
-        <v>500</v>
-      </c>
-      <c r="O18" s="3">
-        <v>1400</v>
-      </c>
-      <c r="P18" s="3">
+      <c r="AC18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="3">
         <v>600</v>
       </c>
-      <c r="Q18" s="3">
-        <v>200</v>
-      </c>
-      <c r="R18" s="3">
-        <v>400</v>
-      </c>
-      <c r="S18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="T18" s="3">
-        <v>-200</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="AG18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH18" s="3">
         <v>-100</v>
       </c>
-      <c r="V18" s="3">
-        <v>100</v>
-      </c>
-      <c r="W18" s="3">
-        <v>600</v>
-      </c>
-      <c r="X18" s="3">
-        <v>100</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>100</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>400</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>500</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>100</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE18" s="3">
-        <v>600</v>
-      </c>
-      <c r="AF18" s="3">
-        <v>100</v>
-      </c>
-      <c r="AG18" s="3">
-        <v>-100</v>
-      </c>
-      <c r="AH18" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,22 +1815,23 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1809,10 +1843,10 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1821,16 +1855,16 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
         <v>0</v>
@@ -1839,10 +1873,10 @@
         <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="W20" s="3">
         <v>0</v>
@@ -1851,135 +1885,141 @@
         <v>0</v>
       </c>
       <c r="Y20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z20" s="3">
         <v>100</v>
       </c>
       <c r="AA20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB20" s="3">
         <v>0</v>
       </c>
       <c r="AC20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AD20" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AE20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="E21" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F21" s="3">
+        <v>100</v>
+      </c>
+      <c r="G21" s="3">
+        <v>100</v>
+      </c>
+      <c r="H21" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>500</v>
+      </c>
+      <c r="J21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="K21" s="3">
+        <v>400</v>
+      </c>
+      <c r="L21" s="3">
+        <v>1500</v>
+      </c>
+      <c r="M21" s="3">
+        <v>800</v>
+      </c>
+      <c r="N21" s="3">
+        <v>500</v>
+      </c>
+      <c r="O21" s="3">
+        <v>800</v>
+      </c>
+      <c r="P21" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>900</v>
+      </c>
+      <c r="R21" s="3">
+        <v>500</v>
+      </c>
+      <c r="S21" s="3">
+        <v>700</v>
+      </c>
+      <c r="T21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="U21" s="3">
+        <v>100</v>
+      </c>
+      <c r="V21" s="3">
+        <v>300</v>
+      </c>
+      <c r="W21" s="3">
+        <v>400</v>
+      </c>
+      <c r="X21" s="3">
+        <v>900</v>
+      </c>
+      <c r="Y21" s="3">
+        <v>500</v>
+      </c>
+      <c r="Z21" s="3">
+        <v>400</v>
+      </c>
+      <c r="AA21" s="3">
+        <v>1300</v>
+      </c>
+      <c r="AB21" s="3">
         <v>1100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="AC21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD21" s="3">
         <v>500</v>
       </c>
-      <c r="I21" s="3">
-        <v>300</v>
-      </c>
-      <c r="J21" s="3">
-        <v>400</v>
-      </c>
-      <c r="K21" s="3">
-        <v>1500</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="AE21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF21" s="3">
         <v>800</v>
       </c>
-      <c r="M21" s="3">
-        <v>500</v>
-      </c>
-      <c r="N21" s="3">
-        <v>800</v>
-      </c>
-      <c r="O21" s="3">
-        <v>1700</v>
-      </c>
-      <c r="P21" s="3">
-        <v>900</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>500</v>
-      </c>
-      <c r="R21" s="3">
-        <v>700</v>
-      </c>
-      <c r="S21" s="3">
-        <v>1300</v>
-      </c>
-      <c r="T21" s="3">
-        <v>100</v>
-      </c>
-      <c r="U21" s="3">
-        <v>300</v>
-      </c>
-      <c r="V21" s="3">
-        <v>400</v>
-      </c>
-      <c r="W21" s="3">
-        <v>900</v>
-      </c>
-      <c r="X21" s="3">
-        <v>500</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>400</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>1300</v>
-      </c>
-      <c r="AA21" s="3">
-        <v>1100</v>
-      </c>
-      <c r="AB21" s="3">
-        <v>300</v>
-      </c>
-      <c r="AC21" s="3">
-        <v>500</v>
-      </c>
-      <c r="AD21" s="3">
-        <v>300</v>
-      </c>
-      <c r="AE21" s="3">
-        <v>800</v>
-      </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>600</v>
       </c>
-      <c r="AG21" s="3">
-        <v>100</v>
-      </c>
       <c r="AH21" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="AI21" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2050,11 +2090,11 @@
         <v>100</v>
       </c>
       <c r="Z22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA22" s="3">
         <v>200</v>
       </c>
-      <c r="AA22" s="3">
-        <v>100</v>
-      </c>
       <c r="AB22" s="3">
         <v>100</v>
       </c>
@@ -2065,7 +2105,7 @@
         <v>100</v>
       </c>
       <c r="AE22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
@@ -2076,124 +2116,130 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E23" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="F23" s="3">
         <v>-200</v>
       </c>
       <c r="G23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="H23" s="3">
         <v>800</v>
       </c>
-      <c r="H23" s="3">
-        <v>100</v>
-      </c>
       <c r="I23" s="3">
+        <v>100</v>
+      </c>
+      <c r="J23" s="3">
         <v>-100</v>
       </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>1100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>500</v>
       </c>
-      <c r="Q23" s="3">
-        <v>100</v>
-      </c>
       <c r="R23" s="3">
+        <v>100</v>
+      </c>
+      <c r="S23" s="3">
         <v>400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
       <c r="W23" s="3">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3">
         <v>500</v>
       </c>
-      <c r="X23" s="3">
-        <v>100</v>
-      </c>
       <c r="Y23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z23" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB23" s="3">
         <v>500</v>
       </c>
-      <c r="AB23" s="3">
-        <v>0</v>
-      </c>
       <c r="AC23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="3">
         <v>200</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
         <v>500</v>
       </c>
-      <c r="AF23" s="3">
-        <v>300</v>
-      </c>
       <c r="AG23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH23" s="3">
         <v>-200</v>
       </c>
-      <c r="AH23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>200</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
         <v>0</v>
       </c>
@@ -2201,79 +2247,82 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="M24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
+        <v>100</v>
+      </c>
+      <c r="P24" s="3">
         <v>400</v>
       </c>
-      <c r="P24" s="3">
-        <v>100</v>
-      </c>
       <c r="Q24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S24" s="3">
+        <v>100</v>
+      </c>
+      <c r="T24" s="3">
         <v>200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-100</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
-      </c>
       <c r="V24" s="3">
         <v>0</v>
       </c>
       <c r="W24" s="3">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3">
         <v>200</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
       <c r="Z24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="3">
         <v>100</v>
       </c>
       <c r="AB24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="3">
         <v>200</v>
       </c>
-      <c r="AF24" s="3">
-        <v>100</v>
-      </c>
       <c r="AG24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH24" s="3">
         <v>-100</v>
       </c>
-      <c r="AH24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>600</v>
       </c>
-      <c r="H26" s="3">
-        <v>100</v>
-      </c>
       <c r="I26" s="3">
+        <v>100</v>
+      </c>
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
       <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
         <v>800</v>
       </c>
-      <c r="L26" s="3">
-        <v>300</v>
-      </c>
       <c r="M26" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N26" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O26" s="3">
+        <v>300</v>
+      </c>
+      <c r="P26" s="3">
         <v>1000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="Q26" s="3">
-        <v>100</v>
-      </c>
       <c r="R26" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="S26" s="3">
+        <v>300</v>
+      </c>
+      <c r="T26" s="3">
         <v>700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
       <c r="W26" s="3">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3">
         <v>400</v>
       </c>
-      <c r="X26" s="3">
-        <v>100</v>
-      </c>
       <c r="Y26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>200</v>
       </c>
-      <c r="AA26" s="3">
-        <v>300</v>
-      </c>
       <c r="AB26" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AC26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE26" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG26" s="3">
         <v>200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-100</v>
       </c>
-      <c r="AH26" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>600</v>
       </c>
-      <c r="H27" s="3">
-        <v>100</v>
-      </c>
       <c r="I27" s="3">
+        <v>100</v>
+      </c>
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
       <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
         <v>800</v>
       </c>
-      <c r="L27" s="3">
-        <v>300</v>
-      </c>
       <c r="M27" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N27" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O27" s="3">
+        <v>300</v>
+      </c>
+      <c r="P27" s="3">
         <v>1000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="Q27" s="3">
-        <v>100</v>
-      </c>
       <c r="R27" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="S27" s="3">
+        <v>300</v>
+      </c>
+      <c r="T27" s="3">
         <v>700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
       <c r="W27" s="3">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3">
         <v>400</v>
       </c>
-      <c r="X27" s="3">
-        <v>100</v>
-      </c>
       <c r="Y27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>200</v>
       </c>
-      <c r="AA27" s="3">
-        <v>300</v>
-      </c>
       <c r="AB27" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AC27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE27" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG27" s="3">
         <v>200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-100</v>
       </c>
-      <c r="AH27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2714,8 +2775,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2732,38 +2793,41 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-200</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="3">
         <v>200</v>
       </c>
       <c r="AC29" s="3">
+        <v>200</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-200</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
         <v>0</v>
       </c>
       <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
         <v>200</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,68 +3025,71 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+      <c r="F32" s="3">
+        <v>100</v>
+      </c>
+      <c r="G32" s="3">
+        <v>100</v>
+      </c>
+      <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="F32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
         <v>0</v>
       </c>
@@ -3027,135 +3097,141 @@
         <v>0</v>
       </c>
       <c r="Y32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="Z32" s="3">
         <v>-100</v>
       </c>
       <c r="AA32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AB32" s="3">
         <v>0</v>
       </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>-300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-100</v>
       </c>
-      <c r="AE32" s="3">
-        <v>0</v>
-      </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>600</v>
       </c>
-      <c r="H33" s="3">
-        <v>100</v>
-      </c>
       <c r="I33" s="3">
+        <v>100</v>
+      </c>
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
       <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
         <v>800</v>
       </c>
-      <c r="L33" s="3">
-        <v>300</v>
-      </c>
       <c r="M33" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O33" s="3">
+        <v>300</v>
+      </c>
+      <c r="P33" s="3">
         <v>1000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="Q33" s="3">
-        <v>100</v>
-      </c>
       <c r="R33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="S33" s="3">
+        <v>300</v>
+      </c>
+      <c r="T33" s="3">
         <v>700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
       <c r="W33" s="3">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3">
         <v>400</v>
       </c>
-      <c r="X33" s="3">
-        <v>100</v>
-      </c>
       <c r="Y33" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-100</v>
       </c>
-      <c r="AD33" s="3">
-        <v>0</v>
-      </c>
       <c r="AE33" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG33" s="3">
         <v>400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-100</v>
       </c>
-      <c r="AH33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>600</v>
       </c>
-      <c r="H35" s="3">
-        <v>100</v>
-      </c>
       <c r="I35" s="3">
+        <v>100</v>
+      </c>
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
       <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
         <v>800</v>
       </c>
-      <c r="L35" s="3">
-        <v>300</v>
-      </c>
       <c r="M35" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O35" s="3">
+        <v>300</v>
+      </c>
+      <c r="P35" s="3">
         <v>1000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="Q35" s="3">
-        <v>100</v>
-      </c>
       <c r="R35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="S35" s="3">
+        <v>300</v>
+      </c>
+      <c r="T35" s="3">
         <v>700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
       <c r="W35" s="3">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3">
         <v>400</v>
       </c>
-      <c r="X35" s="3">
-        <v>100</v>
-      </c>
       <c r="Y35" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-100</v>
       </c>
-      <c r="AD35" s="3">
-        <v>0</v>
-      </c>
       <c r="AE35" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG35" s="3">
         <v>400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-100</v>
       </c>
-      <c r="AH35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42766</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E41" s="3">
         <v>3400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6300</v>
-      </c>
-      <c r="I41" s="3">
-        <v>7300</v>
       </c>
       <c r="J41" s="3">
         <v>7300</v>
       </c>
       <c r="K41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="L41" s="3">
         <v>7800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>8100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>6600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3600</v>
-      </c>
-      <c r="AC41" s="3">
-        <v>4000</v>
       </c>
       <c r="AD41" s="3">
         <v>4000</v>
       </c>
       <c r="AE41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AF41" s="3">
         <v>4300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3632,13 +3722,13 @@
         <v>3900</v>
       </c>
       <c r="E42" s="3">
+        <v>3900</v>
+      </c>
+      <c r="F42" s="3">
         <v>4800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5200</v>
-      </c>
-      <c r="G42" s="3">
-        <v>1200</v>
       </c>
       <c r="H42" s="3">
         <v>1200</v>
@@ -3689,13 +3779,13 @@
         <v>1200</v>
       </c>
       <c r="X42" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Y42" s="3">
         <v>1000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>900</v>
-      </c>
-      <c r="Z42" s="3">
-        <v>1000</v>
       </c>
       <c r="AA42" s="3">
         <v>1000</v>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3781,10 +3874,10 @@
         <v>0</v>
       </c>
       <c r="V43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
@@ -3819,159 +3912,165 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E44" s="3">
         <v>5400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6500</v>
-      </c>
-      <c r="I44" s="3">
-        <v>5700</v>
       </c>
       <c r="J44" s="3">
         <v>5700</v>
       </c>
       <c r="K44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="L44" s="3">
         <v>5800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>3900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4000</v>
-      </c>
-      <c r="V44" s="3">
-        <v>4200</v>
       </c>
       <c r="W44" s="3">
         <v>4200</v>
       </c>
       <c r="X44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Y44" s="3">
         <v>4400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>3600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="G45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="I45" s="3">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="J45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="K45" s="3">
+        <v>300</v>
+      </c>
+      <c r="L45" s="3">
         <v>200</v>
       </c>
-      <c r="L45" s="3">
-        <v>300</v>
-      </c>
       <c r="M45" s="3">
         <v>300</v>
       </c>
       <c r="N45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="O45" s="3">
         <v>200</v>
       </c>
       <c r="P45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="Q45" s="3">
         <v>300</v>
       </c>
       <c r="R45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="S45" s="3">
         <v>200</v>
       </c>
       <c r="T45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U45" s="3">
         <v>300</v>
@@ -3992,7 +4091,7 @@
         <v>300</v>
       </c>
       <c r="AA45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AB45" s="3">
         <v>400</v>
@@ -4001,7 +4100,7 @@
         <v>400</v>
       </c>
       <c r="AD45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AE45" s="3">
         <v>300</v>
@@ -4010,150 +4109,156 @@
         <v>300</v>
       </c>
       <c r="AG45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH45" s="3">
         <v>400</v>
       </c>
-      <c r="AH45" s="3">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E46" s="3">
         <v>13200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>14000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>13400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>12700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12000</v>
-      </c>
-      <c r="T46" s="3">
-        <v>10300</v>
       </c>
       <c r="U46" s="3">
         <v>10300</v>
       </c>
       <c r="V46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="W46" s="3">
         <v>10500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>10900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>9600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>8900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>300</v>
-      </c>
-      <c r="G47" s="3">
-        <v>300</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>300</v>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>300</v>
       </c>
       <c r="L47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
       <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3">
         <v>700</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4170,7 +4275,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="V47" s="3">
         <v>800</v>
@@ -4185,7 +4290,7 @@
         <v>800</v>
       </c>
       <c r="Z47" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="AA47" s="3">
         <v>300</v>
@@ -4209,30 +4314,33 @@
         <v>300</v>
       </c>
       <c r="AH47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F48" s="3">
+        <v>12800</v>
+      </c>
+      <c r="G48" s="3">
         <v>12900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
+        <v>13000</v>
+      </c>
+      <c r="I48" s="3">
         <v>13100</v>
-      </c>
-      <c r="F48" s="3">
-        <v>12900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>13000</v>
-      </c>
-      <c r="H48" s="3">
-        <v>13400</v>
-      </c>
-      <c r="I48" s="3">
-        <v>13200</v>
       </c>
       <c r="J48" s="3">
         <v>12900</v>
@@ -4241,81 +4349,84 @@
         <v>12900</v>
       </c>
       <c r="L48" s="3">
+        <v>12900</v>
+      </c>
+      <c r="M48" s="3">
         <v>13800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>14300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>13700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14500</v>
-      </c>
-      <c r="R48" s="3">
-        <v>14600</v>
       </c>
       <c r="S48" s="3">
         <v>14600</v>
       </c>
       <c r="T48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="U48" s="3">
         <v>14900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>14000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>13700</v>
-      </c>
-      <c r="W48" s="3">
-        <v>14000</v>
       </c>
       <c r="X48" s="3">
         <v>14000</v>
       </c>
       <c r="Y48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="Z48" s="3">
         <v>13000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>12100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>10500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>9800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
         <v>0</v>
@@ -4374,14 +4485,14 @@
       <c r="W49" s="3">
         <v>0</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>8</v>
+      <c r="X49" s="3">
+        <v>0</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
@@ -4393,10 +4504,10 @@
         <v>0</v>
       </c>
       <c r="AD49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF49" s="3">
         <v>0</v>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,31 +4720,34 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -4665,17 +4785,17 @@
       <c r="V52" s="3">
         <v>0</v>
       </c>
-      <c r="W52" s="3" t="s">
+      <c r="W52" s="3">
+        <v>0</v>
+      </c>
+      <c r="X52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X52" s="3">
-        <v>0</v>
-      </c>
       <c r="Y52" s="3">
         <v>0</v>
       </c>
       <c r="Z52" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AA52" s="3">
         <v>500</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3">
         <v>500</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26800</v>
+      </c>
+      <c r="E54" s="3">
         <v>26100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>27100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>28100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>28400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26700</v>
-      </c>
-      <c r="T54" s="3">
-        <v>25200</v>
       </c>
       <c r="U54" s="3">
         <v>25200</v>
       </c>
       <c r="V54" s="3">
+        <v>25200</v>
+      </c>
+      <c r="W54" s="3">
         <v>25100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>25700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>24400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>23300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>22100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>20300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>19700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>20000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>19300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>18900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,129 +5099,133 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1300</v>
-      </c>
-      <c r="E57" s="3">
-        <v>800</v>
       </c>
       <c r="F57" s="3">
         <v>800</v>
       </c>
       <c r="G57" s="3">
+        <v>800</v>
+      </c>
+      <c r="H57" s="3">
         <v>1200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1100</v>
-      </c>
-      <c r="S57" s="3">
-        <v>1000</v>
       </c>
       <c r="T57" s="3">
         <v>1000</v>
       </c>
       <c r="U57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V57" s="3">
         <v>900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1000</v>
-      </c>
-      <c r="W57" s="3">
-        <v>1400</v>
       </c>
       <c r="X57" s="3">
         <v>1400</v>
       </c>
       <c r="Y57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="Z57" s="3">
         <v>600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>800</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>1200</v>
       </c>
       <c r="AF57" s="3">
         <v>1200</v>
       </c>
       <c r="AG57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AH57" s="3">
         <v>600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="E58" s="3">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="F58" s="3">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="G58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H58" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="I58" s="3">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="J58" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="K58" s="3">
         <v>500</v>
@@ -5112,10 +5246,10 @@
         <v>500</v>
       </c>
       <c r="Q58" s="3">
+        <v>500</v>
+      </c>
+      <c r="R58" s="3">
         <v>600</v>
-      </c>
-      <c r="R58" s="3">
-        <v>500</v>
       </c>
       <c r="S58" s="3">
         <v>500</v>
@@ -5133,7 +5267,7 @@
         <v>500</v>
       </c>
       <c r="X58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Y58" s="3">
         <v>400</v>
@@ -5142,393 +5276,405 @@
         <v>400</v>
       </c>
       <c r="AA58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AB58" s="3">
         <v>300</v>
       </c>
       <c r="AC58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AD58" s="3">
         <v>200</v>
       </c>
       <c r="AE58" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AF58" s="3">
         <v>400</v>
       </c>
       <c r="AG58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AH58" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="E59" s="3">
-        <v>1600</v>
+        <v>0</v>
       </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
+        <v>0</v>
+      </c>
+      <c r="I59" s="3">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3">
+        <v>0</v>
+      </c>
+      <c r="K59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="L59" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M59" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N59" s="3">
+        <v>3500</v>
+      </c>
+      <c r="O59" s="3">
+        <v>3000</v>
+      </c>
+      <c r="P59" s="3">
+        <v>3200</v>
+      </c>
+      <c r="Q59" s="3">
+        <v>1500</v>
+      </c>
+      <c r="R59" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S59" s="3">
+        <v>1800</v>
+      </c>
+      <c r="T59" s="3">
         <v>1400</v>
       </c>
-      <c r="G59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="U59" s="3">
+        <v>600</v>
+      </c>
+      <c r="V59" s="3">
+        <v>1400</v>
+      </c>
+      <c r="W59" s="3">
         <v>1100</v>
       </c>
-      <c r="I59" s="3">
-        <v>2100</v>
-      </c>
-      <c r="J59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>1900</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="X59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
-        <v>3500</v>
-      </c>
-      <c r="N59" s="3">
-        <v>3000</v>
-      </c>
-      <c r="O59" s="3">
-        <v>3200</v>
-      </c>
-      <c r="P59" s="3">
-        <v>1500</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>2100</v>
-      </c>
-      <c r="R59" s="3">
-        <v>1800</v>
-      </c>
-      <c r="S59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="T59" s="3">
+      <c r="Y59" s="3">
         <v>600</v>
       </c>
-      <c r="U59" s="3">
-        <v>1400</v>
-      </c>
-      <c r="V59" s="3">
-        <v>1100</v>
-      </c>
-      <c r="W59" s="3">
+      <c r="Z59" s="3">
         <v>1200</v>
-      </c>
-      <c r="X59" s="3">
-        <v>600</v>
-      </c>
-      <c r="Y59" s="3">
-        <v>1200</v>
-      </c>
-      <c r="Z59" s="3">
-        <v>1000</v>
       </c>
       <c r="AA59" s="3">
         <v>1000</v>
       </c>
       <c r="AB59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AC59" s="3">
         <v>700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E60" s="3">
         <v>2700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>5400</v>
+        <v>6400</v>
       </c>
       <c r="E61" s="3">
-        <v>5500</v>
+        <v>6300</v>
       </c>
       <c r="F61" s="3">
-        <v>5600</v>
+        <v>6500</v>
       </c>
       <c r="G61" s="3">
-        <v>5700</v>
+        <v>6600</v>
       </c>
       <c r="H61" s="3">
-        <v>5900</v>
+        <v>6700</v>
       </c>
       <c r="I61" s="3">
-        <v>6000</v>
+        <v>6700</v>
       </c>
       <c r="J61" s="3">
+        <v>6800</v>
+      </c>
+      <c r="K61" s="3">
         <v>6100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>7900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>8000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>1700</v>
-      </c>
-      <c r="E62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="F62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G62" s="3">
-        <v>2000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="I62" s="3">
-        <v>1900</v>
-      </c>
-      <c r="J62" s="3">
-        <v>1800</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>1800</v>
       </c>
       <c r="L62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M62" s="3">
         <v>1700</v>
-      </c>
-      <c r="M62" s="3">
-        <v>2100</v>
       </c>
       <c r="N62" s="3">
         <v>2100</v>
       </c>
       <c r="O62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="P62" s="3">
         <v>2200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2100</v>
-      </c>
-      <c r="R62" s="3">
-        <v>2000</v>
       </c>
       <c r="S62" s="3">
         <v>2000</v>
       </c>
       <c r="T62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="U62" s="3">
         <v>1700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1900</v>
-      </c>
-      <c r="V62" s="3">
-        <v>1700</v>
       </c>
       <c r="W62" s="3">
         <v>1700</v>
       </c>
       <c r="X62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Y62" s="3">
         <v>1500</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>600</v>
       </c>
       <c r="Z62" s="3">
         <v>600</v>
@@ -5537,10 +5683,10 @@
         <v>600</v>
       </c>
       <c r="AB62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC62" s="3">
         <v>500</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>800</v>
       </c>
       <c r="AD62" s="3">
         <v>800</v>
@@ -5549,16 +5695,19 @@
         <v>800</v>
       </c>
       <c r="AF62" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AG62" s="3">
         <v>700</v>
       </c>
       <c r="AH62" s="3">
+        <v>700</v>
+      </c>
+      <c r="AI62" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E66" s="3">
         <v>9800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>12400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>10500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>9600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E72" s="3">
         <v>8000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4100</v>
-      </c>
-      <c r="V72" s="3">
-        <v>4200</v>
       </c>
       <c r="W72" s="3">
         <v>4200</v>
       </c>
       <c r="X72" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Y72" s="3">
         <v>3800</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>3700</v>
       </c>
       <c r="Z72" s="3">
         <v>3700</v>
       </c>
       <c r="AA72" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AB72" s="3">
         <v>3800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>3500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3200</v>
-      </c>
-      <c r="AD72" s="3">
-        <v>3300</v>
       </c>
       <c r="AE72" s="3">
         <v>3300</v>
       </c>
       <c r="AF72" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AG72" s="3">
         <v>3000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>2800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,73 +6952,76 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E76" s="3">
         <v>16300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16500</v>
-      </c>
-      <c r="J76" s="3">
-        <v>16700</v>
       </c>
       <c r="K76" s="3">
         <v>16700</v>
       </c>
       <c r="L76" s="3">
+        <v>16700</v>
+      </c>
+      <c r="M76" s="3">
         <v>15900</v>
-      </c>
-      <c r="M76" s="3">
-        <v>15500</v>
       </c>
       <c r="N76" s="3">
         <v>15500</v>
       </c>
       <c r="O76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="P76" s="3">
         <v>15200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>12800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13000</v>
-      </c>
-      <c r="V76" s="3">
-        <v>13200</v>
       </c>
       <c r="W76" s="3">
         <v>13200</v>
       </c>
       <c r="X76" s="3">
-        <v>12800</v>
+        <v>13200</v>
       </c>
       <c r="Y76" s="3">
         <v>12800</v>
@@ -6844,31 +7030,34 @@
         <v>12800</v>
       </c>
       <c r="AA76" s="3">
+        <v>12800</v>
+      </c>
+      <c r="AB76" s="3">
         <v>12900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>12500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12300</v>
-      </c>
-      <c r="AD76" s="3">
-        <v>12400</v>
       </c>
       <c r="AE76" s="3">
         <v>12400</v>
       </c>
       <c r="AF76" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AG76" s="3">
         <v>12100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>11900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="E80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42766</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>600</v>
       </c>
-      <c r="H81" s="3">
-        <v>100</v>
-      </c>
       <c r="I81" s="3">
+        <v>100</v>
+      </c>
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
       <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
         <v>800</v>
       </c>
-      <c r="L81" s="3">
-        <v>300</v>
-      </c>
       <c r="M81" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="O81" s="3">
+        <v>300</v>
+      </c>
+      <c r="P81" s="3">
         <v>1000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="Q81" s="3">
-        <v>100</v>
-      </c>
       <c r="R81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="S81" s="3">
+        <v>300</v>
+      </c>
+      <c r="T81" s="3">
         <v>700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
       <c r="W81" s="3">
+        <v>0</v>
+      </c>
+      <c r="X81" s="3">
         <v>400</v>
       </c>
-      <c r="X81" s="3">
-        <v>100</v>
-      </c>
       <c r="Y81" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-100</v>
       </c>
-      <c r="AD81" s="3">
-        <v>0</v>
-      </c>
       <c r="AE81" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG81" s="3">
         <v>400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-100</v>
       </c>
-      <c r="AH81" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7214,7 +7413,7 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G83" s="3">
         <v>300</v>
@@ -7274,14 +7473,14 @@
         <v>300</v>
       </c>
       <c r="Z83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA83" s="3">
         <v>800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>500</v>
       </c>
-      <c r="AB83" s="3">
-        <v>300</v>
-      </c>
       <c r="AC83" s="3">
         <v>300</v>
       </c>
@@ -7289,19 +7488,22 @@
         <v>300</v>
       </c>
       <c r="AE83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF83" s="3">
         <v>200</v>
       </c>
-      <c r="AF83" s="3">
-        <v>300</v>
-      </c>
       <c r="AG83" s="3">
         <v>300</v>
       </c>
       <c r="AH83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-500</v>
       </c>
-      <c r="I89" s="3">
-        <v>300</v>
-      </c>
       <c r="J89" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K89" s="3">
+        <v>0</v>
+      </c>
+      <c r="L89" s="3">
         <v>1600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>2400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>400</v>
-      </c>
-      <c r="Z89" s="3">
-        <v>800</v>
       </c>
       <c r="AA89" s="3">
         <v>800</v>
       </c>
       <c r="AB89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AC89" s="3">
         <v>-100</v>
       </c>
-      <c r="AC89" s="3">
-        <v>100</v>
-      </c>
       <c r="AD89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
-      <c r="AH89" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,16 +8144,17 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-300</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-200</v>
       </c>
       <c r="F91" s="3">
         <v>-200</v>
@@ -7942,88 +8163,91 @@
         <v>-200</v>
       </c>
       <c r="H91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I91" s="3">
         <v>-400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-200</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-300</v>
       </c>
       <c r="K91" s="3">
         <v>-300</v>
       </c>
       <c r="L91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="M91" s="3">
         <v>-200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
       </c>
       <c r="O91" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-200</v>
       </c>
       <c r="Q91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R91" s="3">
         <v>-300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-200</v>
       </c>
-      <c r="S91" s="3">
-        <v>0</v>
-      </c>
       <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
         <v>-400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-200</v>
       </c>
-      <c r="AG91" s="3">
-        <v>0</v>
-      </c>
       <c r="AH91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E94" s="3">
         <v>700</v>
       </c>
-      <c r="E94" s="3">
-        <v>300</v>
-      </c>
       <c r="F94" s="3">
+        <v>300</v>
+      </c>
+      <c r="G94" s="3">
         <v>-4200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-300</v>
       </c>
       <c r="N94" s="3">
         <v>-300</v>
       </c>
       <c r="O94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="P94" s="3">
         <v>-200</v>
       </c>
       <c r="Q94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-200</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
       <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
         <v>-400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-400</v>
       </c>
       <c r="AE94" s="3">
         <v>-400</v>
       </c>
       <c r="AF94" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="AG94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,31 +8585,32 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,16 +8987,19 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-700</v>
-      </c>
-      <c r="E100" s="3">
-        <v>-100</v>
       </c>
       <c r="F100" s="3">
         <v>-100</v>
@@ -8768,25 +9014,25 @@
         <v>-100</v>
       </c>
       <c r="J100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="K100" s="3">
         <v>-200</v>
-      </c>
-      <c r="K100" s="3">
-        <v>-100</v>
       </c>
       <c r="L100" s="3">
         <v>-100</v>
       </c>
       <c r="M100" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="N100" s="3">
         <v>-200</v>
       </c>
       <c r="O100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="P100" s="3">
         <v>-1300</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-100</v>
       </c>
       <c r="Q100" s="3">
         <v>-100</v>
@@ -8798,37 +9044,37 @@
         <v>-100</v>
       </c>
       <c r="T100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="U100" s="3">
         <v>1000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>2800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>2600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>700</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>-100</v>
       </c>
       <c r="AE100" s="3">
         <v>-100</v>
@@ -8842,31 +9088,34 @@
       <c r="AH100" s="3">
         <v>-100</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="Q102" s="3">
-        <v>300</v>
-      </c>
       <c r="R102" s="3">
+        <v>300</v>
+      </c>
+      <c r="S102" s="3">
         <v>700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-500</v>
       </c>
-      <c r="Y102" s="3">
-        <v>300</v>
-      </c>
       <c r="Z102" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AA102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB102" s="3">
         <v>400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-400</v>
       </c>
-      <c r="AC102" s="3">
-        <v>100</v>
-      </c>
       <c r="AD102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>700</v>
       </c>
-      <c r="AF102" s="3">
-        <v>100</v>
-      </c>
       <c r="AG102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
   <si>
     <t>BWTL</t>
   </si>
@@ -656,373 +656,383 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
         <v>45504</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45412</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45322</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45230</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45138</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44957</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44592</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44316</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44227</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44043</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43951</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43861</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43769</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43677</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43585</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43496</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43404</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43312</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43220</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43131</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43039</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42947</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42855</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42766</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E8" s="3">
         <v>10200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>6400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>9500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>12900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>9700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9600</v>
-      </c>
-      <c r="R8" s="3">
-        <v>7600</v>
       </c>
       <c r="S8" s="3">
         <v>7600</v>
       </c>
       <c r="T8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="U8" s="3">
         <v>8900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>7000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>22900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>16000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>8300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6300</v>
-      </c>
-      <c r="AH8" s="3">
-        <v>5900</v>
       </c>
       <c r="AI8" s="3">
         <v>5900</v>
       </c>
+      <c r="AJ8" s="3">
+        <v>5900</v>
+      </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E9" s="3">
         <v>5400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>7300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>7200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5200</v>
-      </c>
-      <c r="R9" s="3">
-        <v>3800</v>
       </c>
       <c r="S9" s="3">
         <v>3800</v>
       </c>
       <c r="T9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U9" s="3">
         <v>4100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>13200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>9300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4000</v>
-      </c>
-      <c r="AD9" s="3">
-        <v>3600</v>
       </c>
       <c r="AE9" s="3">
         <v>3600</v>
       </c>
       <c r="AF9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AG9" s="3">
         <v>4500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E10" s="3">
         <v>4800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3700</v>
-      </c>
-      <c r="F10" s="3">
-        <v>3600</v>
       </c>
       <c r="G10" s="3">
         <v>3600</v>
       </c>
       <c r="H10" s="3">
+        <v>3600</v>
+      </c>
+      <c r="I10" s="3">
         <v>5200</v>
-      </c>
-      <c r="I10" s="3">
-        <v>4000</v>
       </c>
       <c r="J10" s="3">
         <v>4000</v>
@@ -1031,79 +1041,82 @@
         <v>4000</v>
       </c>
       <c r="L10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="M10" s="3">
         <v>5600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>4300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>6800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4400</v>
-      </c>
-      <c r="R10" s="3">
-        <v>3800</v>
       </c>
       <c r="S10" s="3">
         <v>3800</v>
       </c>
       <c r="T10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U10" s="3">
         <v>4800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>2500</v>
-      </c>
-      <c r="V10" s="3">
-        <v>3100</v>
       </c>
       <c r="W10" s="3">
         <v>3100</v>
       </c>
       <c r="X10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Y10" s="3">
         <v>4200</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>3100</v>
       </c>
       <c r="Z10" s="3">
         <v>3100</v>
       </c>
       <c r="AA10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AB10" s="3">
         <v>9700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>6700</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>2900</v>
       </c>
       <c r="AD10" s="3">
         <v>2900</v>
       </c>
       <c r="AE10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AF10" s="3">
         <v>2800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>2700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,8 +1358,11 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1365,22 +1385,22 @@
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>-100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1388,11 +1408,11 @@
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
-        <v>100</v>
-      </c>
-      <c r="S14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="S14" s="3">
+        <v>100</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1409,8 +1429,8 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1418,17 +1438,17 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AD14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1436,14 +1456,17 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AI14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1517,14 +1540,14 @@
         <v>300</v>
       </c>
       <c r="AA15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB15" s="3">
         <v>800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>500</v>
       </c>
-      <c r="AC15" s="3">
-        <v>300</v>
-      </c>
       <c r="AD15" s="3">
         <v>300</v>
       </c>
@@ -1532,19 +1555,22 @@
         <v>300</v>
       </c>
       <c r="AF15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG15" s="3">
         <v>200</v>
       </c>
-      <c r="AG15" s="3">
-        <v>300</v>
-      </c>
       <c r="AH15" s="3">
         <v>300</v>
       </c>
       <c r="AI15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E17" s="3">
         <v>9700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>9300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>11800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>10000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>12600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>6800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>22500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>15500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>6800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>7700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
         <v>500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>800</v>
       </c>
-      <c r="I18" s="3">
-        <v>100</v>
-      </c>
       <c r="J18" s="3">
+        <v>100</v>
+      </c>
+      <c r="K18" s="3">
         <v>-100</v>
       </c>
-      <c r="K18" s="3">
-        <v>100</v>
-      </c>
       <c r="L18" s="3">
+        <v>100</v>
+      </c>
+      <c r="M18" s="3">
         <v>1100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>500</v>
       </c>
-      <c r="N18" s="3">
-        <v>300</v>
-      </c>
       <c r="O18" s="3">
+        <v>300</v>
+      </c>
+      <c r="P18" s="3">
         <v>500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-100</v>
       </c>
-      <c r="W18" s="3">
-        <v>100</v>
-      </c>
       <c r="X18" s="3">
+        <v>100</v>
+      </c>
+      <c r="Y18" s="3">
         <v>600</v>
       </c>
-      <c r="Y18" s="3">
-        <v>100</v>
-      </c>
       <c r="Z18" s="3">
         <v>100</v>
       </c>
       <c r="AA18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB18" s="3">
         <v>400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>500</v>
       </c>
-      <c r="AC18" s="3">
-        <v>100</v>
-      </c>
       <c r="AD18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE18" s="3">
         <v>0</v>
       </c>
       <c r="AF18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="3">
         <v>600</v>
       </c>
-      <c r="AG18" s="3">
-        <v>100</v>
-      </c>
       <c r="AH18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI18" s="3">
         <v>-100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,8 +1849,9 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1828,13 +1862,13 @@
         <v>0</v>
       </c>
       <c r="F20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>-100</v>
       </c>
       <c r="H20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
@@ -1846,10 +1880,10 @@
         <v>0</v>
       </c>
       <c r="L20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
@@ -1858,16 +1892,16 @@
         <v>0</v>
       </c>
       <c r="P20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
         <v>0</v>
@@ -1876,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="V20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="X20" s="3">
         <v>0</v>
@@ -1888,138 +1922,144 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="3">
         <v>100</v>
       </c>
       <c r="AB20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC20" s="3">
         <v>0</v>
       </c>
       <c r="AD20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AF20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
         <v>800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>200</v>
       </c>
-      <c r="F21" s="3">
-        <v>100</v>
-      </c>
       <c r="G21" s="3">
         <v>100</v>
       </c>
       <c r="H21" s="3">
+        <v>100</v>
+      </c>
+      <c r="I21" s="3">
         <v>1100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1300</v>
       </c>
-      <c r="U21" s="3">
-        <v>100</v>
-      </c>
       <c r="V21" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="W21" s="3">
+        <v>300</v>
+      </c>
+      <c r="X21" s="3">
         <v>400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1100</v>
       </c>
-      <c r="AC21" s="3">
-        <v>300</v>
-      </c>
       <c r="AD21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE21" s="3">
         <v>500</v>
       </c>
-      <c r="AE21" s="3">
-        <v>300</v>
-      </c>
       <c r="AF21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG21" s="3">
         <v>800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>600</v>
       </c>
-      <c r="AH21" s="3">
-        <v>100</v>
-      </c>
       <c r="AI21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2093,11 +2133,11 @@
         <v>100</v>
       </c>
       <c r="AA22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB22" s="3">
         <v>200</v>
       </c>
-      <c r="AB22" s="3">
-        <v>100</v>
-      </c>
       <c r="AC22" s="3">
         <v>100</v>
       </c>
@@ -2108,7 +2148,7 @@
         <v>100</v>
       </c>
       <c r="AF22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG22" s="3">
         <v>0</v>
@@ -2119,130 +2159,136 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
         <v>500</v>
       </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
       <c r="F23" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G23" s="3">
         <v>-200</v>
       </c>
       <c r="H23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="I23" s="3">
         <v>800</v>
       </c>
-      <c r="I23" s="3">
-        <v>100</v>
-      </c>
       <c r="J23" s="3">
+        <v>100</v>
+      </c>
+      <c r="K23" s="3">
         <v>-100</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>1100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>500</v>
       </c>
-      <c r="R23" s="3">
-        <v>100</v>
-      </c>
       <c r="S23" s="3">
+        <v>100</v>
+      </c>
+      <c r="T23" s="3">
         <v>400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
       <c r="X23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3">
         <v>500</v>
       </c>
-      <c r="Y23" s="3">
-        <v>100</v>
-      </c>
       <c r="Z23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA23" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC23" s="3">
         <v>500</v>
       </c>
-      <c r="AC23" s="3">
-        <v>0</v>
-      </c>
       <c r="AD23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="3">
         <v>200</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
       <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
         <v>500</v>
       </c>
-      <c r="AG23" s="3">
-        <v>300</v>
-      </c>
       <c r="AH23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI23" s="3">
         <v>-200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>200</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
@@ -2250,79 +2296,82 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="N24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="3">
         <v>400</v>
       </c>
-      <c r="Q24" s="3">
-        <v>100</v>
-      </c>
       <c r="R24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T24" s="3">
+        <v>100</v>
+      </c>
+      <c r="U24" s="3">
         <v>200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-100</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
-      </c>
       <c r="W24" s="3">
         <v>0</v>
       </c>
       <c r="X24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
-      </c>
       <c r="Z24" s="3">
         <v>0</v>
       </c>
       <c r="AA24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB24" s="3">
         <v>100</v>
       </c>
       <c r="AC24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="3">
         <v>200</v>
       </c>
-      <c r="AG24" s="3">
-        <v>100</v>
-      </c>
       <c r="AH24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI24" s="3">
         <v>-100</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E26" s="3">
         <v>400</v>
       </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
       <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
         <v>-200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
-        <v>100</v>
-      </c>
       <c r="J26" s="3">
+        <v>100</v>
+      </c>
+      <c r="K26" s="3">
         <v>-100</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>800</v>
       </c>
-      <c r="M26" s="3">
-        <v>300</v>
-      </c>
       <c r="N26" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O26" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P26" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q26" s="3">
         <v>1000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>400</v>
       </c>
-      <c r="R26" s="3">
-        <v>100</v>
-      </c>
       <c r="S26" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="T26" s="3">
+        <v>300</v>
+      </c>
+      <c r="U26" s="3">
         <v>700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
       <c r="X26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
         <v>400</v>
       </c>
-      <c r="Y26" s="3">
-        <v>100</v>
-      </c>
       <c r="Z26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="3">
         <v>200</v>
       </c>
-      <c r="AB26" s="3">
-        <v>300</v>
-      </c>
       <c r="AC26" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AD26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF26" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH26" s="3">
         <v>200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E27" s="3">
         <v>400</v>
       </c>
-      <c r="E27" s="3">
-        <v>0</v>
-      </c>
       <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
         <v>-200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
-        <v>100</v>
-      </c>
       <c r="J27" s="3">
+        <v>100</v>
+      </c>
+      <c r="K27" s="3">
         <v>-100</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>800</v>
       </c>
-      <c r="M27" s="3">
-        <v>300</v>
-      </c>
       <c r="N27" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O27" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P27" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q27" s="3">
         <v>1000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>400</v>
       </c>
-      <c r="R27" s="3">
-        <v>100</v>
-      </c>
       <c r="S27" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="T27" s="3">
+        <v>300</v>
+      </c>
+      <c r="U27" s="3">
         <v>700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
       <c r="X27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
         <v>400</v>
       </c>
-      <c r="Y27" s="3">
-        <v>100</v>
-      </c>
       <c r="Z27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="3">
         <v>200</v>
       </c>
-      <c r="AB27" s="3">
-        <v>300</v>
-      </c>
       <c r="AC27" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AD27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AE27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF27" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH27" s="3">
         <v>200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2778,8 +2839,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2796,38 +2857,41 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-200</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AC29" s="3">
         <v>200</v>
       </c>
       <c r="AD29" s="3">
+        <v>200</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-200</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
       <c r="AF29" s="3">
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>200</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,8 +3095,11 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3040,13 +3110,13 @@
         <v>0</v>
       </c>
       <c r="F32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>100</v>
       </c>
       <c r="H32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
@@ -3058,11 +3128,11 @@
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -3070,17 +3140,17 @@
         <v>0</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
         <v>0</v>
       </c>
@@ -3088,11 +3158,11 @@
         <v>0</v>
       </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
@@ -3100,138 +3170,144 @@
         <v>0</v>
       </c>
       <c r="Z32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="3">
         <v>-100</v>
       </c>
       <c r="AB32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AC32" s="3">
         <v>0</v>
       </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
       <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3">
         <v>-300</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E33" s="3">
         <v>400</v>
       </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
       <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
         <v>-200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>600</v>
       </c>
-      <c r="I33" s="3">
-        <v>100</v>
-      </c>
       <c r="J33" s="3">
+        <v>100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-100</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>800</v>
       </c>
-      <c r="M33" s="3">
-        <v>300</v>
-      </c>
       <c r="N33" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P33" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q33" s="3">
         <v>1000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>400</v>
       </c>
-      <c r="R33" s="3">
-        <v>100</v>
-      </c>
       <c r="S33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="T33" s="3">
+        <v>300</v>
+      </c>
+      <c r="U33" s="3">
         <v>700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
       <c r="X33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
         <v>400</v>
       </c>
-      <c r="Y33" s="3">
-        <v>100</v>
-      </c>
       <c r="Z33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-100</v>
       </c>
-      <c r="AE33" s="3">
-        <v>0</v>
-      </c>
       <c r="AF33" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH33" s="3">
         <v>400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E35" s="3">
         <v>400</v>
       </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
       <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
         <v>-200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>600</v>
       </c>
-      <c r="I35" s="3">
-        <v>100</v>
-      </c>
       <c r="J35" s="3">
+        <v>100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-100</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>800</v>
       </c>
-      <c r="M35" s="3">
-        <v>300</v>
-      </c>
       <c r="N35" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P35" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q35" s="3">
         <v>1000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>400</v>
       </c>
-      <c r="R35" s="3">
-        <v>100</v>
-      </c>
       <c r="S35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="T35" s="3">
+        <v>300</v>
+      </c>
+      <c r="U35" s="3">
         <v>700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
       <c r="X35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="3">
         <v>400</v>
       </c>
-      <c r="Y35" s="3">
-        <v>100</v>
-      </c>
       <c r="Z35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-100</v>
       </c>
-      <c r="AE35" s="3">
-        <v>0</v>
-      </c>
       <c r="AF35" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH35" s="3">
         <v>400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
         <v>45504</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45412</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45322</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45230</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45138</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44957</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44592</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44316</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44227</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44043</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43951</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43861</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43769</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43677</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43585</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43496</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43404</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43312</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43220</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43131</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43039</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42947</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42855</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42766</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,126 +3698,130 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E41" s="3">
         <v>4200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6300</v>
-      </c>
-      <c r="J41" s="3">
-        <v>7300</v>
       </c>
       <c r="K41" s="3">
         <v>7300</v>
       </c>
       <c r="L41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="M41" s="3">
         <v>7800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>9100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3600</v>
-      </c>
-      <c r="AD41" s="3">
-        <v>4000</v>
       </c>
       <c r="AE41" s="3">
         <v>4000</v>
       </c>
       <c r="AF41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AG41" s="3">
         <v>4300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="E42" s="3">
         <v>3900</v>
       </c>
       <c r="F42" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G42" s="3">
         <v>4800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5200</v>
-      </c>
-      <c r="H42" s="3">
-        <v>1200</v>
       </c>
       <c r="I42" s="3">
         <v>1200</v>
@@ -3782,13 +3872,13 @@
         <v>1200</v>
       </c>
       <c r="Y42" s="3">
+        <v>1200</v>
+      </c>
+      <c r="Z42" s="3">
         <v>1000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>900</v>
-      </c>
-      <c r="AA42" s="3">
-        <v>1000</v>
       </c>
       <c r="AB42" s="3">
         <v>1000</v>
@@ -3814,8 +3904,11 @@
       <c r="AI42" s="3">
         <v>1000</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3877,10 +3970,10 @@
         <v>0</v>
       </c>
       <c r="W43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y43" s="3">
         <v>0</v>
@@ -3915,114 +4008,120 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E44" s="3">
         <v>5200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6500</v>
-      </c>
-      <c r="J44" s="3">
-        <v>5700</v>
       </c>
       <c r="K44" s="3">
         <v>5700</v>
       </c>
       <c r="L44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="M44" s="3">
         <v>5800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>3900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4000</v>
-      </c>
-      <c r="W44" s="3">
-        <v>4200</v>
       </c>
       <c r="X44" s="3">
         <v>4200</v>
       </c>
       <c r="Y44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Z44" s="3">
         <v>4400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>3600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>3700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E45" s="3">
         <v>100</v>
@@ -4043,37 +4142,37 @@
         <v>100</v>
       </c>
       <c r="K45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="L45" s="3">
+        <v>300</v>
+      </c>
+      <c r="M45" s="3">
         <v>200</v>
       </c>
-      <c r="M45" s="3">
-        <v>300</v>
-      </c>
       <c r="N45" s="3">
         <v>300</v>
       </c>
       <c r="O45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="P45" s="3">
         <v>200</v>
       </c>
       <c r="Q45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="R45" s="3">
         <v>300</v>
       </c>
       <c r="S45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="T45" s="3">
         <v>200</v>
       </c>
       <c r="U45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="V45" s="3">
         <v>300</v>
@@ -4094,7 +4193,7 @@
         <v>300</v>
       </c>
       <c r="AB45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AC45" s="3">
         <v>400</v>
@@ -4103,7 +4202,7 @@
         <v>400</v>
       </c>
       <c r="AE45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AF45" s="3">
         <v>300</v>
@@ -4112,114 +4211,120 @@
         <v>300</v>
       </c>
       <c r="AH45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI45" s="3">
         <v>400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E46" s="3">
         <v>13800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>14000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>12700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12000</v>
-      </c>
-      <c r="U46" s="3">
-        <v>10300</v>
       </c>
       <c r="V46" s="3">
         <v>10300</v>
       </c>
       <c r="W46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="X46" s="3">
         <v>10500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>10900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>9600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>8900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4244,24 +4349,24 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>300</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>300</v>
       </c>
       <c r="M47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
       <c r="O47" s="3">
+        <v>0</v>
+      </c>
+      <c r="P47" s="3">
         <v>700</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4278,7 +4383,7 @@
         <v>0</v>
       </c>
       <c r="V47" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="W47" s="3">
         <v>800</v>
@@ -4293,7 +4398,7 @@
         <v>800</v>
       </c>
       <c r="AA47" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="AB47" s="3">
         <v>300</v>
@@ -4317,33 +4422,36 @@
         <v>300</v>
       </c>
       <c r="AI47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E48" s="3">
         <v>12700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>13000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13100</v>
-      </c>
-      <c r="J48" s="3">
-        <v>12900</v>
       </c>
       <c r="K48" s="3">
         <v>12900</v>
@@ -4352,84 +4460,87 @@
         <v>12900</v>
       </c>
       <c r="M48" s="3">
+        <v>12900</v>
+      </c>
+      <c r="N48" s="3">
         <v>13800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>14300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>13700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14500</v>
-      </c>
-      <c r="S48" s="3">
-        <v>14600</v>
       </c>
       <c r="T48" s="3">
         <v>14600</v>
       </c>
       <c r="U48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="V48" s="3">
         <v>14900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>14000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>13700</v>
-      </c>
-      <c r="X48" s="3">
-        <v>14000</v>
       </c>
       <c r="Y48" s="3">
         <v>14000</v>
       </c>
       <c r="Z48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AA48" s="3">
         <v>13000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>13100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>12100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>10500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>9800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3">
         <v>0</v>
@@ -4488,14 +4599,14 @@
       <c r="X49" s="3">
         <v>0</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>8</v>
+      <c r="Y49" s="3">
+        <v>0</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
@@ -4507,10 +4618,10 @@
         <v>0</v>
       </c>
       <c r="AE49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG49" s="3">
         <v>0</v>
@@ -4521,8 +4632,11 @@
       <c r="AI49" s="3">
         <v>0</v>
       </c>
+      <c r="AJ49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,8 +4840,11 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4732,11 +4852,11 @@
         <v>300</v>
       </c>
       <c r="E52" s="3">
+        <v>300</v>
+      </c>
+      <c r="F52" s="3">
         <v>400</v>
       </c>
-      <c r="F52" s="3">
-        <v>300</v>
-      </c>
       <c r="G52" s="3">
         <v>300</v>
       </c>
@@ -4750,7 +4870,7 @@
         <v>300</v>
       </c>
       <c r="K52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L52" s="3">
         <v>0</v>
@@ -4788,17 +4908,17 @@
       <c r="W52" s="3">
         <v>0</v>
       </c>
-      <c r="X52" s="3" t="s">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y52" s="3">
-        <v>0</v>
-      </c>
       <c r="Z52" s="3">
         <v>0</v>
       </c>
       <c r="AA52" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AB52" s="3">
         <v>500</v>
@@ -4824,8 +4944,11 @@
       <c r="AI52" s="3">
         <v>500</v>
       </c>
+      <c r="AJ52" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E54" s="3">
         <v>26800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>27100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>29400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26700</v>
-      </c>
-      <c r="U54" s="3">
-        <v>25200</v>
       </c>
       <c r="V54" s="3">
         <v>25200</v>
       </c>
       <c r="W54" s="3">
+        <v>25200</v>
+      </c>
+      <c r="X54" s="3">
         <v>25100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>25700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>24400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>23300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>23700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>22100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>20300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>19700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>19300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>18900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,109 +5230,113 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1300</v>
-      </c>
-      <c r="F57" s="3">
-        <v>800</v>
       </c>
       <c r="G57" s="3">
         <v>800</v>
       </c>
       <c r="H57" s="3">
+        <v>800</v>
+      </c>
+      <c r="I57" s="3">
         <v>1200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1100</v>
-      </c>
-      <c r="T57" s="3">
-        <v>1000</v>
       </c>
       <c r="U57" s="3">
         <v>1000</v>
       </c>
       <c r="V57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W57" s="3">
         <v>900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1000</v>
-      </c>
-      <c r="X57" s="3">
-        <v>1400</v>
       </c>
       <c r="Y57" s="3">
         <v>1400</v>
       </c>
       <c r="Z57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AA57" s="3">
         <v>600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>800</v>
-      </c>
-      <c r="AF57" s="3">
-        <v>1200</v>
       </c>
       <c r="AG57" s="3">
         <v>1200</v>
       </c>
       <c r="AH57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AI57" s="3">
         <v>600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5213,22 +5347,22 @@
         <v>700</v>
       </c>
       <c r="F58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G58" s="3">
         <v>600</v>
       </c>
       <c r="H58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="I58" s="3">
         <v>700</v>
       </c>
       <c r="J58" s="3">
+        <v>700</v>
+      </c>
+      <c r="K58" s="3">
         <v>600</v>
-      </c>
-      <c r="K58" s="3">
-        <v>500</v>
       </c>
       <c r="L58" s="3">
         <v>500</v>
@@ -5249,10 +5383,10 @@
         <v>500</v>
       </c>
       <c r="R58" s="3">
+        <v>500</v>
+      </c>
+      <c r="S58" s="3">
         <v>600</v>
-      </c>
-      <c r="S58" s="3">
-        <v>500</v>
       </c>
       <c r="T58" s="3">
         <v>500</v>
@@ -5270,7 +5404,7 @@
         <v>500</v>
       </c>
       <c r="Y58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="Z58" s="3">
         <v>400</v>
@@ -5279,31 +5413,34 @@
         <v>400</v>
       </c>
       <c r="AB58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AC58" s="3">
         <v>300</v>
       </c>
       <c r="AD58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AE58" s="3">
         <v>200</v>
       </c>
       <c r="AF58" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AG58" s="3">
         <v>400</v>
       </c>
       <c r="AH58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AI58" s="3">
         <v>300</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5329,284 +5466,293 @@
         <v>0</v>
       </c>
       <c r="K59" s="3">
+        <v>0</v>
+      </c>
+      <c r="L59" s="3">
         <v>1800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1200</v>
-      </c>
-      <c r="AA59" s="3">
-        <v>1000</v>
       </c>
       <c r="AB59" s="3">
         <v>1000</v>
       </c>
       <c r="AC59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AD59" s="3">
         <v>700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E60" s="3">
         <v>2900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2200</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6300</v>
+      </c>
+      <c r="E61" s="3">
         <v>6400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6600</v>
-      </c>
-      <c r="H61" s="3">
-        <v>6700</v>
       </c>
       <c r="I61" s="3">
         <v>6700</v>
       </c>
       <c r="J61" s="3">
+        <v>6700</v>
+      </c>
+      <c r="K61" s="3">
         <v>6800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>6100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>7900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>8000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>6600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5631,53 +5777,53 @@
       <c r="J62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K62" s="3">
-        <v>1800</v>
+      <c r="K62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L62" s="3">
         <v>1800</v>
       </c>
       <c r="M62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="N62" s="3">
         <v>1700</v>
-      </c>
-      <c r="N62" s="3">
-        <v>2100</v>
       </c>
       <c r="O62" s="3">
         <v>2100</v>
       </c>
       <c r="P62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="Q62" s="3">
         <v>2200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2100</v>
-      </c>
-      <c r="S62" s="3">
-        <v>2000</v>
       </c>
       <c r="T62" s="3">
         <v>2000</v>
       </c>
       <c r="U62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="V62" s="3">
         <v>1700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1900</v>
-      </c>
-      <c r="W62" s="3">
-        <v>1700</v>
       </c>
       <c r="X62" s="3">
         <v>1700</v>
       </c>
       <c r="Y62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="Z62" s="3">
         <v>1500</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>600</v>
       </c>
       <c r="AA62" s="3">
         <v>600</v>
@@ -5686,10 +5832,10 @@
         <v>600</v>
       </c>
       <c r="AC62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AD62" s="3">
         <v>500</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>800</v>
       </c>
       <c r="AE62" s="3">
         <v>800</v>
@@ -5698,16 +5844,19 @@
         <v>800</v>
       </c>
       <c r="AG62" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AH62" s="3">
         <v>700</v>
       </c>
       <c r="AI62" s="3">
+        <v>700</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E66" s="3">
         <v>10200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>12400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>11900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>12500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>10500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>9600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E72" s="3">
         <v>8400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>6700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4100</v>
-      </c>
-      <c r="W72" s="3">
-        <v>4200</v>
       </c>
       <c r="X72" s="3">
         <v>4200</v>
       </c>
       <c r="Y72" s="3">
+        <v>4200</v>
+      </c>
+      <c r="Z72" s="3">
         <v>3800</v>
-      </c>
-      <c r="Z72" s="3">
-        <v>3700</v>
       </c>
       <c r="AA72" s="3">
         <v>3700</v>
       </c>
       <c r="AB72" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AC72" s="3">
         <v>3800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>3500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3200</v>
-      </c>
-      <c r="AE72" s="3">
-        <v>3300</v>
       </c>
       <c r="AF72" s="3">
         <v>3300</v>
       </c>
       <c r="AG72" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AH72" s="3">
         <v>3000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>2800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,76 +7138,79 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16400</v>
+      </c>
+      <c r="E76" s="3">
         <v>16600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>16600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16500</v>
-      </c>
-      <c r="K76" s="3">
-        <v>16700</v>
       </c>
       <c r="L76" s="3">
         <v>16700</v>
       </c>
       <c r="M76" s="3">
+        <v>16700</v>
+      </c>
+      <c r="N76" s="3">
         <v>15900</v>
-      </c>
-      <c r="N76" s="3">
-        <v>15500</v>
       </c>
       <c r="O76" s="3">
         <v>15500</v>
       </c>
       <c r="P76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="Q76" s="3">
         <v>15200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>12800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13000</v>
-      </c>
-      <c r="W76" s="3">
-        <v>13200</v>
       </c>
       <c r="X76" s="3">
         <v>13200</v>
       </c>
       <c r="Y76" s="3">
-        <v>12800</v>
+        <v>13200</v>
       </c>
       <c r="Z76" s="3">
         <v>12800</v>
@@ -7033,31 +7219,34 @@
         <v>12800</v>
       </c>
       <c r="AB76" s="3">
+        <v>12800</v>
+      </c>
+      <c r="AC76" s="3">
         <v>12900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>12500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12300</v>
-      </c>
-      <c r="AE76" s="3">
-        <v>12400</v>
       </c>
       <c r="AF76" s="3">
         <v>12400</v>
       </c>
       <c r="AG76" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AH76" s="3">
         <v>12100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
         <v>45504</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45412</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45322</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45230</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45138</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44957</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44592</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44316</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44227</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44043</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43951</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43861</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43769</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43677</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43585</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43496</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43404</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43312</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43220</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43131</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43039</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42947</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42855</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42766</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E81" s="3">
         <v>400</v>
       </c>
-      <c r="E81" s="3">
-        <v>0</v>
-      </c>
       <c r="F81" s="3">
+        <v>0</v>
+      </c>
+      <c r="G81" s="3">
         <v>-200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>600</v>
       </c>
-      <c r="I81" s="3">
-        <v>100</v>
-      </c>
       <c r="J81" s="3">
+        <v>100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-100</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>800</v>
       </c>
-      <c r="M81" s="3">
-        <v>300</v>
-      </c>
       <c r="N81" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="P81" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q81" s="3">
         <v>1000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>400</v>
       </c>
-      <c r="R81" s="3">
-        <v>100</v>
-      </c>
       <c r="S81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="T81" s="3">
+        <v>300</v>
+      </c>
+      <c r="U81" s="3">
         <v>700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
       <c r="X81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3">
         <v>400</v>
       </c>
-      <c r="Y81" s="3">
-        <v>100</v>
-      </c>
       <c r="Z81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-100</v>
       </c>
-      <c r="AE81" s="3">
-        <v>0</v>
-      </c>
       <c r="AF81" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH81" s="3">
         <v>400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,8 +7599,9 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7413,11 +7612,11 @@
         <v>300</v>
       </c>
       <c r="F83" s="3">
+        <v>300</v>
+      </c>
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="G83" s="3">
-        <v>300</v>
-      </c>
       <c r="H83" s="3">
         <v>300</v>
       </c>
@@ -7476,14 +7675,14 @@
         <v>300</v>
       </c>
       <c r="AA83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB83" s="3">
         <v>800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>500</v>
       </c>
-      <c r="AC83" s="3">
-        <v>300</v>
-      </c>
       <c r="AD83" s="3">
         <v>300</v>
       </c>
@@ -7491,19 +7690,22 @@
         <v>300</v>
       </c>
       <c r="AF83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG83" s="3">
         <v>200</v>
       </c>
-      <c r="AG83" s="3">
-        <v>300</v>
-      </c>
       <c r="AH83" s="3">
         <v>300</v>
       </c>
       <c r="AI83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100</v>
+      </c>
+      <c r="E89" s="3">
         <v>1200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-500</v>
       </c>
-      <c r="J89" s="3">
-        <v>300</v>
-      </c>
       <c r="K89" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L89" s="3">
+        <v>0</v>
+      </c>
+      <c r="M89" s="3">
         <v>1600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>400</v>
-      </c>
-      <c r="AA89" s="3">
-        <v>800</v>
       </c>
       <c r="AB89" s="3">
         <v>800</v>
       </c>
       <c r="AC89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AD89" s="3">
         <v>-100</v>
       </c>
-      <c r="AD89" s="3">
-        <v>100</v>
-      </c>
       <c r="AE89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,19 +8365,20 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-300</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-200</v>
       </c>
       <c r="G91" s="3">
         <v>-200</v>
@@ -8166,88 +8387,91 @@
         <v>-200</v>
       </c>
       <c r="I91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J91" s="3">
         <v>-400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-200</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-300</v>
       </c>
       <c r="L91" s="3">
         <v>-300</v>
       </c>
       <c r="M91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="N91" s="3">
         <v>-200</v>
-      </c>
-      <c r="N91" s="3">
-        <v>-300</v>
       </c>
       <c r="O91" s="3">
         <v>-300</v>
       </c>
       <c r="P91" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-200</v>
       </c>
       <c r="R91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S91" s="3">
         <v>-300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-200</v>
       </c>
-      <c r="T91" s="3">
-        <v>0</v>
-      </c>
       <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
         <v>-400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-200</v>
       </c>
-      <c r="AH91" s="3">
-        <v>0</v>
-      </c>
       <c r="AI91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>700</v>
       </c>
-      <c r="F94" s="3">
-        <v>300</v>
-      </c>
       <c r="G94" s="3">
+        <v>300</v>
+      </c>
+      <c r="H94" s="3">
         <v>-4200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-200</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-300</v>
       </c>
       <c r="O94" s="3">
         <v>-300</v>
       </c>
       <c r="P94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="Q94" s="3">
         <v>-200</v>
       </c>
       <c r="R94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-200</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
       <c r="U94" s="3">
+        <v>0</v>
+      </c>
+      <c r="V94" s="3">
         <v>-400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-700</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-400</v>
       </c>
       <c r="AF94" s="3">
         <v>-400</v>
       </c>
       <c r="AG94" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="AH94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,8 +8819,9 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8612,8 +8846,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,8 +9233,11 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -8999,10 +9245,10 @@
         <v>-100</v>
       </c>
       <c r="E100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-700</v>
-      </c>
-      <c r="F100" s="3">
-        <v>-100</v>
       </c>
       <c r="G100" s="3">
         <v>-100</v>
@@ -9017,25 +9263,25 @@
         <v>-100</v>
       </c>
       <c r="K100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="L100" s="3">
         <v>-200</v>
-      </c>
-      <c r="L100" s="3">
-        <v>-100</v>
       </c>
       <c r="M100" s="3">
         <v>-100</v>
       </c>
       <c r="N100" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="O100" s="3">
         <v>-200</v>
       </c>
       <c r="P100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-1300</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-100</v>
       </c>
       <c r="R100" s="3">
         <v>-100</v>
@@ -9047,37 +9293,37 @@
         <v>-100</v>
       </c>
       <c r="U100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="V100" s="3">
         <v>1000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>2800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>2600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>700</v>
-      </c>
-      <c r="AE100" s="3">
-        <v>-100</v>
       </c>
       <c r="AF100" s="3">
         <v>-100</v>
@@ -9091,8 +9337,11 @@
       <c r="AI100" s="3">
         <v>-100</v>
       </c>
+      <c r="AJ100" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9117,8 +9366,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E102" s="3">
         <v>900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-4500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1000</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
       <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-100</v>
       </c>
-      <c r="R102" s="3">
-        <v>300</v>
-      </c>
       <c r="S102" s="3">
+        <v>300</v>
+      </c>
+      <c r="T102" s="3">
         <v>700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
-        <v>300</v>
-      </c>
       <c r="AA102" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AB102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC102" s="3">
         <v>400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
-        <v>100</v>
-      </c>
       <c r="AE102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AF102" s="3">
         <v>-300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>700</v>
       </c>
-      <c r="AG102" s="3">
-        <v>100</v>
-      </c>
       <c r="AH102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
   <si>
     <t>BWTL</t>
   </si>
@@ -656,386 +656,396 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E8" s="3">
         <v>7800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>10200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>9500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>10500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>9700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>9600</v>
-      </c>
-      <c r="S8" s="3">
-        <v>7600</v>
       </c>
       <c r="T8" s="3">
         <v>7600</v>
       </c>
       <c r="U8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="V8" s="3">
         <v>8900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>7000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>7200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>22900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>16000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>8300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>6300</v>
-      </c>
-      <c r="AI8" s="3">
-        <v>5900</v>
       </c>
       <c r="AJ8" s="3">
         <v>5900</v>
       </c>
+      <c r="AK8" s="3">
+        <v>5900</v>
+      </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E9" s="3">
         <v>4300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>4700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>7300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5200</v>
-      </c>
-      <c r="S9" s="3">
-        <v>3800</v>
       </c>
       <c r="T9" s="3">
         <v>3800</v>
       </c>
       <c r="U9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="V9" s="3">
         <v>4100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>5100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>13200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4000</v>
-      </c>
-      <c r="AE9" s="3">
-        <v>3600</v>
       </c>
       <c r="AF9" s="3">
         <v>3600</v>
       </c>
       <c r="AG9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AH9" s="3">
         <v>4500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E10" s="3">
         <v>3400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3700</v>
-      </c>
-      <c r="G10" s="3">
-        <v>3600</v>
       </c>
       <c r="H10" s="3">
         <v>3600</v>
       </c>
       <c r="I10" s="3">
+        <v>3600</v>
+      </c>
+      <c r="J10" s="3">
         <v>5200</v>
-      </c>
-      <c r="J10" s="3">
-        <v>4000</v>
       </c>
       <c r="K10" s="3">
         <v>4000</v>
@@ -1044,79 +1054,82 @@
         <v>4000</v>
       </c>
       <c r="M10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="N10" s="3">
         <v>5600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>4300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>6800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>4400</v>
-      </c>
-      <c r="S10" s="3">
-        <v>3800</v>
       </c>
       <c r="T10" s="3">
         <v>3800</v>
       </c>
       <c r="U10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="V10" s="3">
         <v>4800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2500</v>
-      </c>
-      <c r="W10" s="3">
-        <v>3100</v>
       </c>
       <c r="X10" s="3">
         <v>3100</v>
       </c>
       <c r="Y10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="Z10" s="3">
         <v>4200</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>3100</v>
       </c>
       <c r="AA10" s="3">
         <v>3100</v>
       </c>
       <c r="AB10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AC10" s="3">
         <v>9700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>6700</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>2900</v>
       </c>
       <c r="AE10" s="3">
         <v>2900</v>
       </c>
       <c r="AF10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AG10" s="3">
         <v>2800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>2700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1153,8 +1166,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1257,8 +1271,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,13 +1378,16 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E14" s="3">
         <v>0</v>
@@ -1388,22 +1408,22 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>-100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1411,11 +1431,11 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>100</v>
-      </c>
-      <c r="T14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="T14" s="3">
+        <v>100</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1432,8 +1452,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1441,17 +1461,17 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1459,14 +1479,17 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1543,14 +1566,14 @@
         <v>300</v>
       </c>
       <c r="AB15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC15" s="3">
         <v>800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>500</v>
       </c>
-      <c r="AD15" s="3">
-        <v>300</v>
-      </c>
       <c r="AE15" s="3">
         <v>300</v>
       </c>
@@ -1558,19 +1581,22 @@
         <v>300</v>
       </c>
       <c r="AG15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH15" s="3">
         <v>200</v>
       </c>
-      <c r="AH15" s="3">
-        <v>300</v>
-      </c>
       <c r="AI15" s="3">
         <v>300</v>
       </c>
       <c r="AJ15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK15" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1630,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E17" s="3">
         <v>8100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>9700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>8500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>9300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>11800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>10000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>12600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>9000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>7400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>7100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>22500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>15500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>6800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>7700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>6200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>800</v>
       </c>
-      <c r="J18" s="3">
-        <v>100</v>
-      </c>
       <c r="K18" s="3">
+        <v>100</v>
+      </c>
+      <c r="L18" s="3">
         <v>-100</v>
       </c>
-      <c r="L18" s="3">
-        <v>100</v>
-      </c>
       <c r="M18" s="3">
+        <v>100</v>
+      </c>
+      <c r="N18" s="3">
         <v>1100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>500</v>
       </c>
-      <c r="O18" s="3">
-        <v>300</v>
-      </c>
       <c r="P18" s="3">
+        <v>300</v>
+      </c>
+      <c r="Q18" s="3">
         <v>500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-100</v>
       </c>
-      <c r="X18" s="3">
-        <v>100</v>
-      </c>
       <c r="Y18" s="3">
+        <v>100</v>
+      </c>
+      <c r="Z18" s="3">
         <v>600</v>
       </c>
-      <c r="Z18" s="3">
-        <v>100</v>
-      </c>
       <c r="AA18" s="3">
         <v>100</v>
       </c>
       <c r="AB18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC18" s="3">
         <v>400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>500</v>
       </c>
-      <c r="AD18" s="3">
-        <v>100</v>
-      </c>
       <c r="AE18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF18" s="3">
         <v>0</v>
       </c>
       <c r="AG18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3">
         <v>600</v>
       </c>
-      <c r="AH18" s="3">
-        <v>100</v>
-      </c>
       <c r="AI18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ18" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,13 +1883,14 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1865,13 +1899,13 @@
         <v>0</v>
       </c>
       <c r="G20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>-100</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="J20" s="3">
         <v>0</v>
@@ -1883,10 +1917,10 @@
         <v>0</v>
       </c>
       <c r="M20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1895,16 +1929,16 @@
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U20" s="3">
         <v>0</v>
@@ -1913,10 +1947,10 @@
         <v>0</v>
       </c>
       <c r="W20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y20" s="3">
         <v>0</v>
@@ -1925,141 +1959,147 @@
         <v>0</v>
       </c>
       <c r="AA20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="3">
         <v>100</v>
       </c>
       <c r="AC20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
       <c r="AE20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AF20" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AG20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>200</v>
       </c>
-      <c r="G21" s="3">
-        <v>100</v>
-      </c>
       <c r="H21" s="3">
         <v>100</v>
       </c>
       <c r="I21" s="3">
+        <v>100</v>
+      </c>
+      <c r="J21" s="3">
         <v>1100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1300</v>
       </c>
-      <c r="V21" s="3">
-        <v>100</v>
-      </c>
       <c r="W21" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="X21" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y21" s="3">
         <v>400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1100</v>
       </c>
-      <c r="AD21" s="3">
-        <v>300</v>
-      </c>
       <c r="AE21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF21" s="3">
         <v>500</v>
       </c>
-      <c r="AF21" s="3">
-        <v>300</v>
-      </c>
       <c r="AG21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH21" s="3">
         <v>800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>600</v>
       </c>
-      <c r="AI21" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2136,11 +2176,11 @@
         <v>100</v>
       </c>
       <c r="AB22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC22" s="3">
         <v>200</v>
       </c>
-      <c r="AC22" s="3">
-        <v>100</v>
-      </c>
       <c r="AD22" s="3">
         <v>100</v>
       </c>
@@ -2151,7 +2191,7 @@
         <v>100</v>
       </c>
       <c r="AG22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH22" s="3">
         <v>0</v>
@@ -2162,136 +2202,142 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
         <v>-300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>500</v>
       </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
       <c r="G23" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="H23" s="3">
         <v>-200</v>
       </c>
       <c r="I23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="J23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
-        <v>100</v>
-      </c>
       <c r="K23" s="3">
+        <v>100</v>
+      </c>
+      <c r="L23" s="3">
         <v>-100</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
       <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>1100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>500</v>
       </c>
-      <c r="S23" s="3">
-        <v>100</v>
-      </c>
       <c r="T23" s="3">
+        <v>100</v>
+      </c>
+      <c r="U23" s="3">
         <v>400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
       <c r="Y23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3">
         <v>500</v>
       </c>
-      <c r="Z23" s="3">
-        <v>100</v>
-      </c>
       <c r="AA23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB23" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD23" s="3">
         <v>500</v>
       </c>
-      <c r="AD23" s="3">
-        <v>0</v>
-      </c>
       <c r="AE23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="3">
         <v>200</v>
       </c>
-      <c r="AF23" s="3">
-        <v>0</v>
-      </c>
       <c r="AG23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="3">
         <v>500</v>
       </c>
-      <c r="AH23" s="3">
-        <v>300</v>
-      </c>
       <c r="AI23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ23" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-100</v>
       </c>
-      <c r="E24" s="3">
-        <v>100</v>
-      </c>
       <c r="F24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>200</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
@@ -2299,79 +2345,82 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="N24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="O24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>100</v>
+      </c>
+      <c r="R24" s="3">
         <v>400</v>
       </c>
-      <c r="R24" s="3">
-        <v>100</v>
-      </c>
       <c r="S24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U24" s="3">
+        <v>100</v>
+      </c>
+      <c r="V24" s="3">
         <v>200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-100</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
-      </c>
       <c r="X24" s="3">
         <v>0</v>
       </c>
       <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
-      </c>
       <c r="AA24" s="3">
         <v>0</v>
       </c>
       <c r="AB24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC24" s="3">
         <v>100</v>
       </c>
       <c r="AD24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="3">
         <v>200</v>
       </c>
-      <c r="AH24" s="3">
-        <v>100</v>
-      </c>
       <c r="AI24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ24" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2523,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
         <v>-200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>400</v>
       </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
       <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
         <v>-200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>600</v>
       </c>
-      <c r="J26" s="3">
-        <v>100</v>
-      </c>
       <c r="K26" s="3">
+        <v>100</v>
+      </c>
+      <c r="L26" s="3">
         <v>-100</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>800</v>
       </c>
-      <c r="N26" s="3">
-        <v>300</v>
-      </c>
       <c r="O26" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P26" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="3">
+        <v>300</v>
+      </c>
+      <c r="R26" s="3">
         <v>1000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>400</v>
       </c>
-      <c r="S26" s="3">
-        <v>100</v>
-      </c>
       <c r="T26" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U26" s="3">
+        <v>300</v>
+      </c>
+      <c r="V26" s="3">
         <v>700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
       <c r="Y26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3">
         <v>400</v>
       </c>
-      <c r="Z26" s="3">
-        <v>100</v>
-      </c>
       <c r="AA26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="3">
         <v>200</v>
       </c>
-      <c r="AC26" s="3">
-        <v>300</v>
-      </c>
       <c r="AD26" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AE26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG26" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AH26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI26" s="3">
         <v>200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
         <v>-200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>400</v>
       </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
       <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
         <v>-200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>600</v>
       </c>
-      <c r="J27" s="3">
-        <v>100</v>
-      </c>
       <c r="K27" s="3">
+        <v>100</v>
+      </c>
+      <c r="L27" s="3">
         <v>-100</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>800</v>
       </c>
-      <c r="N27" s="3">
-        <v>300</v>
-      </c>
       <c r="O27" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P27" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q27" s="3">
+        <v>300</v>
+      </c>
+      <c r="R27" s="3">
         <v>1000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>400</v>
       </c>
-      <c r="S27" s="3">
-        <v>100</v>
-      </c>
       <c r="T27" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U27" s="3">
+        <v>300</v>
+      </c>
+      <c r="V27" s="3">
         <v>700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
       <c r="Y27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3">
         <v>400</v>
       </c>
-      <c r="Z27" s="3">
-        <v>100</v>
-      </c>
       <c r="AA27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AB27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="3">
         <v>200</v>
       </c>
-      <c r="AC27" s="3">
-        <v>300</v>
-      </c>
       <c r="AD27" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AE27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG27" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AH27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI27" s="3">
         <v>200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2844,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2842,8 +2903,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2860,38 +2921,41 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-200</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
       <c r="AC29" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AD29" s="3">
         <v>200</v>
       </c>
       <c r="AE29" s="3">
+        <v>200</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-200</v>
       </c>
-      <c r="AF29" s="3">
-        <v>0</v>
-      </c>
       <c r="AG29" s="3">
         <v>0</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>200</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3058,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,13 +3165,16 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -3113,13 +3183,13 @@
         <v>0</v>
       </c>
       <c r="G32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>100</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32" s="3">
         <v>0</v>
@@ -3131,11 +3201,11 @@
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3143,17 +3213,17 @@
         <v>0</v>
       </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3161,11 +3231,11 @@
         <v>0</v>
       </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
-        <v>0</v>
-      </c>
       <c r="Y32" s="3">
         <v>0</v>
       </c>
@@ -3173,141 +3243,147 @@
         <v>0</v>
       </c>
       <c r="AA32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AB32" s="3">
         <v>-100</v>
       </c>
       <c r="AC32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
       <c r="AE32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3">
         <v>-300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
       <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-300</v>
       </c>
-      <c r="AI32" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
         <v>-200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>400</v>
       </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
       <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
         <v>-200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>600</v>
       </c>
-      <c r="J33" s="3">
-        <v>100</v>
-      </c>
       <c r="K33" s="3">
+        <v>100</v>
+      </c>
+      <c r="L33" s="3">
         <v>-100</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>800</v>
       </c>
-      <c r="N33" s="3">
-        <v>300</v>
-      </c>
       <c r="O33" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q33" s="3">
+        <v>300</v>
+      </c>
+      <c r="R33" s="3">
         <v>1000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>400</v>
       </c>
-      <c r="S33" s="3">
-        <v>100</v>
-      </c>
       <c r="T33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U33" s="3">
+        <v>300</v>
+      </c>
+      <c r="V33" s="3">
         <v>700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
       <c r="Y33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="3">
         <v>400</v>
       </c>
-      <c r="Z33" s="3">
-        <v>100</v>
-      </c>
       <c r="AA33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-100</v>
       </c>
-      <c r="AF33" s="3">
-        <v>0</v>
-      </c>
       <c r="AG33" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI33" s="3">
         <v>400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3486,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
         <v>-200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>400</v>
       </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
       <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
         <v>-200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>600</v>
       </c>
-      <c r="J35" s="3">
-        <v>100</v>
-      </c>
       <c r="K35" s="3">
+        <v>100</v>
+      </c>
+      <c r="L35" s="3">
         <v>-100</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>800</v>
       </c>
-      <c r="N35" s="3">
-        <v>300</v>
-      </c>
       <c r="O35" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q35" s="3">
+        <v>300</v>
+      </c>
+      <c r="R35" s="3">
         <v>1000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>400</v>
       </c>
-      <c r="S35" s="3">
-        <v>100</v>
-      </c>
       <c r="T35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U35" s="3">
+        <v>300</v>
+      </c>
+      <c r="V35" s="3">
         <v>700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
       <c r="Y35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="3">
         <v>400</v>
       </c>
-      <c r="Z35" s="3">
-        <v>100</v>
-      </c>
       <c r="AA35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-100</v>
       </c>
-      <c r="AF35" s="3">
-        <v>0</v>
-      </c>
       <c r="AG35" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AH35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI35" s="3">
         <v>400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3746,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,112 +3785,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E41" s="3">
         <v>4100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6300</v>
-      </c>
-      <c r="K41" s="3">
-        <v>7300</v>
       </c>
       <c r="L41" s="3">
         <v>7300</v>
       </c>
       <c r="M41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="N41" s="3">
         <v>7800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>7400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3600</v>
-      </c>
-      <c r="AE41" s="3">
-        <v>4000</v>
       </c>
       <c r="AF41" s="3">
         <v>4000</v>
       </c>
       <c r="AG41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AH41" s="3">
         <v>4300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3812,19 +3902,19 @@
         <v>4000</v>
       </c>
       <c r="E42" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="F42" s="3">
         <v>3900</v>
       </c>
       <c r="G42" s="3">
+        <v>3900</v>
+      </c>
+      <c r="H42" s="3">
         <v>4800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5200</v>
-      </c>
-      <c r="I42" s="3">
-        <v>1200</v>
       </c>
       <c r="J42" s="3">
         <v>1200</v>
@@ -3875,13 +3965,13 @@
         <v>1200</v>
       </c>
       <c r="Z42" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AA42" s="3">
         <v>1000</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>900</v>
-      </c>
-      <c r="AB42" s="3">
-        <v>1000</v>
       </c>
       <c r="AC42" s="3">
         <v>1000</v>
@@ -3907,13 +3997,16 @@
       <c r="AJ42" s="3">
         <v>1000</v>
       </c>
+      <c r="AK42" s="3">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E43" s="3">
         <v>0</v>
@@ -3973,10 +4066,10 @@
         <v>0</v>
       </c>
       <c r="X43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
@@ -4011,112 +4104,118 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E44" s="3">
         <v>4800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>5200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>6500</v>
-      </c>
-      <c r="K44" s="3">
-        <v>5700</v>
       </c>
       <c r="L44" s="3">
         <v>5700</v>
       </c>
       <c r="M44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="N44" s="3">
         <v>5800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>3900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>4000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4000</v>
-      </c>
-      <c r="X44" s="3">
-        <v>4200</v>
       </c>
       <c r="Y44" s="3">
         <v>4200</v>
       </c>
       <c r="Z44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AA44" s="3">
         <v>4400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>3800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>4300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>3600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4124,7 +4223,7 @@
         <v>200</v>
       </c>
       <c r="E45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F45" s="3">
         <v>100</v>
@@ -4145,37 +4244,37 @@
         <v>100</v>
       </c>
       <c r="L45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="M45" s="3">
+        <v>300</v>
+      </c>
+      <c r="N45" s="3">
         <v>200</v>
       </c>
-      <c r="N45" s="3">
-        <v>300</v>
-      </c>
       <c r="O45" s="3">
         <v>300</v>
       </c>
       <c r="P45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="Q45" s="3">
         <v>200</v>
       </c>
       <c r="R45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="S45" s="3">
         <v>300</v>
       </c>
       <c r="T45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U45" s="3">
         <v>200</v>
       </c>
       <c r="V45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="W45" s="3">
         <v>300</v>
@@ -4196,7 +4295,7 @@
         <v>300</v>
       </c>
       <c r="AC45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AD45" s="3">
         <v>400</v>
@@ -4205,7 +4304,7 @@
         <v>400</v>
       </c>
       <c r="AF45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AG45" s="3">
         <v>300</v>
@@ -4214,117 +4313,123 @@
         <v>300</v>
       </c>
       <c r="AI45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ45" s="3">
         <v>400</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13600</v>
+      </c>
+      <c r="E46" s="3">
         <v>13400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>14000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>14700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>13400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>12700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12000</v>
-      </c>
-      <c r="V46" s="3">
-        <v>10300</v>
       </c>
       <c r="W46" s="3">
         <v>10300</v>
       </c>
       <c r="X46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="Y46" s="3">
         <v>10500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>10900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>9600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>8900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4352,24 +4457,24 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>300</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>300</v>
       </c>
       <c r="N47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
       <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3">
         <v>700</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
       <c r="R47" s="3">
         <v>0</v>
       </c>
@@ -4386,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="W47" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="X47" s="3">
         <v>800</v>
@@ -4401,7 +4506,7 @@
         <v>800</v>
       </c>
       <c r="AB47" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="AC47" s="3">
         <v>300</v>
@@ -4425,36 +4530,39 @@
         <v>300</v>
       </c>
       <c r="AJ47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E48" s="3">
         <v>12500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13100</v>
-      </c>
-      <c r="K48" s="3">
-        <v>12900</v>
       </c>
       <c r="L48" s="3">
         <v>12900</v>
@@ -4463,87 +4571,90 @@
         <v>12900</v>
       </c>
       <c r="N48" s="3">
+        <v>12900</v>
+      </c>
+      <c r="O48" s="3">
         <v>13800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>14300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>13700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>14500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14500</v>
-      </c>
-      <c r="T48" s="3">
-        <v>14600</v>
       </c>
       <c r="U48" s="3">
         <v>14600</v>
       </c>
       <c r="V48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="W48" s="3">
         <v>14900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>14000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>13700</v>
-      </c>
-      <c r="Y48" s="3">
-        <v>14000</v>
       </c>
       <c r="Z48" s="3">
         <v>14000</v>
       </c>
       <c r="AA48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AB48" s="3">
         <v>13000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>13100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>12100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>10500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>9800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G49" s="3">
         <v>0</v>
@@ -4602,14 +4713,14 @@
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-      <c r="Z49" s="3" t="s">
-        <v>8</v>
+      <c r="Z49" s="3">
+        <v>0</v>
       </c>
       <c r="AA49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
@@ -4621,10 +4732,10 @@
         <v>0</v>
       </c>
       <c r="AF49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH49" s="3">
         <v>0</v>
@@ -4635,8 +4746,11 @@
       <c r="AJ49" s="3">
         <v>0</v>
       </c>
+      <c r="AK49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4853,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,8 +4960,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4855,11 +4975,11 @@
         <v>300</v>
       </c>
       <c r="F52" s="3">
+        <v>300</v>
+      </c>
+      <c r="G52" s="3">
         <v>400</v>
       </c>
-      <c r="G52" s="3">
-        <v>300</v>
-      </c>
       <c r="H52" s="3">
         <v>300</v>
       </c>
@@ -4873,7 +4993,7 @@
         <v>300</v>
       </c>
       <c r="L52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M52" s="3">
         <v>0</v>
@@ -4911,17 +5031,17 @@
       <c r="X52" s="3">
         <v>0</v>
       </c>
-      <c r="Y52" s="3" t="s">
+      <c r="Y52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z52" s="3">
-        <v>0</v>
-      </c>
       <c r="AA52" s="3">
         <v>0</v>
       </c>
       <c r="AB52" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AC52" s="3">
         <v>500</v>
@@ -4947,8 +5067,11 @@
       <c r="AJ52" s="3">
         <v>500</v>
       </c>
+      <c r="AK52" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5174,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26500</v>
+      </c>
+      <c r="E54" s="3">
         <v>26300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>28100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>27800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>28000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>29400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>27400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26700</v>
-      </c>
-      <c r="V54" s="3">
-        <v>25200</v>
       </c>
       <c r="W54" s="3">
         <v>25200</v>
       </c>
       <c r="X54" s="3">
+        <v>25200</v>
+      </c>
+      <c r="Y54" s="3">
         <v>25100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>25700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>24400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>23300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>23600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>23700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>22100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>20300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>19700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>20000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>19300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>18900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5322,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,117 +5361,121 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>800</v>
+      </c>
+      <c r="E57" s="3">
         <v>900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1300</v>
-      </c>
-      <c r="G57" s="3">
-        <v>800</v>
       </c>
       <c r="H57" s="3">
         <v>800</v>
       </c>
       <c r="I57" s="3">
+        <v>800</v>
+      </c>
+      <c r="J57" s="3">
         <v>1200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1100</v>
-      </c>
-      <c r="U57" s="3">
-        <v>1000</v>
       </c>
       <c r="V57" s="3">
         <v>1000</v>
       </c>
       <c r="W57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X57" s="3">
         <v>900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1000</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>1400</v>
       </c>
       <c r="Z57" s="3">
         <v>1400</v>
       </c>
       <c r="AA57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AB57" s="3">
         <v>600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>1200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>800</v>
-      </c>
-      <c r="AG57" s="3">
-        <v>1200</v>
       </c>
       <c r="AH57" s="3">
         <v>1200</v>
       </c>
       <c r="AI57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AJ57" s="3">
         <v>600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E58" s="3">
         <v>700</v>
@@ -5350,22 +5484,22 @@
         <v>700</v>
       </c>
       <c r="G58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="H58" s="3">
         <v>600</v>
       </c>
       <c r="I58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="J58" s="3">
         <v>700</v>
       </c>
       <c r="K58" s="3">
+        <v>700</v>
+      </c>
+      <c r="L58" s="3">
         <v>600</v>
-      </c>
-      <c r="L58" s="3">
-        <v>500</v>
       </c>
       <c r="M58" s="3">
         <v>500</v>
@@ -5386,10 +5520,10 @@
         <v>500</v>
       </c>
       <c r="S58" s="3">
+        <v>500</v>
+      </c>
+      <c r="T58" s="3">
         <v>600</v>
-      </c>
-      <c r="T58" s="3">
-        <v>500</v>
       </c>
       <c r="U58" s="3">
         <v>500</v>
@@ -5407,7 +5541,7 @@
         <v>500</v>
       </c>
       <c r="Z58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AA58" s="3">
         <v>400</v>
@@ -5416,31 +5550,34 @@
         <v>400</v>
       </c>
       <c r="AC58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AD58" s="3">
         <v>300</v>
       </c>
       <c r="AE58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AF58" s="3">
         <v>200</v>
       </c>
       <c r="AG58" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AH58" s="3">
         <v>400</v>
       </c>
       <c r="AI58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AJ58" s="3">
         <v>300</v>
       </c>
+      <c r="AK58" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5469,82 +5606,85 @@
         <v>0</v>
       </c>
       <c r="L59" s="3">
+        <v>0</v>
+      </c>
+      <c r="M59" s="3">
         <v>1800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1200</v>
-      </c>
-      <c r="AB59" s="3">
-        <v>1000</v>
       </c>
       <c r="AC59" s="3">
         <v>1000</v>
       </c>
       <c r="AD59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AE59" s="3">
         <v>700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5552,207 +5692,213 @@
         <v>2700</v>
       </c>
       <c r="E60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F60" s="3">
         <v>2900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2200</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E61" s="3">
         <v>6300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6600</v>
-      </c>
-      <c r="I61" s="3">
-        <v>6700</v>
       </c>
       <c r="J61" s="3">
         <v>6700</v>
       </c>
       <c r="K61" s="3">
+        <v>6700</v>
+      </c>
+      <c r="L61" s="3">
         <v>6800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>7900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>8000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>7500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>6600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5780,53 +5926,53 @@
       <c r="K62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L62" s="3">
-        <v>1800</v>
+      <c r="L62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M62" s="3">
         <v>1800</v>
       </c>
       <c r="N62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="O62" s="3">
         <v>1700</v>
-      </c>
-      <c r="O62" s="3">
-        <v>2100</v>
       </c>
       <c r="P62" s="3">
         <v>2100</v>
       </c>
       <c r="Q62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="R62" s="3">
         <v>2200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2100</v>
-      </c>
-      <c r="T62" s="3">
-        <v>2000</v>
       </c>
       <c r="U62" s="3">
         <v>2000</v>
       </c>
       <c r="V62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="W62" s="3">
         <v>1700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1900</v>
-      </c>
-      <c r="X62" s="3">
-        <v>1700</v>
       </c>
       <c r="Y62" s="3">
         <v>1700</v>
       </c>
       <c r="Z62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AA62" s="3">
         <v>1500</v>
-      </c>
-      <c r="AA62" s="3">
-        <v>600</v>
       </c>
       <c r="AB62" s="3">
         <v>600</v>
@@ -5835,10 +5981,10 @@
         <v>600</v>
       </c>
       <c r="AD62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE62" s="3">
         <v>500</v>
-      </c>
-      <c r="AE62" s="3">
-        <v>800</v>
       </c>
       <c r="AF62" s="3">
         <v>800</v>
@@ -5847,16 +5993,19 @@
         <v>800</v>
       </c>
       <c r="AH62" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AI62" s="3">
         <v>700</v>
       </c>
       <c r="AJ62" s="3">
+        <v>700</v>
+      </c>
+      <c r="AK62" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6108,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6215,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6322,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E66" s="3">
         <v>9800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>12400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>12500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>10500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6470,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6575,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6682,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6789,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,8 +6896,11 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -6734,103 +6908,106 @@
         <v>8200</v>
       </c>
       <c r="E72" s="3">
+        <v>8200</v>
+      </c>
+      <c r="F72" s="3">
         <v>8400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>6700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4100</v>
-      </c>
-      <c r="X72" s="3">
-        <v>4200</v>
       </c>
       <c r="Y72" s="3">
         <v>4200</v>
       </c>
       <c r="Z72" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AA72" s="3">
         <v>3800</v>
-      </c>
-      <c r="AA72" s="3">
-        <v>3700</v>
       </c>
       <c r="AB72" s="3">
         <v>3700</v>
       </c>
       <c r="AC72" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AD72" s="3">
         <v>3800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>3500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3200</v>
-      </c>
-      <c r="AF72" s="3">
-        <v>3300</v>
       </c>
       <c r="AG72" s="3">
         <v>3300</v>
       </c>
       <c r="AH72" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AI72" s="3">
         <v>3000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7110,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7217,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,8 +7324,11 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -7150,70 +7336,70 @@
         <v>16400</v>
       </c>
       <c r="E76" s="3">
+        <v>16400</v>
+      </c>
+      <c r="F76" s="3">
         <v>16600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>16600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16500</v>
-      </c>
-      <c r="L76" s="3">
-        <v>16700</v>
       </c>
       <c r="M76" s="3">
         <v>16700</v>
       </c>
       <c r="N76" s="3">
+        <v>16700</v>
+      </c>
+      <c r="O76" s="3">
         <v>15900</v>
-      </c>
-      <c r="O76" s="3">
-        <v>15500</v>
       </c>
       <c r="P76" s="3">
         <v>15500</v>
       </c>
       <c r="Q76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="R76" s="3">
         <v>15200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>13000</v>
-      </c>
-      <c r="X76" s="3">
-        <v>13200</v>
       </c>
       <c r="Y76" s="3">
         <v>13200</v>
       </c>
       <c r="Z76" s="3">
-        <v>12800</v>
+        <v>13200</v>
       </c>
       <c r="AA76" s="3">
         <v>12800</v>
@@ -7222,31 +7408,34 @@
         <v>12800</v>
       </c>
       <c r="AC76" s="3">
+        <v>12800</v>
+      </c>
+      <c r="AD76" s="3">
         <v>12900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>12500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12300</v>
-      </c>
-      <c r="AF76" s="3">
-        <v>12400</v>
       </c>
       <c r="AG76" s="3">
         <v>12400</v>
       </c>
       <c r="AH76" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AI76" s="3">
         <v>12100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7538,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3">
         <v>-200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>400</v>
       </c>
-      <c r="F81" s="3">
-        <v>0</v>
-      </c>
       <c r="G81" s="3">
+        <v>0</v>
+      </c>
+      <c r="H81" s="3">
         <v>-200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>600</v>
       </c>
-      <c r="J81" s="3">
-        <v>100</v>
-      </c>
       <c r="K81" s="3">
+        <v>100</v>
+      </c>
+      <c r="L81" s="3">
         <v>-100</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>800</v>
       </c>
-      <c r="N81" s="3">
-        <v>300</v>
-      </c>
       <c r="O81" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Q81" s="3">
+        <v>300</v>
+      </c>
+      <c r="R81" s="3">
         <v>1000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>400</v>
       </c>
-      <c r="S81" s="3">
-        <v>100</v>
-      </c>
       <c r="T81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U81" s="3">
+        <v>300</v>
+      </c>
+      <c r="V81" s="3">
         <v>700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
       <c r="Y81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="3">
         <v>400</v>
       </c>
-      <c r="Z81" s="3">
-        <v>100</v>
-      </c>
       <c r="AA81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-100</v>
       </c>
-      <c r="AF81" s="3">
-        <v>0</v>
-      </c>
       <c r="AG81" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AH81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI81" s="3">
         <v>400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,13 +7798,14 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="E83" s="3">
         <v>300</v>
@@ -7615,11 +7814,11 @@
         <v>300</v>
       </c>
       <c r="G83" s="3">
+        <v>300</v>
+      </c>
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3">
-        <v>300</v>
-      </c>
       <c r="I83" s="3">
         <v>300</v>
       </c>
@@ -7678,14 +7877,14 @@
         <v>300</v>
       </c>
       <c r="AB83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AC83" s="3">
         <v>800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>500</v>
       </c>
-      <c r="AD83" s="3">
-        <v>300</v>
-      </c>
       <c r="AE83" s="3">
         <v>300</v>
       </c>
@@ -7693,19 +7892,22 @@
         <v>300</v>
       </c>
       <c r="AG83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AH83" s="3">
         <v>200</v>
       </c>
-      <c r="AH83" s="3">
-        <v>300</v>
-      </c>
       <c r="AI83" s="3">
         <v>300</v>
       </c>
       <c r="AJ83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8010,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8117,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8224,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8331,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8438,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
         <v>1200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-500</v>
       </c>
-      <c r="K89" s="3">
-        <v>300</v>
-      </c>
       <c r="L89" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M89" s="3">
+        <v>0</v>
+      </c>
+      <c r="N89" s="3">
         <v>1600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>2400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>400</v>
-      </c>
-      <c r="AB89" s="3">
-        <v>800</v>
       </c>
       <c r="AC89" s="3">
         <v>800</v>
       </c>
       <c r="AD89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-100</v>
       </c>
-      <c r="AE89" s="3">
-        <v>100</v>
-      </c>
       <c r="AF89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG89" s="3">
         <v>-100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,8 +8586,9 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8375,13 +8596,13 @@
         <v>-100</v>
       </c>
       <c r="E91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F91" s="3">
         <v>-200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-300</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-200</v>
       </c>
       <c r="H91" s="3">
         <v>-200</v>
@@ -8390,88 +8611,91 @@
         <v>-200</v>
       </c>
       <c r="J91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-200</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-300</v>
       </c>
       <c r="M91" s="3">
         <v>-300</v>
       </c>
       <c r="N91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="O91" s="3">
         <v>-200</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-300</v>
       </c>
       <c r="P91" s="3">
         <v>-300</v>
       </c>
       <c r="Q91" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="R91" s="3">
         <v>-200</v>
       </c>
       <c r="S91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T91" s="3">
         <v>-300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-200</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-200</v>
       </c>
-      <c r="AI91" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8798,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8905,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
         <v>-100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>700</v>
       </c>
-      <c r="G94" s="3">
-        <v>300</v>
-      </c>
       <c r="H94" s="3">
+        <v>300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-4200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-200</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-300</v>
       </c>
       <c r="P94" s="3">
         <v>-300</v>
       </c>
       <c r="Q94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="R94" s="3">
         <v>-200</v>
       </c>
       <c r="S94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-200</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-700</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-400</v>
       </c>
       <c r="AG94" s="3">
         <v>-400</v>
       </c>
       <c r="AH94" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="AI94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,8 +9053,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8849,8 +9083,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -8924,8 +9158,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9265,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9372,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,8 +9479,11 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9248,10 +9494,10 @@
         <v>-100</v>
       </c>
       <c r="F100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G100" s="3">
         <v>-700</v>
-      </c>
-      <c r="G100" s="3">
-        <v>-100</v>
       </c>
       <c r="H100" s="3">
         <v>-100</v>
@@ -9266,25 +9512,25 @@
         <v>-100</v>
       </c>
       <c r="L100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="M100" s="3">
         <v>-200</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-100</v>
       </c>
       <c r="N100" s="3">
         <v>-100</v>
       </c>
       <c r="O100" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="P100" s="3">
         <v>-200</v>
       </c>
       <c r="Q100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="R100" s="3">
         <v>-1300</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-100</v>
       </c>
       <c r="S100" s="3">
         <v>-100</v>
@@ -9296,37 +9542,37 @@
         <v>-100</v>
       </c>
       <c r="V100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="W100" s="3">
         <v>1000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-100</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>2800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>700</v>
-      </c>
-      <c r="AF100" s="3">
-        <v>-100</v>
       </c>
       <c r="AG100" s="3">
         <v>-100</v>
@@ -9340,8 +9586,11 @@
       <c r="AJ100" s="3">
         <v>-100</v>
       </c>
+      <c r="AK100" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9369,8 +9618,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9444,108 +9693,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>-500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
-        <v>300</v>
-      </c>
       <c r="T102" s="3">
+        <v>300</v>
+      </c>
+      <c r="U102" s="3">
         <v>700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="AA102" s="3">
-        <v>300</v>
-      </c>
       <c r="AB102" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AC102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD102" s="3">
         <v>400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-400</v>
       </c>
-      <c r="AE102" s="3">
-        <v>100</v>
-      </c>
       <c r="AF102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AG102" s="3">
         <v>-300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>700</v>
       </c>
-      <c r="AH102" s="3">
-        <v>100</v>
-      </c>
       <c r="AI102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AJ102" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BWTL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="92">
   <si>
     <t>BWTL</t>
   </si>
@@ -656,399 +656,408 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42947</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42766</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>7900</v>
+      </c>
+      <c r="E8" s="3">
         <v>6400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>9500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>7700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>12900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>10500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>10400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>9700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>14000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9600</v>
-      </c>
-      <c r="T8" s="3">
-        <v>7600</v>
       </c>
       <c r="U8" s="3">
         <v>7600</v>
       </c>
       <c r="V8" s="3">
+        <v>7600</v>
+      </c>
+      <c r="W8" s="3">
         <v>8900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>7000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>7100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>9300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>7200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>22900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>16000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>6400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>8300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>6300</v>
-      </c>
-      <c r="AJ8" s="3">
-        <v>5900</v>
       </c>
       <c r="AK8" s="3">
         <v>5900</v>
       </c>
+      <c r="AL8" s="3">
+        <v>5900</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4400</v>
+      </c>
+      <c r="E9" s="3">
         <v>2700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>4300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>4700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>7300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>7200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5200</v>
-      </c>
-      <c r="T9" s="3">
-        <v>3800</v>
       </c>
       <c r="U9" s="3">
         <v>3800</v>
       </c>
       <c r="V9" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W9" s="3">
         <v>4100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>5100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>13200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>9300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4000</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>3600</v>
       </c>
       <c r="AG9" s="3">
         <v>3600</v>
       </c>
       <c r="AH9" s="3">
+        <v>3600</v>
+      </c>
+      <c r="AI9" s="3">
         <v>4500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E10" s="3">
         <v>3700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>3400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3700</v>
-      </c>
-      <c r="H10" s="3">
-        <v>3600</v>
       </c>
       <c r="I10" s="3">
         <v>3600</v>
       </c>
       <c r="J10" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K10" s="3">
         <v>5200</v>
-      </c>
-      <c r="K10" s="3">
-        <v>4000</v>
       </c>
       <c r="L10" s="3">
         <v>4000</v>
@@ -1057,79 +1066,82 @@
         <v>4000</v>
       </c>
       <c r="N10" s="3">
+        <v>4000</v>
+      </c>
+      <c r="O10" s="3">
         <v>5600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>4300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>4700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4400</v>
-      </c>
-      <c r="T10" s="3">
-        <v>3800</v>
       </c>
       <c r="U10" s="3">
         <v>3800</v>
       </c>
       <c r="V10" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W10" s="3">
         <v>4800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2500</v>
-      </c>
-      <c r="X10" s="3">
-        <v>3100</v>
       </c>
       <c r="Y10" s="3">
         <v>3100</v>
       </c>
       <c r="Z10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AA10" s="3">
         <v>4200</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>3100</v>
       </c>
       <c r="AB10" s="3">
         <v>3100</v>
       </c>
       <c r="AC10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="AD10" s="3">
         <v>9700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>6700</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>2900</v>
       </c>
       <c r="AF10" s="3">
         <v>2900</v>
       </c>
       <c r="AG10" s="3">
+        <v>2900</v>
+      </c>
+      <c r="AH10" s="3">
         <v>2800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>2700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>2600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1274,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,17 +1397,20 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
         <v>0</v>
       </c>
@@ -1411,22 +1430,22 @@
         <v>0</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1434,11 +1453,11 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>100</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
+        <v>100</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1455,8 +1474,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1464,17 +1483,17 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
@@ -1482,14 +1501,17 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>100</v>
-      </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1569,14 +1591,14 @@
         <v>300</v>
       </c>
       <c r="AC15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD15" s="3">
         <v>800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>500</v>
       </c>
-      <c r="AE15" s="3">
-        <v>300</v>
-      </c>
       <c r="AF15" s="3">
         <v>300</v>
       </c>
@@ -1584,19 +1606,22 @@
         <v>300</v>
       </c>
       <c r="AH15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI15" s="3">
         <v>200</v>
       </c>
-      <c r="AI15" s="3">
-        <v>300</v>
-      </c>
       <c r="AJ15" s="3">
         <v>300</v>
       </c>
       <c r="AK15" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL15" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E17" s="3">
         <v>6600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>8100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>9700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>8500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>8400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>11800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>10000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>10100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>9200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>7400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>7200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>7800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>7100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>7000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>7100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>6800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>22500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>15500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>6800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>6500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>6400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>7700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>6000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>800</v>
       </c>
-      <c r="K18" s="3">
-        <v>100</v>
-      </c>
       <c r="L18" s="3">
+        <v>100</v>
+      </c>
+      <c r="M18" s="3">
         <v>-100</v>
       </c>
-      <c r="M18" s="3">
-        <v>100</v>
-      </c>
       <c r="N18" s="3">
+        <v>100</v>
+      </c>
+      <c r="O18" s="3">
         <v>1100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>500</v>
       </c>
-      <c r="P18" s="3">
-        <v>300</v>
-      </c>
       <c r="Q18" s="3">
+        <v>300</v>
+      </c>
+      <c r="R18" s="3">
         <v>500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-100</v>
       </c>
-      <c r="Y18" s="3">
-        <v>100</v>
-      </c>
       <c r="Z18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AA18" s="3">
         <v>600</v>
       </c>
-      <c r="AA18" s="3">
-        <v>100</v>
-      </c>
       <c r="AB18" s="3">
         <v>100</v>
       </c>
       <c r="AC18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD18" s="3">
         <v>400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>500</v>
       </c>
-      <c r="AE18" s="3">
-        <v>100</v>
-      </c>
       <c r="AF18" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AG18" s="3">
         <v>0</v>
       </c>
       <c r="AH18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="3">
         <v>600</v>
       </c>
-      <c r="AI18" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ18" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK18" s="3">
         <v>-100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1893,7 +1926,7 @@
         <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="3">
         <v>0</v>
@@ -1902,13 +1935,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>-100</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1920,10 +1953,10 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P20" s="3">
         <v>0</v>
@@ -1932,16 +1965,16 @@
         <v>0</v>
       </c>
       <c r="R20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="U20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="V20" s="3">
         <v>0</v>
@@ -1950,10 +1983,10 @@
         <v>0</v>
       </c>
       <c r="X20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z20" s="3">
         <v>0</v>
@@ -1962,144 +1995,150 @@
         <v>0</v>
       </c>
       <c r="AB20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AC20" s="3">
         <v>100</v>
       </c>
       <c r="AD20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AE20" s="3">
         <v>0</v>
       </c>
       <c r="AF20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AG20" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AH20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AJ20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>100</v>
+      </c>
+      <c r="E21" s="3">
         <v>200</v>
       </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
       <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
         <v>800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>200</v>
       </c>
-      <c r="H21" s="3">
-        <v>100</v>
-      </c>
       <c r="I21" s="3">
         <v>100</v>
       </c>
       <c r="J21" s="3">
+        <v>100</v>
+      </c>
+      <c r="K21" s="3">
         <v>1100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1300</v>
       </c>
-      <c r="W21" s="3">
-        <v>100</v>
-      </c>
       <c r="X21" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="Y21" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z21" s="3">
         <v>400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1100</v>
       </c>
-      <c r="AE21" s="3">
-        <v>300</v>
-      </c>
       <c r="AF21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG21" s="3">
         <v>500</v>
       </c>
-      <c r="AG21" s="3">
-        <v>300</v>
-      </c>
       <c r="AH21" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI21" s="3">
         <v>800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>600</v>
       </c>
-      <c r="AJ21" s="3">
-        <v>100</v>
-      </c>
       <c r="AK21" s="3">
+        <v>100</v>
+      </c>
+      <c r="AL21" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2179,11 +2218,11 @@
         <v>100</v>
       </c>
       <c r="AC22" s="3">
+        <v>100</v>
+      </c>
+      <c r="AD22" s="3">
         <v>200</v>
       </c>
-      <c r="AD22" s="3">
-        <v>100</v>
-      </c>
       <c r="AE22" s="3">
         <v>100</v>
       </c>
@@ -2194,7 +2233,7 @@
         <v>100</v>
       </c>
       <c r="AH22" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI22" s="3">
         <v>0</v>
@@ -2205,142 +2244,148 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
         <v>-300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>500</v>
       </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
       <c r="H23" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="I23" s="3">
         <v>-200</v>
       </c>
       <c r="J23" s="3">
+        <v>-200</v>
+      </c>
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="K23" s="3">
-        <v>100</v>
-      </c>
       <c r="L23" s="3">
+        <v>100</v>
+      </c>
+      <c r="M23" s="3">
         <v>-100</v>
       </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
       <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>1100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>500</v>
       </c>
-      <c r="T23" s="3">
-        <v>100</v>
-      </c>
       <c r="U23" s="3">
+        <v>100</v>
+      </c>
+      <c r="V23" s="3">
         <v>400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-100</v>
       </c>
-      <c r="Y23" s="3">
-        <v>0</v>
-      </c>
       <c r="Z23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="3">
         <v>500</v>
       </c>
-      <c r="AA23" s="3">
-        <v>100</v>
-      </c>
       <c r="AB23" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC23" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AE23" s="3">
         <v>500</v>
       </c>
-      <c r="AE23" s="3">
-        <v>0</v>
-      </c>
       <c r="AF23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="3">
         <v>200</v>
       </c>
-      <c r="AG23" s="3">
-        <v>0</v>
-      </c>
       <c r="AH23" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="3">
         <v>500</v>
       </c>
-      <c r="AI23" s="3">
-        <v>300</v>
-      </c>
       <c r="AJ23" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK23" s="3">
         <v>-200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-100</v>
       </c>
-      <c r="F24" s="3">
-        <v>100</v>
-      </c>
       <c r="G24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>200</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
@@ -2348,79 +2393,82 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="O24" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="P24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="R24" s="3">
+        <v>100</v>
+      </c>
+      <c r="S24" s="3">
         <v>400</v>
       </c>
-      <c r="S24" s="3">
-        <v>100</v>
-      </c>
       <c r="T24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V24" s="3">
+        <v>100</v>
+      </c>
+      <c r="W24" s="3">
         <v>200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-100</v>
       </c>
-      <c r="X24" s="3">
-        <v>0</v>
-      </c>
       <c r="Y24" s="3">
         <v>0</v>
       </c>
       <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
-      <c r="AA24" s="3">
-        <v>0</v>
-      </c>
       <c r="AB24" s="3">
         <v>0</v>
       </c>
       <c r="AC24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AD24" s="3">
         <v>100</v>
       </c>
       <c r="AE24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="3">
         <v>200</v>
       </c>
-      <c r="AI24" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ24" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK24" s="3">
         <v>-100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
         <v>-200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>400</v>
       </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
       <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
         <v>-200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>600</v>
       </c>
-      <c r="K26" s="3">
-        <v>100</v>
-      </c>
       <c r="L26" s="3">
+        <v>100</v>
+      </c>
+      <c r="M26" s="3">
         <v>-100</v>
       </c>
-      <c r="M26" s="3">
-        <v>0</v>
-      </c>
       <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>800</v>
       </c>
-      <c r="O26" s="3">
-        <v>300</v>
-      </c>
       <c r="P26" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q26" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="R26" s="3">
+        <v>300</v>
+      </c>
+      <c r="S26" s="3">
         <v>1000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>400</v>
       </c>
-      <c r="T26" s="3">
-        <v>100</v>
-      </c>
       <c r="U26" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="V26" s="3">
+        <v>300</v>
+      </c>
+      <c r="W26" s="3">
         <v>700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-100</v>
       </c>
-      <c r="Y26" s="3">
-        <v>0</v>
-      </c>
       <c r="Z26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3">
         <v>400</v>
       </c>
-      <c r="AA26" s="3">
-        <v>100</v>
-      </c>
       <c r="AB26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="3">
         <v>200</v>
       </c>
-      <c r="AD26" s="3">
-        <v>300</v>
-      </c>
       <c r="AE26" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AF26" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG26" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH26" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E27" s="3">
+        <v>0</v>
+      </c>
+      <c r="F27" s="3">
         <v>-200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>400</v>
       </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
       <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
         <v>-200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>600</v>
       </c>
-      <c r="K27" s="3">
-        <v>100</v>
-      </c>
       <c r="L27" s="3">
+        <v>100</v>
+      </c>
+      <c r="M27" s="3">
         <v>-100</v>
       </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
       <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>800</v>
       </c>
-      <c r="O27" s="3">
-        <v>300</v>
-      </c>
       <c r="P27" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q27" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="R27" s="3">
+        <v>300</v>
+      </c>
+      <c r="S27" s="3">
         <v>1000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>400</v>
       </c>
-      <c r="T27" s="3">
-        <v>100</v>
-      </c>
       <c r="U27" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="V27" s="3">
+        <v>300</v>
+      </c>
+      <c r="W27" s="3">
         <v>700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-100</v>
       </c>
-      <c r="Y27" s="3">
-        <v>0</v>
-      </c>
       <c r="Z27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3">
         <v>400</v>
       </c>
-      <c r="AA27" s="3">
-        <v>100</v>
-      </c>
       <c r="AB27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3">
         <v>200</v>
       </c>
-      <c r="AD27" s="3">
-        <v>300</v>
-      </c>
       <c r="AE27" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AF27" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AG27" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AH27" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AI27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ27" s="3">
         <v>200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-100</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2906,8 +2966,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2924,38 +2984,41 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-200</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
       <c r="AD29" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="AE29" s="3">
         <v>200</v>
       </c>
       <c r="AF29" s="3">
+        <v>200</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-200</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3">
         <v>0</v>
       </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>200</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3177,7 +3246,7 @@
         <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32" s="3">
         <v>0</v>
@@ -3186,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>100</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -3204,11 +3273,11 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -3216,17 +3285,17 @@
         <v>0</v>
       </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -3234,11 +3303,11 @@
         <v>0</v>
       </c>
       <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>-100</v>
       </c>
-      <c r="Y32" s="3">
-        <v>0</v>
-      </c>
       <c r="Z32" s="3">
         <v>0</v>
       </c>
@@ -3246,144 +3315,150 @@
         <v>0</v>
       </c>
       <c r="AB32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="AC32" s="3">
         <v>-100</v>
       </c>
       <c r="AD32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="AE32" s="3">
         <v>0</v>
       </c>
       <c r="AF32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-100</v>
       </c>
-      <c r="AH32" s="3">
-        <v>0</v>
-      </c>
       <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ32" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ32" s="3">
-        <v>0</v>
-      </c>
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
         <v>-200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>400</v>
       </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
       <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
         <v>-200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>600</v>
       </c>
-      <c r="K33" s="3">
-        <v>100</v>
-      </c>
       <c r="L33" s="3">
+        <v>100</v>
+      </c>
+      <c r="M33" s="3">
         <v>-100</v>
       </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
       <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>800</v>
       </c>
-      <c r="O33" s="3">
-        <v>300</v>
-      </c>
       <c r="P33" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="R33" s="3">
+        <v>300</v>
+      </c>
+      <c r="S33" s="3">
         <v>1000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>400</v>
       </c>
-      <c r="T33" s="3">
-        <v>100</v>
-      </c>
       <c r="U33" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="V33" s="3">
+        <v>300</v>
+      </c>
+      <c r="W33" s="3">
         <v>700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-100</v>
       </c>
-      <c r="Y33" s="3">
-        <v>0</v>
-      </c>
       <c r="Z33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3">
         <v>400</v>
       </c>
-      <c r="AA33" s="3">
-        <v>100</v>
-      </c>
       <c r="AB33" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC33" s="3">
         <v>-200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-100</v>
       </c>
-      <c r="AG33" s="3">
-        <v>0</v>
-      </c>
       <c r="AH33" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ33" s="3">
         <v>400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
         <v>-200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>400</v>
       </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
       <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
         <v>-200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>600</v>
       </c>
-      <c r="K35" s="3">
-        <v>100</v>
-      </c>
       <c r="L35" s="3">
+        <v>100</v>
+      </c>
+      <c r="M35" s="3">
         <v>-100</v>
       </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
       <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>800</v>
       </c>
-      <c r="O35" s="3">
-        <v>300</v>
-      </c>
       <c r="P35" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="R35" s="3">
+        <v>300</v>
+      </c>
+      <c r="S35" s="3">
         <v>1000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>400</v>
       </c>
-      <c r="T35" s="3">
-        <v>100</v>
-      </c>
       <c r="U35" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="V35" s="3">
+        <v>300</v>
+      </c>
+      <c r="W35" s="3">
         <v>700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-100</v>
       </c>
-      <c r="Y35" s="3">
-        <v>0</v>
-      </c>
       <c r="Z35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3">
         <v>400</v>
       </c>
-      <c r="AA35" s="3">
-        <v>100</v>
-      </c>
       <c r="AB35" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC35" s="3">
         <v>-200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-100</v>
       </c>
-      <c r="AG35" s="3">
-        <v>0</v>
-      </c>
       <c r="AH35" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AI35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ35" s="3">
         <v>400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42947</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42766</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3871,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E41" s="3">
         <v>4300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6300</v>
-      </c>
-      <c r="L41" s="3">
-        <v>7300</v>
       </c>
       <c r="M41" s="3">
         <v>7300</v>
       </c>
       <c r="N41" s="3">
+        <v>7300</v>
+      </c>
+      <c r="O41" s="3">
         <v>7800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3600</v>
-      </c>
-      <c r="AF41" s="3">
-        <v>4000</v>
       </c>
       <c r="AG41" s="3">
         <v>4000</v>
       </c>
       <c r="AH41" s="3">
+        <v>4000</v>
+      </c>
+      <c r="AI41" s="3">
         <v>4300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3905,19 +3994,19 @@
         <v>4000</v>
       </c>
       <c r="F42" s="3">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="G42" s="3">
         <v>3900</v>
       </c>
       <c r="H42" s="3">
+        <v>3900</v>
+      </c>
+      <c r="I42" s="3">
         <v>4800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>5200</v>
-      </c>
-      <c r="J42" s="3">
-        <v>1200</v>
       </c>
       <c r="K42" s="3">
         <v>1200</v>
@@ -3968,13 +4057,13 @@
         <v>1200</v>
       </c>
       <c r="AA42" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AB42" s="3">
         <v>1000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>900</v>
-      </c>
-      <c r="AC42" s="3">
-        <v>1000</v>
       </c>
       <c r="AD42" s="3">
         <v>1000</v>
@@ -4000,8 +4089,11 @@
       <c r="AK42" s="3">
         <v>1000</v>
       </c>
+      <c r="AL42" s="3">
+        <v>1000</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4009,7 +4101,7 @@
         <v>100</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F43" s="3">
         <v>0</v>
@@ -4069,10 +4161,10 @@
         <v>0</v>
       </c>
       <c r="Y43" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
@@ -4107,115 +4199,121 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E44" s="3">
         <v>4700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>4800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>5200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>5400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>5200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>5500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>5900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6500</v>
-      </c>
-      <c r="L44" s="3">
-        <v>5700</v>
       </c>
       <c r="M44" s="3">
         <v>5700</v>
       </c>
       <c r="N44" s="3">
+        <v>5700</v>
+      </c>
+      <c r="O44" s="3">
         <v>5800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>3900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4000</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>4200</v>
       </c>
       <c r="Z44" s="3">
         <v>4200</v>
       </c>
       <c r="AA44" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AB44" s="3">
         <v>4400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>3800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>4300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>3600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>3900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>3700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4226,7 +4324,7 @@
         <v>200</v>
       </c>
       <c r="F45" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3">
         <v>100</v>
@@ -4247,37 +4345,37 @@
         <v>100</v>
       </c>
       <c r="M45" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="N45" s="3">
+        <v>300</v>
+      </c>
+      <c r="O45" s="3">
         <v>200</v>
       </c>
-      <c r="O45" s="3">
-        <v>300</v>
-      </c>
       <c r="P45" s="3">
         <v>300</v>
       </c>
       <c r="Q45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="R45" s="3">
         <v>200</v>
       </c>
       <c r="S45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="T45" s="3">
         <v>300</v>
       </c>
       <c r="U45" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="V45" s="3">
         <v>200</v>
       </c>
       <c r="W45" s="3">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="X45" s="3">
         <v>300</v>
@@ -4298,7 +4396,7 @@
         <v>300</v>
       </c>
       <c r="AD45" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AE45" s="3">
         <v>400</v>
@@ -4307,7 +4405,7 @@
         <v>400</v>
       </c>
       <c r="AG45" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AH45" s="3">
         <v>300</v>
@@ -4316,120 +4414,126 @@
         <v>300</v>
       </c>
       <c r="AJ45" s="3">
+        <v>300</v>
+      </c>
+      <c r="AK45" s="3">
         <v>400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E46" s="3">
         <v>13600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>13200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>14000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>14700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>14400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>12700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>12000</v>
-      </c>
-      <c r="W46" s="3">
-        <v>10300</v>
       </c>
       <c r="X46" s="3">
         <v>10300</v>
       </c>
       <c r="Y46" s="3">
+        <v>10300</v>
+      </c>
+      <c r="Z46" s="3">
         <v>10500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>10900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>9600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>9400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>9700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>9900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>9300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>9000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>9100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>9500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>8900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>8500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>8900</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4460,24 +4564,24 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>300</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>300</v>
       </c>
       <c r="O47" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
       <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3">
         <v>700</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
-      </c>
       <c r="S47" s="3">
         <v>0</v>
       </c>
@@ -4494,7 +4598,7 @@
         <v>0</v>
       </c>
       <c r="X47" s="3">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="Y47" s="3">
         <v>800</v>
@@ -4509,7 +4613,7 @@
         <v>800</v>
       </c>
       <c r="AC47" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="AD47" s="3">
         <v>300</v>
@@ -4533,39 +4637,42 @@
         <v>300</v>
       </c>
       <c r="AK47" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL47" s="3">
         <v>400</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E48" s="3">
         <v>12600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>12500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>12700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>12500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>12800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>12900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>13000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>13100</v>
-      </c>
-      <c r="L48" s="3">
-        <v>12900</v>
       </c>
       <c r="M48" s="3">
         <v>12900</v>
@@ -4574,76 +4681,79 @@
         <v>12900</v>
       </c>
       <c r="O48" s="3">
+        <v>12900</v>
+      </c>
+      <c r="P48" s="3">
         <v>13800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>14300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>13700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>14500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>14300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>14500</v>
-      </c>
-      <c r="U48" s="3">
-        <v>14600</v>
       </c>
       <c r="V48" s="3">
         <v>14600</v>
       </c>
       <c r="W48" s="3">
+        <v>14600</v>
+      </c>
+      <c r="X48" s="3">
         <v>14900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>14000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13700</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>14000</v>
       </c>
       <c r="AA48" s="3">
         <v>14000</v>
       </c>
       <c r="AB48" s="3">
+        <v>14000</v>
+      </c>
+      <c r="AC48" s="3">
         <v>13000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>13100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>13000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>12100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>10500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>9800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>9600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>9600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>9500</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4651,13 +4761,13 @@
         <v>100</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H49" s="3">
         <v>0</v>
@@ -4716,14 +4826,14 @@
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-      <c r="AA49" s="3" t="s">
-        <v>8</v>
+      <c r="AA49" s="3">
+        <v>0</v>
       </c>
       <c r="AB49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC49" s="3">
-        <v>0</v>
+      <c r="AC49" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD49" s="3">
         <v>0</v>
@@ -4735,10 +4845,10 @@
         <v>0</v>
       </c>
       <c r="AG49" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AI49" s="3">
         <v>0</v>
@@ -4749,8 +4859,11 @@
       <c r="AK49" s="3">
         <v>0</v>
       </c>
+      <c r="AL49" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,8 +5079,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4978,11 +5097,11 @@
         <v>300</v>
       </c>
       <c r="G52" s="3">
+        <v>300</v>
+      </c>
+      <c r="H52" s="3">
         <v>400</v>
       </c>
-      <c r="H52" s="3">
-        <v>300</v>
-      </c>
       <c r="I52" s="3">
         <v>300</v>
       </c>
@@ -4996,7 +5115,7 @@
         <v>300</v>
       </c>
       <c r="M52" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N52" s="3">
         <v>0</v>
@@ -5034,17 +5153,17 @@
       <c r="Y52" s="3">
         <v>0</v>
       </c>
-      <c r="Z52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>0</v>
+      <c r="Z52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB52" s="3">
         <v>0</v>
       </c>
       <c r="AC52" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="AD52" s="3">
         <v>500</v>
@@ -5070,8 +5189,11 @@
       <c r="AK52" s="3">
         <v>500</v>
       </c>
+      <c r="AL52" s="3">
+        <v>500</v>
+      </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>26400</v>
+      </c>
+      <c r="E54" s="3">
         <v>26500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>26300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>26800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>26100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>27100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>27200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>28100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>28400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>29400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>29600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>29200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>27600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>27400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>26700</v>
-      </c>
-      <c r="W54" s="3">
-        <v>25200</v>
       </c>
       <c r="X54" s="3">
         <v>25200</v>
       </c>
       <c r="Y54" s="3">
+        <v>25200</v>
+      </c>
+      <c r="Z54" s="3">
         <v>25100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>25700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>24400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>23300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>23600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>23700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>22100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>20300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>19700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>20000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>19300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>18900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>19300</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,123 +5491,127 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E57" s="3">
         <v>800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1300</v>
-      </c>
-      <c r="H57" s="3">
-        <v>800</v>
       </c>
       <c r="I57" s="3">
         <v>800</v>
       </c>
       <c r="J57" s="3">
+        <v>800</v>
+      </c>
+      <c r="K57" s="3">
         <v>1200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1100</v>
-      </c>
-      <c r="V57" s="3">
-        <v>1000</v>
       </c>
       <c r="W57" s="3">
         <v>1000</v>
       </c>
       <c r="X57" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y57" s="3">
         <v>900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1000</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>1400</v>
       </c>
       <c r="AA57" s="3">
         <v>1400</v>
       </c>
       <c r="AB57" s="3">
+        <v>1400</v>
+      </c>
+      <c r="AC57" s="3">
         <v>600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>1200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>1300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>800</v>
-      </c>
-      <c r="AH57" s="3">
-        <v>1200</v>
       </c>
       <c r="AI57" s="3">
         <v>1200</v>
       </c>
       <c r="AJ57" s="3">
+        <v>1200</v>
+      </c>
+      <c r="AK57" s="3">
         <v>600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>700</v>
+      </c>
+      <c r="E58" s="3">
         <v>600</v>
-      </c>
-      <c r="E58" s="3">
-        <v>700</v>
       </c>
       <c r="F58" s="3">
         <v>700</v>
@@ -5487,22 +5620,22 @@
         <v>700</v>
       </c>
       <c r="H58" s="3">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="I58" s="3">
         <v>600</v>
       </c>
       <c r="J58" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K58" s="3">
         <v>700</v>
       </c>
       <c r="L58" s="3">
+        <v>700</v>
+      </c>
+      <c r="M58" s="3">
         <v>600</v>
-      </c>
-      <c r="M58" s="3">
-        <v>500</v>
       </c>
       <c r="N58" s="3">
         <v>500</v>
@@ -5523,10 +5656,10 @@
         <v>500</v>
       </c>
       <c r="T58" s="3">
+        <v>500</v>
+      </c>
+      <c r="U58" s="3">
         <v>600</v>
-      </c>
-      <c r="U58" s="3">
-        <v>500</v>
       </c>
       <c r="V58" s="3">
         <v>500</v>
@@ -5544,7 +5677,7 @@
         <v>500</v>
       </c>
       <c r="AA58" s="3">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AB58" s="3">
         <v>400</v>
@@ -5553,31 +5686,34 @@
         <v>400</v>
       </c>
       <c r="AD58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AE58" s="3">
         <v>300</v>
       </c>
       <c r="AF58" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="AG58" s="3">
         <v>200</v>
       </c>
       <c r="AH58" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AI58" s="3">
         <v>400</v>
       </c>
       <c r="AJ58" s="3">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AK58" s="3">
         <v>300</v>
       </c>
+      <c r="AL58" s="3">
+        <v>300</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5609,296 +5745,305 @@
         <v>0</v>
       </c>
       <c r="M59" s="3">
+        <v>0</v>
+      </c>
+      <c r="N59" s="3">
         <v>1800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1200</v>
-      </c>
-      <c r="AC59" s="3">
-        <v>1000</v>
       </c>
       <c r="AD59" s="3">
         <v>1000</v>
       </c>
       <c r="AE59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AF59" s="3">
         <v>700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1000</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>2700</v>
+        <v>2900</v>
       </c>
       <c r="E60" s="3">
         <v>2700</v>
       </c>
       <c r="F60" s="3">
+        <v>2700</v>
+      </c>
+      <c r="G60" s="3">
         <v>2900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2300</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E61" s="3">
         <v>6600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>6300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6600</v>
-      </c>
-      <c r="J61" s="3">
-        <v>6700</v>
       </c>
       <c r="K61" s="3">
         <v>6700</v>
       </c>
       <c r="L61" s="3">
+        <v>6700</v>
+      </c>
+      <c r="M61" s="3">
         <v>6800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>8000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>8200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>8500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>7500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>7600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>7700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>7600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>7700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>7800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>7600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>6600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>4300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>4200</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5929,53 +6074,53 @@
       <c r="L62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M62" s="3">
-        <v>1800</v>
+      <c r="M62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N62" s="3">
         <v>1800</v>
       </c>
       <c r="O62" s="3">
+        <v>1800</v>
+      </c>
+      <c r="P62" s="3">
         <v>1700</v>
-      </c>
-      <c r="P62" s="3">
-        <v>2100</v>
       </c>
       <c r="Q62" s="3">
         <v>2100</v>
       </c>
       <c r="R62" s="3">
+        <v>2100</v>
+      </c>
+      <c r="S62" s="3">
         <v>2200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2100</v>
-      </c>
-      <c r="U62" s="3">
-        <v>2000</v>
       </c>
       <c r="V62" s="3">
         <v>2000</v>
       </c>
       <c r="W62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="X62" s="3">
         <v>1700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1900</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>1700</v>
       </c>
       <c r="Z62" s="3">
         <v>1700</v>
       </c>
       <c r="AA62" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AB62" s="3">
         <v>1500</v>
-      </c>
-      <c r="AB62" s="3">
-        <v>600</v>
       </c>
       <c r="AC62" s="3">
         <v>600</v>
@@ -5984,10 +6129,10 @@
         <v>600</v>
       </c>
       <c r="AE62" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF62" s="3">
         <v>500</v>
-      </c>
-      <c r="AF62" s="3">
-        <v>800</v>
       </c>
       <c r="AG62" s="3">
         <v>800</v>
@@ -5996,16 +6141,19 @@
         <v>800</v>
       </c>
       <c r="AI62" s="3">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AJ62" s="3">
         <v>700</v>
       </c>
       <c r="AK62" s="3">
+        <v>700</v>
+      </c>
+      <c r="AL62" s="3">
         <v>800</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,8 +6479,11 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6334,106 +6491,109 @@
         <v>10100</v>
       </c>
       <c r="E66" s="3">
+        <v>10100</v>
+      </c>
+      <c r="F66" s="3">
         <v>9800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>13200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>12400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>12100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>12500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>10500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>10900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>10800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>7000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7300</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>8200</v>
+        <v>8000</v>
       </c>
       <c r="E72" s="3">
         <v>8200</v>
       </c>
       <c r="F72" s="3">
+        <v>8200</v>
+      </c>
+      <c r="G72" s="3">
         <v>8400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>6700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>6500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>6200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>3800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4100</v>
-      </c>
-      <c r="Y72" s="3">
-        <v>4200</v>
       </c>
       <c r="Z72" s="3">
         <v>4200</v>
       </c>
       <c r="AA72" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AB72" s="3">
         <v>3800</v>
-      </c>
-      <c r="AB72" s="3">
-        <v>3700</v>
       </c>
       <c r="AC72" s="3">
         <v>3700</v>
       </c>
       <c r="AD72" s="3">
+        <v>3700</v>
+      </c>
+      <c r="AE72" s="3">
         <v>3800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>3500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>3200</v>
-      </c>
-      <c r="AG72" s="3">
-        <v>3300</v>
       </c>
       <c r="AH72" s="3">
         <v>3300</v>
       </c>
       <c r="AI72" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>2800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>2900</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,82 +7509,85 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>16400</v>
+        <v>16300</v>
       </c>
       <c r="E76" s="3">
         <v>16400</v>
       </c>
       <c r="F76" s="3">
+        <v>16400</v>
+      </c>
+      <c r="G76" s="3">
         <v>16600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>17000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>17200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16500</v>
-      </c>
-      <c r="M76" s="3">
-        <v>16700</v>
       </c>
       <c r="N76" s="3">
         <v>16700</v>
       </c>
       <c r="O76" s="3">
+        <v>16700</v>
+      </c>
+      <c r="P76" s="3">
         <v>15900</v>
-      </c>
-      <c r="P76" s="3">
-        <v>15500</v>
       </c>
       <c r="Q76" s="3">
         <v>15500</v>
       </c>
       <c r="R76" s="3">
+        <v>15500</v>
+      </c>
+      <c r="S76" s="3">
         <v>15200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>13000</v>
-      </c>
-      <c r="Y76" s="3">
-        <v>13200</v>
       </c>
       <c r="Z76" s="3">
         <v>13200</v>
       </c>
       <c r="AA76" s="3">
-        <v>12800</v>
+        <v>13200</v>
       </c>
       <c r="AB76" s="3">
         <v>12800</v>
@@ -7411,31 +7596,34 @@
         <v>12800</v>
       </c>
       <c r="AD76" s="3">
+        <v>12800</v>
+      </c>
+      <c r="AE76" s="3">
         <v>12900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>12500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12300</v>
-      </c>
-      <c r="AG76" s="3">
-        <v>12400</v>
       </c>
       <c r="AH76" s="3">
         <v>12400</v>
       </c>
       <c r="AI76" s="3">
+        <v>12400</v>
+      </c>
+      <c r="AJ76" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>11900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12000</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42947</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42766</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42674</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E81" s="3">
+        <v>0</v>
+      </c>
+      <c r="F81" s="3">
         <v>-200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>400</v>
       </c>
-      <c r="G81" s="3">
-        <v>0</v>
-      </c>
       <c r="H81" s="3">
+        <v>0</v>
+      </c>
+      <c r="I81" s="3">
         <v>-200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>600</v>
       </c>
-      <c r="K81" s="3">
-        <v>100</v>
-      </c>
       <c r="L81" s="3">
+        <v>100</v>
+      </c>
+      <c r="M81" s="3">
         <v>-100</v>
       </c>
-      <c r="M81" s="3">
-        <v>0</v>
-      </c>
       <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>800</v>
       </c>
-      <c r="O81" s="3">
-        <v>300</v>
-      </c>
       <c r="P81" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="Q81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="R81" s="3">
+        <v>300</v>
+      </c>
+      <c r="S81" s="3">
         <v>1000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>400</v>
       </c>
-      <c r="T81" s="3">
-        <v>100</v>
-      </c>
       <c r="U81" s="3">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="V81" s="3">
+        <v>300</v>
+      </c>
+      <c r="W81" s="3">
         <v>700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-100</v>
       </c>
-      <c r="Y81" s="3">
-        <v>0</v>
-      </c>
       <c r="Z81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="3">
         <v>400</v>
       </c>
-      <c r="AA81" s="3">
-        <v>100</v>
-      </c>
       <c r="AB81" s="3">
+        <v>100</v>
+      </c>
+      <c r="AC81" s="3">
         <v>-200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-100</v>
       </c>
-      <c r="AG81" s="3">
-        <v>0</v>
-      </c>
       <c r="AH81" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AI81" s="3">
+        <v>300</v>
+      </c>
+      <c r="AJ81" s="3">
         <v>400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,17 +7996,18 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>300</v>
+      </c>
+      <c r="E83" s="3">
         <v>400</v>
       </c>
-      <c r="E83" s="3">
-        <v>300</v>
-      </c>
       <c r="F83" s="3">
         <v>300</v>
       </c>
@@ -7817,11 +8015,11 @@
         <v>300</v>
       </c>
       <c r="H83" s="3">
+        <v>300</v>
+      </c>
+      <c r="I83" s="3">
         <v>500</v>
       </c>
-      <c r="I83" s="3">
-        <v>300</v>
-      </c>
       <c r="J83" s="3">
         <v>300</v>
       </c>
@@ -7880,14 +8078,14 @@
         <v>300</v>
       </c>
       <c r="AC83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AD83" s="3">
         <v>800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>500</v>
       </c>
-      <c r="AE83" s="3">
-        <v>300</v>
-      </c>
       <c r="AF83" s="3">
         <v>300</v>
       </c>
@@ -7895,19 +8093,22 @@
         <v>300</v>
       </c>
       <c r="AH83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AI83" s="3">
         <v>200</v>
       </c>
-      <c r="AI83" s="3">
-        <v>300</v>
-      </c>
       <c r="AJ83" s="3">
         <v>300</v>
       </c>
       <c r="AK83" s="3">
+        <v>300</v>
+      </c>
+      <c r="AL83" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
         <v>200</v>
       </c>
-      <c r="E89" s="3">
-        <v>100</v>
-      </c>
       <c r="F89" s="3">
+        <v>100</v>
+      </c>
+      <c r="G89" s="3">
         <v>1200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-500</v>
       </c>
-      <c r="L89" s="3">
-        <v>300</v>
-      </c>
       <c r="M89" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="N89" s="3">
+        <v>0</v>
+      </c>
+      <c r="O89" s="3">
         <v>1600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>1000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>400</v>
-      </c>
-      <c r="AC89" s="3">
-        <v>800</v>
       </c>
       <c r="AD89" s="3">
         <v>800</v>
       </c>
       <c r="AE89" s="3">
+        <v>800</v>
+      </c>
+      <c r="AF89" s="3">
         <v>-100</v>
       </c>
-      <c r="AF89" s="3">
-        <v>100</v>
-      </c>
       <c r="AG89" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH89" s="3">
         <v>-100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>1100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,25 +8806,26 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-100</v>
+        <v>-400</v>
       </c>
       <c r="E91" s="3">
         <v>-100</v>
       </c>
       <c r="F91" s="3">
+        <v>-100</v>
+      </c>
+      <c r="G91" s="3">
         <v>-200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-300</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-200</v>
       </c>
       <c r="I91" s="3">
         <v>-200</v>
@@ -8614,88 +8834,91 @@
         <v>-200</v>
       </c>
       <c r="K91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="L91" s="3">
         <v>-400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-200</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-300</v>
       </c>
       <c r="N91" s="3">
         <v>-300</v>
       </c>
       <c r="O91" s="3">
+        <v>-300</v>
+      </c>
+      <c r="P91" s="3">
         <v>-200</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-300</v>
       </c>
       <c r="Q91" s="3">
         <v>-300</v>
       </c>
       <c r="R91" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="S91" s="3">
         <v>-200</v>
       </c>
       <c r="T91" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U91" s="3">
         <v>-300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-200</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
-      </c>
       <c r="W91" s="3">
+        <v>0</v>
+      </c>
+      <c r="X91" s="3">
         <v>-400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-200</v>
       </c>
-      <c r="AJ91" s="3">
-        <v>0</v>
-      </c>
       <c r="AK91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL91" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>-100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>700</v>
       </c>
-      <c r="H94" s="3">
-        <v>300</v>
-      </c>
       <c r="I94" s="3">
+        <v>300</v>
+      </c>
+      <c r="J94" s="3">
         <v>-4200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-200</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-300</v>
       </c>
       <c r="Q94" s="3">
         <v>-300</v>
       </c>
       <c r="R94" s="3">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="S94" s="3">
         <v>-200</v>
       </c>
       <c r="T94" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-200</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
       <c r="W94" s="3">
+        <v>0</v>
+      </c>
+      <c r="X94" s="3">
         <v>-400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-700</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>-400</v>
       </c>
       <c r="AH94" s="3">
         <v>-400</v>
       </c>
       <c r="AI94" s="3">
-        <v>100</v>
+        <v>-400</v>
       </c>
       <c r="AJ94" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,8 +9286,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9086,8 +9319,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9161,8 +9394,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,8 +9724,11 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9497,10 +9742,10 @@
         <v>-100</v>
       </c>
       <c r="G100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="H100" s="3">
         <v>-700</v>
-      </c>
-      <c r="H100" s="3">
-        <v>-100</v>
       </c>
       <c r="I100" s="3">
         <v>-100</v>
@@ -9515,25 +9760,25 @@
         <v>-100</v>
       </c>
       <c r="M100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="N100" s="3">
         <v>-200</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-100</v>
       </c>
       <c r="O100" s="3">
         <v>-100</v>
       </c>
       <c r="P100" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="Q100" s="3">
         <v>-200</v>
       </c>
       <c r="R100" s="3">
+        <v>-200</v>
+      </c>
+      <c r="S100" s="3">
         <v>-1300</v>
-      </c>
-      <c r="S100" s="3">
-        <v>-100</v>
       </c>
       <c r="T100" s="3">
         <v>-100</v>
@@ -9545,37 +9790,37 @@
         <v>-100</v>
       </c>
       <c r="W100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="X100" s="3">
         <v>1000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-100</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>2800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>1500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>700</v>
-      </c>
-      <c r="AG100" s="3">
-        <v>-100</v>
       </c>
       <c r="AH100" s="3">
         <v>-100</v>
@@ -9589,8 +9834,11 @@
       <c r="AK100" s="3">
         <v>-100</v>
       </c>
+      <c r="AL100" s="3">
+        <v>-100</v>
+      </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9621,8 +9869,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9696,111 +9944,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>100</v>
+        <v>-1000</v>
       </c>
       <c r="E102" s="3">
+        <v>100</v>
+      </c>
+      <c r="F102" s="3">
         <v>-100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1000</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
       <c r="M102" s="3">
+        <v>0</v>
+      </c>
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-2200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-100</v>
       </c>
-      <c r="T102" s="3">
-        <v>300</v>
-      </c>
       <c r="U102" s="3">
+        <v>300</v>
+      </c>
+      <c r="V102" s="3">
         <v>700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
-        <v>300</v>
-      </c>
       <c r="AC102" s="3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="AD102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AE102" s="3">
         <v>400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AF102" s="3">
-        <v>100</v>
-      </c>
       <c r="AG102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AH102" s="3">
         <v>-300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>700</v>
       </c>
-      <c r="AI102" s="3">
-        <v>100</v>
-      </c>
       <c r="AJ102" s="3">
+        <v>100</v>
+      </c>
+      <c r="AK102" s="3">
         <v>-300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-200</v>
       </c>
     </row>
